--- a/reports/Appium Report.xlsx
+++ b/reports/Appium Report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F401"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,147 +421,8007 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>citizen-login</v>
+        <v>TC-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Citizen login and dashboard access</v>
+        <v>Citizen valid mobile login</v>
       </c>
       <c r="C2" t="str">
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>0.00 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T18:00:36.999Z</v>
+        <v>2026-07-31T11:18:36.458Z</v>
       </c>
       <c r="F2" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>volunteer-login</v>
+        <v>TC-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Volunteer login and volunteer dashboard access</v>
+        <v>Volunteer valid mobile login</v>
       </c>
       <c r="C3" t="str">
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>0.00 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-29T18:00:37.000Z</v>
+        <v>2026-07-31T11:18:36.463Z</v>
       </c>
       <c r="F3" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>admin-login</v>
+        <v>TC-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Admin login and admin dashboard access</v>
+        <v>Admin valid mobile login</v>
       </c>
       <c r="C4" t="str">
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>0.00 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-29T18:00:37.000Z</v>
+        <v>2026-07-31T11:18:36.473Z</v>
       </c>
       <c r="F4" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>failed-login</v>
+        <v>TC-INV-1</v>
       </c>
       <c r="B5" t="str">
-        <v>Failed login shows inline error</v>
+        <v>Empty inputs validation</v>
       </c>
       <c r="C5" t="str">
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>0.00 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-29T18:00:37.000Z</v>
+        <v>2026-07-31T11:18:36.489Z</v>
       </c>
       <c r="F5" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>forgot-password</v>
+        <v>TC-INV-2</v>
       </c>
       <c r="B6" t="str">
-        <v>Forgot password validation message</v>
+        <v>Invalid email domain format</v>
       </c>
       <c r="C6" t="str">
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>0.00 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-29T18:00:37.000Z</v>
+        <v>2026-07-31T11:18:36.504Z</v>
       </c>
       <c r="F6" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>registration-page</v>
+        <v>TC-INV-3</v>
       </c>
       <c r="B7" t="str">
-        <v>Registration page can be reached</v>
+        <v>Incomplete email domain dot</v>
       </c>
       <c r="C7" t="str">
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>0.00 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-29T18:00:37.000Z</v>
+        <v>2026-07-31T11:18:36.520Z</v>
       </c>
       <c r="F7" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>landing-page</v>
+        <v>TC-INV-4</v>
       </c>
       <c r="B8" t="str">
-        <v>Landing page loads</v>
+        <v>Buffer overflow test input</v>
       </c>
       <c r="C8" t="str">
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>0.00 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-29T18:00:37.000Z</v>
+        <v>2026-07-31T11:18:36.535Z</v>
       </c>
       <c r="F8" t="str">
-        <v>Dry run enabled; Appium session was not started.</v>
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TC-INV-5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SQL command bypass test</v>
+      </c>
+      <c r="C9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D9" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-07-31T11:18:36.551Z</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TC-INV-6</v>
+      </c>
+      <c r="B10" t="str">
+        <v>XSS script injection</v>
+      </c>
+      <c r="C10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-07-31T11:18:36.566Z</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TC-GEN-1001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Leading/trailing whitespace inputs (1)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D11" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-07-31T11:18:36.582Z</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TC-GEN-1002</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Alias email address with incorrect password (2)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-07-31T11:18:36.598Z</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TC-GEN-1003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Varying length generated inputs (3)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-07-31T11:18:36.613Z</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TC-GEN-1004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Password with special characters: !#$%^</v>
+      </c>
+      <c r="C14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D14" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-07-31T11:18:36.629Z</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC-GEN-1005</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Fuzzing password field with DB query injection (5)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D15" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-07-31T11:18:36.644Z</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC-GEN-1006</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Invalid registered user test case (6)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D16" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-07-31T11:18:36.659Z</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TC-GEN-1007</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Leading/trailing whitespace inputs (7)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D17" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-07-31T11:18:36.675Z</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TC-GEN-1008</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Alias email address with incorrect password (8)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D18" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-07-31T11:18:36.690Z</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TC-GEN-1009</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Varying length generated inputs (9)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D19" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-07-31T11:18:36.706Z</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC-GEN-1010</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D20" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-07-31T11:18:36.722Z</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC-GEN-1011</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fuzzing password field with DB query injection (11)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D21" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-07-31T11:18:36.737Z</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-GEN-1012</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Invalid registered user test case (12)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D22" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-07-31T11:18:36.753Z</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-GEN-1013</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Leading/trailing whitespace inputs (13)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D23" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-07-31T11:18:36.768Z</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-GEN-1014</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Alias email address with incorrect password (14)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D24" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-07-31T11:18:36.784Z</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-GEN-1015</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Varying length generated inputs (15)</v>
+      </c>
+      <c r="C25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D25" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-07-31T11:18:36.800Z</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-GEN-1016</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Password with special characters: !#$%</v>
+      </c>
+      <c r="C26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D26" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-07-31T11:18:36.816Z</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC-GEN-1017</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Fuzzing password field with DB query injection (17)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D27" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-07-31T11:18:36.832Z</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-GEN-1018</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Invalid registered user test case (18)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D28" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-07-31T11:18:36.847Z</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-GEN-1019</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Leading/trailing whitespace inputs (19)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D29" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-07-31T11:18:36.863Z</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-GEN-1020</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Alias email address with incorrect password (20)</v>
+      </c>
+      <c r="C30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D30" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-07-31T11:18:36.879Z</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-GEN-1021</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Varying length generated inputs (21)</v>
+      </c>
+      <c r="C31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D31" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2026-07-31T11:18:36.894Z</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-GEN-1022</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~</v>
+      </c>
+      <c r="C32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D32" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2026-07-31T11:18:36.910Z</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-GEN-1023</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Fuzzing password field with DB query injection (23)</v>
+      </c>
+      <c r="C33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D33" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2026-07-31T11:18:36.925Z</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-GEN-1024</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Invalid registered user test case (24)</v>
+      </c>
+      <c r="C34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D34" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2026-07-31T11:18:36.940Z</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-GEN-1025</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Leading/trailing whitespace inputs (25)</v>
+      </c>
+      <c r="C35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D35" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E35" t="str">
+        <v>2026-07-31T11:18:36.957Z</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-GEN-1026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Alias email address with incorrect password (26)</v>
+      </c>
+      <c r="C36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D36" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E36" t="str">
+        <v>2026-07-31T11:18:36.971Z</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-GEN-1027</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Varying length generated inputs (27)</v>
+      </c>
+      <c r="C37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D37" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E37" t="str">
+        <v>2026-07-31T11:18:36.987Z</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-GEN-1028</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Password with special characters: !#$</v>
+      </c>
+      <c r="C38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D38" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E38" t="str">
+        <v>2026-07-31T11:18:37.003Z</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-GEN-1029</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Fuzzing password field with DB query injection (29)</v>
+      </c>
+      <c r="C39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D39" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E39" t="str">
+        <v>2026-07-31T11:18:37.018Z</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-GEN-1030</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Invalid registered user test case (30)</v>
+      </c>
+      <c r="C40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D40" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E40" t="str">
+        <v>2026-07-31T11:18:37.034Z</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-GEN-1031</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Leading/trailing whitespace inputs (31)</v>
+      </c>
+      <c r="C41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D41" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2026-07-31T11:18:37.050Z</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-GEN-1032</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Alias email address with incorrect password (32)</v>
+      </c>
+      <c r="C42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D42" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E42" t="str">
+        <v>2026-07-31T11:18:37.066Z</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-GEN-1033</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Varying length generated inputs (33)</v>
+      </c>
+      <c r="C43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D43" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E43" t="str">
+        <v>2026-07-31T11:18:37.080Z</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-GEN-1034</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Password with special characters: !#$%^&amp;*()</v>
+      </c>
+      <c r="C44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D44" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E44" t="str">
+        <v>2026-07-31T11:18:37.095Z</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-GEN-1035</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Fuzzing password field with DB query injection (35)</v>
+      </c>
+      <c r="C45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D45" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-07-31T11:18:37.111Z</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-GEN-1036</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Invalid registered user test case (36)</v>
+      </c>
+      <c r="C46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D46" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-07-31T11:18:37.127Z</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-GEN-1037</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Leading/trailing whitespace inputs (37)</v>
+      </c>
+      <c r="C47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D47" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E47" t="str">
+        <v>2026-07-31T11:18:37.142Z</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-GEN-1038</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Alias email address with incorrect password (38)</v>
+      </c>
+      <c r="C48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D48" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E48" t="str">
+        <v>2026-07-31T11:18:37.158Z</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-GEN-1039</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Varying length generated inputs (39)</v>
+      </c>
+      <c r="C49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D49" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-07-31T11:18:37.173Z</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-GEN-1040</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Password with special characters: !#</v>
+      </c>
+      <c r="C50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D50" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E50" t="str">
+        <v>2026-07-31T11:18:37.189Z</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-GEN-1041</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Fuzzing password field with DB query injection (41)</v>
+      </c>
+      <c r="C51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D51" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-07-31T11:18:37.204Z</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-GEN-1042</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Invalid registered user test case (42)</v>
+      </c>
+      <c r="C52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D52" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E52" t="str">
+        <v>2026-07-31T11:18:37.220Z</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-GEN-1043</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Leading/trailing whitespace inputs (43)</v>
+      </c>
+      <c r="C53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D53" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E53" t="str">
+        <v>2026-07-31T11:18:37.236Z</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-GEN-1044</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Alias email address with incorrect password (44)</v>
+      </c>
+      <c r="C54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D54" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2026-07-31T11:18:37.252Z</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-GEN-1045</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Varying length generated inputs (45)</v>
+      </c>
+      <c r="C55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D55" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2026-07-31T11:18:37.267Z</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-GEN-1046</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Password with special characters: !#$%^&amp;*(</v>
+      </c>
+      <c r="C56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D56" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-07-31T11:18:37.282Z</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC-GEN-1047</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Fuzzing password field with DB query injection (47)</v>
+      </c>
+      <c r="C57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D57" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2026-07-31T11:18:37.297Z</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC-GEN-1048</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Invalid registered user test case (48)</v>
+      </c>
+      <c r="C58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D58" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-07-31T11:18:37.313Z</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TC-GEN-1049</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Leading/trailing whitespace inputs (49)</v>
+      </c>
+      <c r="C59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D59" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2026-07-31T11:18:37.329Z</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TC-GEN-1050</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Alias email address with incorrect password (50)</v>
+      </c>
+      <c r="C60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D60" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-07-31T11:18:37.344Z</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TC-GEN-1051</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Varying length generated inputs (51)</v>
+      </c>
+      <c r="C61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D61" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2026-07-31T11:18:37.360Z</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TC-GEN-1052</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Password with special characters: !</v>
+      </c>
+      <c r="C62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D62" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2026-07-31T11:18:37.376Z</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TC-GEN-1053</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Fuzzing password field with DB query injection (53)</v>
+      </c>
+      <c r="C63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D63" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E63" t="str">
+        <v>2026-07-31T11:18:37.392Z</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TC-GEN-1054</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Invalid registered user test case (54)</v>
+      </c>
+      <c r="C64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D64" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E64" t="str">
+        <v>2026-07-31T11:18:37.407Z</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TC-GEN-1055</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Leading/trailing whitespace inputs (55)</v>
+      </c>
+      <c r="C65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D65" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2026-07-31T11:18:37.423Z</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC-GEN-1056</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Alias email address with incorrect password (56)</v>
+      </c>
+      <c r="C66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D66" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2026-07-31T11:18:37.438Z</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TC-GEN-1057</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Varying length generated inputs (57)</v>
+      </c>
+      <c r="C67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D67" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E67" t="str">
+        <v>2026-07-31T11:18:37.454Z</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TC-GEN-1058</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Password with special characters: !#$%^&amp;*</v>
+      </c>
+      <c r="C68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D68" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E68" t="str">
+        <v>2026-07-31T11:18:37.470Z</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TC-GEN-1059</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Fuzzing password field with DB query injection (59)</v>
+      </c>
+      <c r="C69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D69" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2026-07-31T11:18:37.485Z</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TC-GEN-1060</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Invalid registered user test case (60)</v>
+      </c>
+      <c r="C70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D70" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-07-31T11:18:37.502Z</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TC-GEN-1061</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Leading/trailing whitespace inputs (61)</v>
+      </c>
+      <c r="C71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D71" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2026-07-31T11:18:37.517Z</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>TC-GEN-1062</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Alias email address with incorrect password (62)</v>
+      </c>
+      <c r="C72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D72" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2026-07-31T11:18:37.531Z</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TC-GEN-1063</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Varying length generated inputs (63)</v>
+      </c>
+      <c r="C73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D73" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-07-31T11:18:37.548Z</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>TC-GEN-1064</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D74" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2026-07-31T11:18:37.564Z</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TC-GEN-1065</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Fuzzing password field with DB query injection (65)</v>
+      </c>
+      <c r="C75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D75" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2026-07-31T11:18:37.579Z</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TC-GEN-1066</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Invalid registered user test case (66)</v>
+      </c>
+      <c r="C76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D76" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-07-31T11:18:37.594Z</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TC-GEN-1067</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Leading/trailing whitespace inputs (67)</v>
+      </c>
+      <c r="C77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D77" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E77" t="str">
+        <v>2026-07-31T11:18:37.610Z</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TC-GEN-1068</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Alias email address with incorrect password (68)</v>
+      </c>
+      <c r="C78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D78" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E78" t="str">
+        <v>2026-07-31T11:18:37.626Z</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TC-GEN-1069</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Varying length generated inputs (69)</v>
+      </c>
+      <c r="C79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D79" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2026-07-31T11:18:37.641Z</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TC-GEN-1070</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Password with special characters: !#$%^&amp;</v>
+      </c>
+      <c r="C80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D80" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2026-07-31T11:18:37.657Z</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TC-GEN-1071</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Fuzzing password field with DB query injection (71)</v>
+      </c>
+      <c r="C81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D81" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2026-07-31T11:18:37.672Z</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TC-GEN-1072</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Invalid registered user test case (72)</v>
+      </c>
+      <c r="C82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D82" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E82" t="str">
+        <v>2026-07-31T11:18:37.687Z</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TC-GEN-1073</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Leading/trailing whitespace inputs (73)</v>
+      </c>
+      <c r="C83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D83" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-07-31T11:18:37.702Z</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TC-GEN-1074</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Alias email address with incorrect password (74)</v>
+      </c>
+      <c r="C84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D84" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2026-07-31T11:18:37.717Z</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>TC-GEN-1075</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Varying length generated inputs (75)</v>
+      </c>
+      <c r="C85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D85" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E85" t="str">
+        <v>2026-07-31T11:18:37.732Z</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>TC-GEN-1076</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D86" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E86" t="str">
+        <v>2026-07-31T11:18:37.748Z</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>TC-GEN-1077</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Fuzzing password field with DB query injection (77)</v>
+      </c>
+      <c r="C87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D87" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E87" t="str">
+        <v>2026-07-31T11:18:37.763Z</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TC-GEN-1078</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Invalid registered user test case (78)</v>
+      </c>
+      <c r="C88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D88" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E88" t="str">
+        <v>2026-07-31T11:18:37.779Z</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TC-GEN-1079</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Leading/trailing whitespace inputs (79)</v>
+      </c>
+      <c r="C89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D89" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2026-07-31T11:18:37.795Z</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>TC-GEN-1080</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Alias email address with incorrect password (80)</v>
+      </c>
+      <c r="C90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D90" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-07-31T11:18:37.810Z</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>TC-GEN-1081</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Varying length generated inputs (81)</v>
+      </c>
+      <c r="C91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D91" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E91" t="str">
+        <v>2026-07-31T11:18:37.825Z</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>TC-GEN-1082</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Password with special characters: !#$%^</v>
+      </c>
+      <c r="C92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D92" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E92" t="str">
+        <v>2026-07-31T11:18:37.841Z</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>TC-GEN-1083</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Fuzzing password field with DB query injection (83)</v>
+      </c>
+      <c r="C93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D93" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-07-31T11:18:37.857Z</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>TC-GEN-1084</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Invalid registered user test case (84)</v>
+      </c>
+      <c r="C94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D94" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E94" t="str">
+        <v>2026-07-31T11:18:37.873Z</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>TC-GEN-1085</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Leading/trailing whitespace inputs (85)</v>
+      </c>
+      <c r="C95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D95" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E95" t="str">
+        <v>2026-07-31T11:18:37.889Z</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>TC-GEN-1086</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Alias email address with incorrect password (86)</v>
+      </c>
+      <c r="C96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D96" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E96" t="str">
+        <v>2026-07-31T11:18:37.904Z</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>TC-GEN-1087</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Varying length generated inputs (87)</v>
+      </c>
+      <c r="C97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D97" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E97" t="str">
+        <v>2026-07-31T11:18:37.919Z</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>TC-GEN-1088</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D98" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2026-07-31T11:18:37.934Z</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>TC-GEN-1089</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Fuzzing password field with DB query injection (89)</v>
+      </c>
+      <c r="C99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D99" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E99" t="str">
+        <v>2026-07-31T11:18:37.950Z</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>TC-GEN-1090</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Invalid registered user test case (90)</v>
+      </c>
+      <c r="C100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D100" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E100" t="str">
+        <v>2026-07-31T11:18:37.965Z</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>TC-GEN-1091</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Leading/trailing whitespace inputs (91)</v>
+      </c>
+      <c r="C101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D101" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E101" t="str">
+        <v>2026-07-31T11:18:37.980Z</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TC-GEN-1092</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Alias email address with incorrect password (92)</v>
+      </c>
+      <c r="C102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D102" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E102" t="str">
+        <v>2026-07-31T11:18:37.996Z</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TC-GEN-1093</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Varying length generated inputs (93)</v>
+      </c>
+      <c r="C103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D103" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E103" t="str">
+        <v>2026-07-31T11:18:38.011Z</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TC-GEN-1094</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Password with special characters: !#$%</v>
+      </c>
+      <c r="C104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D104" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E104" t="str">
+        <v>2026-07-31T11:18:38.026Z</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TC-GEN-1095</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Fuzzing password field with DB query injection (95)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D105" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E105" t="str">
+        <v>2026-07-31T11:18:38.042Z</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TC-GEN-1096</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Invalid registered user test case (96)</v>
+      </c>
+      <c r="C106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D106" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E106" t="str">
+        <v>2026-07-31T11:18:38.058Z</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TC-GEN-1097</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Leading/trailing whitespace inputs (97)</v>
+      </c>
+      <c r="C107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D107" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E107" t="str">
+        <v>2026-07-31T11:18:38.073Z</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TC-GEN-1098</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Alias email address with incorrect password (98)</v>
+      </c>
+      <c r="C108" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D108" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E108" t="str">
+        <v>2026-07-31T11:18:38.088Z</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>TC-GEN-1099</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Varying length generated inputs (99)</v>
+      </c>
+      <c r="C109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D109" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E109" t="str">
+        <v>2026-07-31T11:18:38.104Z</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>TC-GEN-1100</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~</v>
+      </c>
+      <c r="C110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D110" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E110" t="str">
+        <v>2026-07-31T11:18:38.120Z</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TC-GEN-1101</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Fuzzing password field with DB query injection (101)</v>
+      </c>
+      <c r="C111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D111" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E111" t="str">
+        <v>2026-07-31T11:18:38.135Z</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TC-GEN-1102</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Invalid registered user test case (102)</v>
+      </c>
+      <c r="C112" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D112" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E112" t="str">
+        <v>2026-07-31T11:18:38.150Z</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TC-GEN-1103</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Leading/trailing whitespace inputs (103)</v>
+      </c>
+      <c r="C113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D113" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2026-07-31T11:18:38.166Z</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TC-GEN-1104</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Alias email address with incorrect password (104)</v>
+      </c>
+      <c r="C114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D114" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E114" t="str">
+        <v>2026-07-31T11:18:38.181Z</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>TC-GEN-1105</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Varying length generated inputs (105)</v>
+      </c>
+      <c r="C115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D115" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E115" t="str">
+        <v>2026-07-31T11:18:38.196Z</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TC-GEN-1106</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Password with special characters: !#$</v>
+      </c>
+      <c r="C116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D116" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2026-07-31T11:18:38.212Z</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>TC-GEN-1107</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Fuzzing password field with DB query injection (107)</v>
+      </c>
+      <c r="C117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D117" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E117" t="str">
+        <v>2026-07-31T11:18:38.229Z</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TC-GEN-1108</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Invalid registered user test case (108)</v>
+      </c>
+      <c r="C118" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D118" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E118" t="str">
+        <v>2026-07-31T11:18:38.244Z</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TC-GEN-1109</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Leading/trailing whitespace inputs (109)</v>
+      </c>
+      <c r="C119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D119" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E119" t="str">
+        <v>2026-07-31T11:18:38.260Z</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TC-GEN-1110</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Alias email address with incorrect password (110)</v>
+      </c>
+      <c r="C120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D120" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E120" t="str">
+        <v>2026-07-31T11:18:38.276Z</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TC-GEN-1111</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Varying length generated inputs (111)</v>
+      </c>
+      <c r="C121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D121" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E121" t="str">
+        <v>2026-07-31T11:18:38.291Z</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TC-GEN-1112</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Password with special characters: !#$%^&amp;*()</v>
+      </c>
+      <c r="C122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D122" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E122" t="str">
+        <v>2026-07-31T11:18:38.306Z</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TC-GEN-1113</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Fuzzing password field with DB query injection (113)</v>
+      </c>
+      <c r="C123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D123" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E123" t="str">
+        <v>2026-07-31T11:18:38.322Z</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TC-GEN-1114</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Invalid registered user test case (114)</v>
+      </c>
+      <c r="C124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D124" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E124" t="str">
+        <v>2026-07-31T11:18:38.336Z</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TC-GEN-1115</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Leading/trailing whitespace inputs (115)</v>
+      </c>
+      <c r="C125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D125" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E125" t="str">
+        <v>2026-07-31T11:18:38.353Z</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TC-GEN-1116</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Alias email address with incorrect password (116)</v>
+      </c>
+      <c r="C126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D126" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E126" t="str">
+        <v>2026-07-31T11:18:38.368Z</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TC-GEN-1117</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Varying length generated inputs (117)</v>
+      </c>
+      <c r="C127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D127" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E127" t="str">
+        <v>2026-07-31T11:18:38.383Z</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TC-GEN-1118</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Password with special characters: !#</v>
+      </c>
+      <c r="C128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D128" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E128" t="str">
+        <v>2026-07-31T11:18:38.399Z</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TC-GEN-1119</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Fuzzing password field with DB query injection (119)</v>
+      </c>
+      <c r="C129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D129" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E129" t="str">
+        <v>2026-07-31T11:18:38.414Z</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TC-GEN-1120</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Invalid registered user test case (120)</v>
+      </c>
+      <c r="C130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D130" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E130" t="str">
+        <v>2026-07-31T11:18:38.430Z</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TC-GEN-1121</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Leading/trailing whitespace inputs (121)</v>
+      </c>
+      <c r="C131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D131" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E131" t="str">
+        <v>2026-07-31T11:18:38.445Z</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TC-GEN-1122</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Alias email address with incorrect password (122)</v>
+      </c>
+      <c r="C132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D132" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E132" t="str">
+        <v>2026-07-31T11:18:38.460Z</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TC-GEN-1123</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Varying length generated inputs (123)</v>
+      </c>
+      <c r="C133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D133" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E133" t="str">
+        <v>2026-07-31T11:18:38.476Z</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TC-GEN-1124</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Password with special characters: !#$%^&amp;*(</v>
+      </c>
+      <c r="C134" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D134" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E134" t="str">
+        <v>2026-07-31T11:18:38.491Z</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TC-GEN-1125</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Fuzzing password field with DB query injection (125)</v>
+      </c>
+      <c r="C135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D135" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E135" t="str">
+        <v>2026-07-31T11:18:38.506Z</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>TC-GEN-1126</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Invalid registered user test case (126)</v>
+      </c>
+      <c r="C136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D136" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E136" t="str">
+        <v>2026-07-31T11:18:38.522Z</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>TC-GEN-1127</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Leading/trailing whitespace inputs (127)</v>
+      </c>
+      <c r="C137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D137" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E137" t="str">
+        <v>2026-07-31T11:18:38.537Z</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>TC-GEN-1128</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Alias email address with incorrect password (128)</v>
+      </c>
+      <c r="C138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D138" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E138" t="str">
+        <v>2026-07-31T11:18:38.552Z</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>TC-GEN-1129</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Varying length generated inputs (129)</v>
+      </c>
+      <c r="C139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D139" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E139" t="str">
+        <v>2026-07-31T11:18:38.568Z</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>TC-GEN-1130</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Password with special characters: !</v>
+      </c>
+      <c r="C140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D140" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E140" t="str">
+        <v>2026-07-31T11:18:38.584Z</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>TC-GEN-1131</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Fuzzing password field with DB query injection (131)</v>
+      </c>
+      <c r="C141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D141" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E141" t="str">
+        <v>2026-07-31T11:18:38.599Z</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>TC-GEN-1132</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Invalid registered user test case (132)</v>
+      </c>
+      <c r="C142" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D142" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E142" t="str">
+        <v>2026-07-31T11:18:38.615Z</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>TC-GEN-1133</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Leading/trailing whitespace inputs (133)</v>
+      </c>
+      <c r="C143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D143" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E143" t="str">
+        <v>2026-07-31T11:18:38.631Z</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>TC-GEN-1134</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Alias email address with incorrect password (134)</v>
+      </c>
+      <c r="C144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D144" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E144" t="str">
+        <v>2026-07-31T11:18:38.647Z</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>TC-GEN-1135</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Varying length generated inputs (135)</v>
+      </c>
+      <c r="C145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D145" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E145" t="str">
+        <v>2026-07-31T11:18:38.663Z</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>TC-GEN-1136</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Password with special characters: !#$%^&amp;*</v>
+      </c>
+      <c r="C146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D146" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E146" t="str">
+        <v>2026-07-31T11:18:38.679Z</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>TC-GEN-1137</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Fuzzing password field with DB query injection (137)</v>
+      </c>
+      <c r="C147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D147" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E147" t="str">
+        <v>2026-07-31T11:18:38.695Z</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>TC-GEN-1138</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Invalid registered user test case (138)</v>
+      </c>
+      <c r="C148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D148" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E148" t="str">
+        <v>2026-07-31T11:18:38.710Z</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>TC-GEN-1139</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Leading/trailing whitespace inputs (139)</v>
+      </c>
+      <c r="C149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D149" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E149" t="str">
+        <v>2026-07-31T11:18:38.725Z</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>TC-GEN-1140</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Alias email address with incorrect password (140)</v>
+      </c>
+      <c r="C150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D150" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E150" t="str">
+        <v>2026-07-31T11:18:38.741Z</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>TC-GEN-1141</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Varying length generated inputs (141)</v>
+      </c>
+      <c r="C151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D151" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E151" t="str">
+        <v>2026-07-31T11:18:38.757Z</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TC-GEN-1142</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D152" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E152" t="str">
+        <v>2026-07-31T11:18:38.772Z</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TC-GEN-1143</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Fuzzing password field with DB query injection (143)</v>
+      </c>
+      <c r="C153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D153" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E153" t="str">
+        <v>2026-07-31T11:18:38.787Z</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TC-GEN-1144</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Invalid registered user test case (144)</v>
+      </c>
+      <c r="C154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D154" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E154" t="str">
+        <v>2026-07-31T11:18:38.803Z</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>TC-GEN-1145</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Leading/trailing whitespace inputs (145)</v>
+      </c>
+      <c r="C155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D155" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E155" t="str">
+        <v>2026-07-31T11:18:38.818Z</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>TC-GEN-1146</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Alias email address with incorrect password (146)</v>
+      </c>
+      <c r="C156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D156" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E156" t="str">
+        <v>2026-07-31T11:18:38.834Z</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>TC-GEN-1147</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Varying length generated inputs (147)</v>
+      </c>
+      <c r="C157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D157" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E157" t="str">
+        <v>2026-07-31T11:18:38.849Z</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>TC-GEN-1148</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Password with special characters: !#$%^&amp;</v>
+      </c>
+      <c r="C158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D158" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E158" t="str">
+        <v>2026-07-31T11:18:38.867Z</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>TC-GEN-1149</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Fuzzing password field with DB query injection (149)</v>
+      </c>
+      <c r="C159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D159" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E159" t="str">
+        <v>2026-07-31T11:18:38.881Z</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>TC-GEN-1150</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Invalid registered user test case (150)</v>
+      </c>
+      <c r="C160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D160" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E160" t="str">
+        <v>2026-07-31T11:18:38.897Z</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>TC-GEN-1151</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Leading/trailing whitespace inputs (151)</v>
+      </c>
+      <c r="C161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D161" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E161" t="str">
+        <v>2026-07-31T11:18:38.913Z</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>TC-GEN-1152</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Alias email address with incorrect password (152)</v>
+      </c>
+      <c r="C162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D162" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E162" t="str">
+        <v>2026-07-31T11:18:38.928Z</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TC-GEN-1153</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Varying length generated inputs (153)</v>
+      </c>
+      <c r="C163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D163" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E163" t="str">
+        <v>2026-07-31T11:18:38.943Z</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>TC-GEN-1154</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D164" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E164" t="str">
+        <v>2026-07-31T11:18:38.959Z</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>TC-GEN-1155</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Fuzzing password field with DB query injection (155)</v>
+      </c>
+      <c r="C165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D165" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E165" t="str">
+        <v>2026-07-31T11:18:38.974Z</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>TC-GEN-1156</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Invalid registered user test case (156)</v>
+      </c>
+      <c r="C166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D166" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E166" t="str">
+        <v>2026-07-31T11:18:38.990Z</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>TC-GEN-1157</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Leading/trailing whitespace inputs (157)</v>
+      </c>
+      <c r="C167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D167" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E167" t="str">
+        <v>2026-07-31T11:18:39.005Z</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>TC-GEN-1158</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Alias email address with incorrect password (158)</v>
+      </c>
+      <c r="C168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D168" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E168" t="str">
+        <v>2026-07-31T11:18:39.020Z</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>TC-GEN-1159</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Varying length generated inputs (159)</v>
+      </c>
+      <c r="C169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D169" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E169" t="str">
+        <v>2026-07-31T11:18:39.036Z</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>TC-GEN-1160</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Password with special characters: !#$%^</v>
+      </c>
+      <c r="C170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D170" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E170" t="str">
+        <v>2026-07-31T11:18:39.051Z</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>TC-GEN-1161</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Fuzzing password field with DB query injection (161)</v>
+      </c>
+      <c r="C171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D171" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E171" t="str">
+        <v>2026-07-31T11:18:39.067Z</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>TC-GEN-1162</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Invalid registered user test case (162)</v>
+      </c>
+      <c r="C172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D172" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E172" t="str">
+        <v>2026-07-31T11:18:39.082Z</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>TC-GEN-1163</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Leading/trailing whitespace inputs (163)</v>
+      </c>
+      <c r="C173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D173" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E173" t="str">
+        <v>2026-07-31T11:18:39.097Z</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>TC-GEN-1164</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Alias email address with incorrect password (164)</v>
+      </c>
+      <c r="C174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D174" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E174" t="str">
+        <v>2026-07-31T11:18:39.113Z</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>TC-GEN-1165</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Varying length generated inputs (165)</v>
+      </c>
+      <c r="C175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D175" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E175" t="str">
+        <v>2026-07-31T11:18:39.130Z</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>TC-GEN-1166</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D176" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E176" t="str">
+        <v>2026-07-31T11:18:39.145Z</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>TC-GEN-1167</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Fuzzing password field with DB query injection (167)</v>
+      </c>
+      <c r="C177" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D177" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E177" t="str">
+        <v>2026-07-31T11:18:39.160Z</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TC-GEN-1168</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Invalid registered user test case (168)</v>
+      </c>
+      <c r="C178" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D178" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E178" t="str">
+        <v>2026-07-31T11:18:39.176Z</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>TC-GEN-1169</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Leading/trailing whitespace inputs (169)</v>
+      </c>
+      <c r="C179" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D179" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E179" t="str">
+        <v>2026-07-31T11:18:39.192Z</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TC-GEN-1170</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Alias email address with incorrect password (170)</v>
+      </c>
+      <c r="C180" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D180" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E180" t="str">
+        <v>2026-07-31T11:18:39.208Z</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TC-GEN-1171</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Varying length generated inputs (171)</v>
+      </c>
+      <c r="C181" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D181" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E181" t="str">
+        <v>2026-07-31T11:18:39.223Z</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>TC-GEN-1172</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Password with special characters: !#$%</v>
+      </c>
+      <c r="C182" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D182" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E182" t="str">
+        <v>2026-07-31T11:18:39.238Z</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>TC-GEN-1173</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Fuzzing password field with DB query injection (173)</v>
+      </c>
+      <c r="C183" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D183" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E183" t="str">
+        <v>2026-07-31T11:18:39.254Z</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>TC-GEN-1174</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Invalid registered user test case (174)</v>
+      </c>
+      <c r="C184" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D184" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E184" t="str">
+        <v>2026-07-31T11:18:39.270Z</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>TC-GEN-1175</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Leading/trailing whitespace inputs (175)</v>
+      </c>
+      <c r="C185" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D185" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E185" t="str">
+        <v>2026-07-31T11:18:39.286Z</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>TC-GEN-1176</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Alias email address with incorrect password (176)</v>
+      </c>
+      <c r="C186" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D186" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E186" t="str">
+        <v>2026-07-31T11:18:39.301Z</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>TC-GEN-1177</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Varying length generated inputs (177)</v>
+      </c>
+      <c r="C187" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D187" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E187" t="str">
+        <v>2026-07-31T11:18:39.317Z</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>TC-GEN-1178</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~</v>
+      </c>
+      <c r="C188" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D188" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E188" t="str">
+        <v>2026-07-31T11:18:39.333Z</v>
+      </c>
+      <c r="F188" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>TC-GEN-1179</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Fuzzing password field with DB query injection (179)</v>
+      </c>
+      <c r="C189" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D189" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E189" t="str">
+        <v>2026-07-31T11:18:39.348Z</v>
+      </c>
+      <c r="F189" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TC-GEN-1180</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Invalid registered user test case (180)</v>
+      </c>
+      <c r="C190" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D190" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E190" t="str">
+        <v>2026-07-31T11:18:39.363Z</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TC-GEN-1181</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Leading/trailing whitespace inputs (181)</v>
+      </c>
+      <c r="C191" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D191" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E191" t="str">
+        <v>2026-07-31T11:18:39.379Z</v>
+      </c>
+      <c r="F191" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TC-GEN-1182</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Alias email address with incorrect password (182)</v>
+      </c>
+      <c r="C192" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D192" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E192" t="str">
+        <v>2026-07-31T11:18:39.394Z</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TC-GEN-1183</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Varying length generated inputs (183)</v>
+      </c>
+      <c r="C193" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D193" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E193" t="str">
+        <v>2026-07-31T11:18:39.410Z</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TC-GEN-1184</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Password with special characters: !#$</v>
+      </c>
+      <c r="C194" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D194" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E194" t="str">
+        <v>2026-07-31T11:18:39.425Z</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TC-GEN-1185</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Fuzzing password field with DB query injection (185)</v>
+      </c>
+      <c r="C195" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D195" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E195" t="str">
+        <v>2026-07-31T11:18:39.440Z</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TC-GEN-1186</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Invalid registered user test case (186)</v>
+      </c>
+      <c r="C196" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D196" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E196" t="str">
+        <v>2026-07-31T11:18:39.456Z</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>TC-GEN-1187</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Leading/trailing whitespace inputs (187)</v>
+      </c>
+      <c r="C197" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D197" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E197" t="str">
+        <v>2026-07-31T11:18:39.472Z</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>TC-GEN-1188</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Alias email address with incorrect password (188)</v>
+      </c>
+      <c r="C198" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D198" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E198" t="str">
+        <v>2026-07-31T11:18:39.488Z</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>TC-GEN-1189</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Varying length generated inputs (189)</v>
+      </c>
+      <c r="C199" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D199" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E199" t="str">
+        <v>2026-07-31T11:18:39.503Z</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>TC-GEN-1190</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Password with special characters: !#$%^&amp;*()</v>
+      </c>
+      <c r="C200" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D200" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E200" t="str">
+        <v>2026-07-31T11:18:39.521Z</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>TC-GEN-1191</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Fuzzing password field with DB query injection (191)</v>
+      </c>
+      <c r="C201" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D201" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E201" t="str">
+        <v>2026-07-31T11:18:39.533Z</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>TC-GEN-1192</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Invalid registered user test case (192)</v>
+      </c>
+      <c r="C202" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D202" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E202" t="str">
+        <v>2026-07-31T11:18:39.549Z</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>TC-GEN-1193</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Leading/trailing whitespace inputs (193)</v>
+      </c>
+      <c r="C203" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D203" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E203" t="str">
+        <v>2026-07-31T11:18:39.565Z</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>TC-GEN-1194</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Alias email address with incorrect password (194)</v>
+      </c>
+      <c r="C204" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D204" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E204" t="str">
+        <v>2026-07-31T11:18:39.580Z</v>
+      </c>
+      <c r="F204" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>TC-GEN-1195</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Varying length generated inputs (195)</v>
+      </c>
+      <c r="C205" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D205" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E205" t="str">
+        <v>2026-07-31T11:18:39.596Z</v>
+      </c>
+      <c r="F205" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>TC-GEN-1196</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Password with special characters: !#</v>
+      </c>
+      <c r="C206" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D206" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E206" t="str">
+        <v>2026-07-31T11:18:39.611Z</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>TC-GEN-1197</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Fuzzing password field with DB query injection (197)</v>
+      </c>
+      <c r="C207" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D207" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E207" t="str">
+        <v>2026-07-31T11:18:39.627Z</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>TC-GEN-1198</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Invalid registered user test case (198)</v>
+      </c>
+      <c r="C208" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D208" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E208" t="str">
+        <v>2026-07-31T11:18:39.642Z</v>
+      </c>
+      <c r="F208" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TC-GEN-1199</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Leading/trailing whitespace inputs (199)</v>
+      </c>
+      <c r="C209" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D209" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E209" t="str">
+        <v>2026-07-31T11:18:39.657Z</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>TC-GEN-1200</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Alias email address with incorrect password (200)</v>
+      </c>
+      <c r="C210" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D210" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E210" t="str">
+        <v>2026-07-31T11:18:39.673Z</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>TC-GEN-1201</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Varying length generated inputs (201)</v>
+      </c>
+      <c r="C211" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D211" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E211" t="str">
+        <v>2026-07-31T11:18:39.688Z</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>TC-GEN-1202</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Password with special characters: !#$%^&amp;*(</v>
+      </c>
+      <c r="C212" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D212" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E212" t="str">
+        <v>2026-07-31T11:18:39.704Z</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>TC-GEN-1203</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Fuzzing password field with DB query injection (203)</v>
+      </c>
+      <c r="C213" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D213" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E213" t="str">
+        <v>2026-07-31T11:18:39.719Z</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>TC-GEN-1204</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Invalid registered user test case (204)</v>
+      </c>
+      <c r="C214" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D214" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E214" t="str">
+        <v>2026-07-31T11:18:39.735Z</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>TC-GEN-1205</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Leading/trailing whitespace inputs (205)</v>
+      </c>
+      <c r="C215" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D215" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E215" t="str">
+        <v>2026-07-31T11:18:39.751Z</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>TC-GEN-1206</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Alias email address with incorrect password (206)</v>
+      </c>
+      <c r="C216" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D216" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E216" t="str">
+        <v>2026-07-31T11:18:39.766Z</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>TC-GEN-1207</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Varying length generated inputs (207)</v>
+      </c>
+      <c r="C217" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D217" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E217" t="str">
+        <v>2026-07-31T11:18:39.782Z</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>TC-GEN-1208</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Password with special characters: !</v>
+      </c>
+      <c r="C218" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D218" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E218" t="str">
+        <v>2026-07-31T11:18:39.798Z</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>TC-GEN-1209</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Fuzzing password field with DB query injection (209)</v>
+      </c>
+      <c r="C219" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D219" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E219" t="str">
+        <v>2026-07-31T11:18:39.813Z</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>TC-GEN-1210</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Invalid registered user test case (210)</v>
+      </c>
+      <c r="C220" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D220" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E220" t="str">
+        <v>2026-07-31T11:18:39.829Z</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>TC-GEN-1211</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Leading/trailing whitespace inputs (211)</v>
+      </c>
+      <c r="C221" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D221" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E221" t="str">
+        <v>2026-07-31T11:18:39.844Z</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>TC-GEN-1212</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Alias email address with incorrect password (212)</v>
+      </c>
+      <c r="C222" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D222" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E222" t="str">
+        <v>2026-07-31T11:18:39.860Z</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>TC-GEN-1213</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Varying length generated inputs (213)</v>
+      </c>
+      <c r="C223" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D223" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E223" t="str">
+        <v>2026-07-31T11:18:39.876Z</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>TC-GEN-1214</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Password with special characters: !#$%^&amp;*</v>
+      </c>
+      <c r="C224" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D224" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E224" t="str">
+        <v>2026-07-31T11:18:39.892Z</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TC-GEN-1215</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Fuzzing password field with DB query injection (215)</v>
+      </c>
+      <c r="C225" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D225" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E225" t="str">
+        <v>2026-07-31T11:18:39.906Z</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>TC-GEN-1216</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Invalid registered user test case (216)</v>
+      </c>
+      <c r="C226" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D226" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E226" t="str">
+        <v>2026-07-31T11:18:39.922Z</v>
+      </c>
+      <c r="F226" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>TC-GEN-1217</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Leading/trailing whitespace inputs (217)</v>
+      </c>
+      <c r="C227" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D227" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E227" t="str">
+        <v>2026-07-31T11:18:39.937Z</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>TC-GEN-1218</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Alias email address with incorrect password (218)</v>
+      </c>
+      <c r="C228" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D228" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E228" t="str">
+        <v>2026-07-31T11:18:39.953Z</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>TC-GEN-1219</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Varying length generated inputs (219)</v>
+      </c>
+      <c r="C229" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D229" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E229" t="str">
+        <v>2026-07-31T11:18:39.968Z</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>TC-GEN-1220</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C230" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D230" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E230" t="str">
+        <v>2026-07-31T11:18:39.983Z</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>TC-GEN-1221</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Fuzzing password field with DB query injection (221)</v>
+      </c>
+      <c r="C231" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D231" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E231" t="str">
+        <v>2026-07-31T11:18:39.999Z</v>
+      </c>
+      <c r="F231" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>TC-GEN-1222</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Invalid registered user test case (222)</v>
+      </c>
+      <c r="C232" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D232" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E232" t="str">
+        <v>2026-07-31T11:18:40.014Z</v>
+      </c>
+      <c r="F232" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>TC-GEN-1223</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Leading/trailing whitespace inputs (223)</v>
+      </c>
+      <c r="C233" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D233" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E233" t="str">
+        <v>2026-07-31T11:18:40.029Z</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>TC-GEN-1224</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Alias email address with incorrect password (224)</v>
+      </c>
+      <c r="C234" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D234" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E234" t="str">
+        <v>2026-07-31T11:18:40.045Z</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>TC-GEN-1225</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Varying length generated inputs (225)</v>
+      </c>
+      <c r="C235" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D235" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E235" t="str">
+        <v>2026-07-31T11:18:40.061Z</v>
+      </c>
+      <c r="F235" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>TC-GEN-1226</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Password with special characters: !#$%^&amp;</v>
+      </c>
+      <c r="C236" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D236" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E236" t="str">
+        <v>2026-07-31T11:18:40.076Z</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>TC-GEN-1227</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Fuzzing password field with DB query injection (227)</v>
+      </c>
+      <c r="C237" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D237" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E237" t="str">
+        <v>2026-07-31T11:18:40.091Z</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>TC-GEN-1228</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Invalid registered user test case (228)</v>
+      </c>
+      <c r="C238" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D238" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E238" t="str">
+        <v>2026-07-31T11:18:40.107Z</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>TC-GEN-1229</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Leading/trailing whitespace inputs (229)</v>
+      </c>
+      <c r="C239" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D239" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E239" t="str">
+        <v>2026-07-31T11:18:40.122Z</v>
+      </c>
+      <c r="F239" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>TC-GEN-1230</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Alias email address with incorrect password (230)</v>
+      </c>
+      <c r="C240" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D240" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E240" t="str">
+        <v>2026-07-31T11:18:40.138Z</v>
+      </c>
+      <c r="F240" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>TC-GEN-1231</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Varying length generated inputs (231)</v>
+      </c>
+      <c r="C241" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D241" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E241" t="str">
+        <v>2026-07-31T11:18:40.153Z</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>TC-GEN-1232</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C242" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D242" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E242" t="str">
+        <v>2026-07-31T11:18:40.170Z</v>
+      </c>
+      <c r="F242" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>TC-GEN-1233</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Fuzzing password field with DB query injection (233)</v>
+      </c>
+      <c r="C243" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D243" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E243" t="str">
+        <v>2026-07-31T11:18:40.185Z</v>
+      </c>
+      <c r="F243" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>TC-GEN-1234</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Invalid registered user test case (234)</v>
+      </c>
+      <c r="C244" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D244" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E244" t="str">
+        <v>2026-07-31T11:18:40.202Z</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>TC-GEN-1235</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Leading/trailing whitespace inputs (235)</v>
+      </c>
+      <c r="C245" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D245" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E245" t="str">
+        <v>2026-07-31T11:18:40.217Z</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>TC-GEN-1236</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Alias email address with incorrect password (236)</v>
+      </c>
+      <c r="C246" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D246" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E246" t="str">
+        <v>2026-07-31T11:18:40.233Z</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>TC-GEN-1237</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Varying length generated inputs (237)</v>
+      </c>
+      <c r="C247" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D247" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E247" t="str">
+        <v>2026-07-31T11:18:40.249Z</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>TC-GEN-1238</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Password with special characters: !#$%^</v>
+      </c>
+      <c r="C248" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D248" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E248" t="str">
+        <v>2026-07-31T11:18:40.265Z</v>
+      </c>
+      <c r="F248" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>TC-GEN-1239</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Fuzzing password field with DB query injection (239)</v>
+      </c>
+      <c r="C249" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D249" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E249" t="str">
+        <v>2026-07-31T11:18:40.280Z</v>
+      </c>
+      <c r="F249" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>TC-GEN-1240</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Invalid registered user test case (240)</v>
+      </c>
+      <c r="C250" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D250" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E250" t="str">
+        <v>2026-07-31T11:18:40.295Z</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>TC-GEN-1241</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Leading/trailing whitespace inputs (241)</v>
+      </c>
+      <c r="C251" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D251" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E251" t="str">
+        <v>2026-07-31T11:18:40.310Z</v>
+      </c>
+      <c r="F251" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>TC-GEN-1242</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Alias email address with incorrect password (242)</v>
+      </c>
+      <c r="C252" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D252" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E252" t="str">
+        <v>2026-07-31T11:18:40.325Z</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>TC-GEN-1243</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Varying length generated inputs (243)</v>
+      </c>
+      <c r="C253" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D253" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E253" t="str">
+        <v>2026-07-31T11:18:40.340Z</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>TC-GEN-1244</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C254" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D254" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E254" t="str">
+        <v>2026-07-31T11:18:40.356Z</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>TC-GEN-1245</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Fuzzing password field with DB query injection (245)</v>
+      </c>
+      <c r="C255" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D255" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E255" t="str">
+        <v>2026-07-31T11:18:40.371Z</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>TC-GEN-1246</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Invalid registered user test case (246)</v>
+      </c>
+      <c r="C256" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D256" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E256" t="str">
+        <v>2026-07-31T11:18:40.387Z</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>TC-GEN-1247</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Leading/trailing whitespace inputs (247)</v>
+      </c>
+      <c r="C257" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D257" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E257" t="str">
+        <v>2026-07-31T11:18:40.404Z</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>TC-GEN-1248</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Alias email address with incorrect password (248)</v>
+      </c>
+      <c r="C258" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D258" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E258" t="str">
+        <v>2026-07-31T11:18:40.419Z</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>TC-GEN-1249</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Varying length generated inputs (249)</v>
+      </c>
+      <c r="C259" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D259" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E259" t="str">
+        <v>2026-07-31T11:18:40.433Z</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>TC-GEN-1250</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Password with special characters: !#$%</v>
+      </c>
+      <c r="C260" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D260" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E260" t="str">
+        <v>2026-07-31T11:18:40.449Z</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>TC-GEN-1251</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Fuzzing password field with DB query injection (251)</v>
+      </c>
+      <c r="C261" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D261" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E261" t="str">
+        <v>2026-07-31T11:18:40.465Z</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>TC-GEN-1252</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Invalid registered user test case (252)</v>
+      </c>
+      <c r="C262" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D262" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E262" t="str">
+        <v>2026-07-31T11:18:40.481Z</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>TC-GEN-1253</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Leading/trailing whitespace inputs (253)</v>
+      </c>
+      <c r="C263" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D263" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E263" t="str">
+        <v>2026-07-31T11:18:40.497Z</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>TC-GEN-1254</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Alias email address with incorrect password (254)</v>
+      </c>
+      <c r="C264" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D264" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E264" t="str">
+        <v>2026-07-31T11:18:40.512Z</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TC-GEN-1255</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Varying length generated inputs (255)</v>
+      </c>
+      <c r="C265" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D265" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E265" t="str">
+        <v>2026-07-31T11:18:40.528Z</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>TC-GEN-1256</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~</v>
+      </c>
+      <c r="C266" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D266" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E266" t="str">
+        <v>2026-07-31T11:18:40.543Z</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>TC-GEN-1257</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Fuzzing password field with DB query injection (257)</v>
+      </c>
+      <c r="C267" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D267" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E267" t="str">
+        <v>2026-07-31T11:18:40.559Z</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>TC-GEN-1258</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Invalid registered user test case (258)</v>
+      </c>
+      <c r="C268" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D268" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E268" t="str">
+        <v>2026-07-31T11:18:40.575Z</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>TC-GEN-1259</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Leading/trailing whitespace inputs (259)</v>
+      </c>
+      <c r="C269" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D269" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E269" t="str">
+        <v>2026-07-31T11:18:40.591Z</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>TC-GEN-1260</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Alias email address with incorrect password (260)</v>
+      </c>
+      <c r="C270" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D270" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E270" t="str">
+        <v>2026-07-31T11:18:40.607Z</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>TC-GEN-1261</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Varying length generated inputs (261)</v>
+      </c>
+      <c r="C271" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D271" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E271" t="str">
+        <v>2026-07-31T11:18:40.621Z</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>TC-GEN-1262</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Password with special characters: !#$</v>
+      </c>
+      <c r="C272" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D272" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E272" t="str">
+        <v>2026-07-31T11:18:40.637Z</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>TC-GEN-1263</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Fuzzing password field with DB query injection (263)</v>
+      </c>
+      <c r="C273" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D273" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E273" t="str">
+        <v>2026-07-31T11:18:40.652Z</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TC-GEN-1264</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Invalid registered user test case (264)</v>
+      </c>
+      <c r="C274" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D274" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E274" t="str">
+        <v>2026-07-31T11:18:40.667Z</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TC-GEN-1265</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Leading/trailing whitespace inputs (265)</v>
+      </c>
+      <c r="C275" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D275" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E275" t="str">
+        <v>2026-07-31T11:18:40.682Z</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TC-GEN-1266</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Alias email address with incorrect password (266)</v>
+      </c>
+      <c r="C276" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D276" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E276" t="str">
+        <v>2026-07-31T11:18:40.697Z</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TC-GEN-1267</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Varying length generated inputs (267)</v>
+      </c>
+      <c r="C277" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D277" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E277" t="str">
+        <v>2026-07-31T11:18:40.713Z</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TC-GEN-1268</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Password with special characters: !#$%^&amp;*()</v>
+      </c>
+      <c r="C278" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D278" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E278" t="str">
+        <v>2026-07-31T11:18:40.728Z</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TC-GEN-1269</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Fuzzing password field with DB query injection (269)</v>
+      </c>
+      <c r="C279" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D279" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E279" t="str">
+        <v>2026-07-31T11:18:40.743Z</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TC-GEN-1270</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Invalid registered user test case (270)</v>
+      </c>
+      <c r="C280" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D280" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E280" t="str">
+        <v>2026-07-31T11:18:40.760Z</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>TC-GEN-1271</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Leading/trailing whitespace inputs (271)</v>
+      </c>
+      <c r="C281" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D281" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E281" t="str">
+        <v>2026-07-31T11:18:40.776Z</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>TC-GEN-1272</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Alias email address with incorrect password (272)</v>
+      </c>
+      <c r="C282" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D282" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E282" t="str">
+        <v>2026-07-31T11:18:40.791Z</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>TC-GEN-1273</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Varying length generated inputs (273)</v>
+      </c>
+      <c r="C283" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D283" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E283" t="str">
+        <v>2026-07-31T11:18:40.807Z</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>TC-GEN-1274</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Password with special characters: !#</v>
+      </c>
+      <c r="C284" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D284" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E284" t="str">
+        <v>2026-07-31T11:18:40.823Z</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>TC-GEN-1275</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Fuzzing password field with DB query injection (275)</v>
+      </c>
+      <c r="C285" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D285" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E285" t="str">
+        <v>2026-07-31T11:18:40.838Z</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>TC-GEN-1276</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Invalid registered user test case (276)</v>
+      </c>
+      <c r="C286" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D286" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E286" t="str">
+        <v>2026-07-31T11:18:40.854Z</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>TC-GEN-1277</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Leading/trailing whitespace inputs (277)</v>
+      </c>
+      <c r="C287" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D287" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E287" t="str">
+        <v>2026-07-31T11:18:40.869Z</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>TC-GEN-1278</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Alias email address with incorrect password (278)</v>
+      </c>
+      <c r="C288" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D288" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E288" t="str">
+        <v>2026-07-31T11:18:40.884Z</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>TC-GEN-1279</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Varying length generated inputs (279)</v>
+      </c>
+      <c r="C289" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D289" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E289" t="str">
+        <v>2026-07-31T11:18:40.900Z</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>TC-GEN-1280</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Password with special characters: !#$%^&amp;*(</v>
+      </c>
+      <c r="C290" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D290" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E290" t="str">
+        <v>2026-07-31T11:18:40.916Z</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>TC-GEN-1281</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Fuzzing password field with DB query injection (281)</v>
+      </c>
+      <c r="C291" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D291" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E291" t="str">
+        <v>2026-07-31T11:18:40.931Z</v>
+      </c>
+      <c r="F291" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>TC-GEN-1282</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Invalid registered user test case (282)</v>
+      </c>
+      <c r="C292" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D292" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E292" t="str">
+        <v>2026-07-31T11:18:40.947Z</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>TC-GEN-1283</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Leading/trailing whitespace inputs (283)</v>
+      </c>
+      <c r="C293" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D293" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E293" t="str">
+        <v>2026-07-31T11:18:40.962Z</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>TC-GEN-1284</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Alias email address with incorrect password (284)</v>
+      </c>
+      <c r="C294" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D294" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E294" t="str">
+        <v>2026-07-31T11:18:40.977Z</v>
+      </c>
+      <c r="F294" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>TC-GEN-1285</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Varying length generated inputs (285)</v>
+      </c>
+      <c r="C295" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D295" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E295" t="str">
+        <v>2026-07-31T11:18:40.993Z</v>
+      </c>
+      <c r="F295" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>TC-GEN-1286</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Password with special characters: !</v>
+      </c>
+      <c r="C296" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D296" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E296" t="str">
+        <v>2026-07-31T11:18:41.009Z</v>
+      </c>
+      <c r="F296" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>TC-GEN-1287</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Fuzzing password field with DB query injection (287)</v>
+      </c>
+      <c r="C297" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D297" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E297" t="str">
+        <v>2026-07-31T11:18:41.023Z</v>
+      </c>
+      <c r="F297" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>TC-GEN-1288</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Invalid registered user test case (288)</v>
+      </c>
+      <c r="C298" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D298" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E298" t="str">
+        <v>2026-07-31T11:18:41.039Z</v>
+      </c>
+      <c r="F298" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>TC-GEN-1289</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Leading/trailing whitespace inputs (289)</v>
+      </c>
+      <c r="C299" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D299" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E299" t="str">
+        <v>2026-07-31T11:18:41.054Z</v>
+      </c>
+      <c r="F299" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>TC-GEN-1290</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Alias email address with incorrect password (290)</v>
+      </c>
+      <c r="C300" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D300" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E300" t="str">
+        <v>2026-07-31T11:18:41.070Z</v>
+      </c>
+      <c r="F300" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>TC-GEN-1291</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Varying length generated inputs (291)</v>
+      </c>
+      <c r="C301" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D301" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E301" t="str">
+        <v>2026-07-31T11:18:41.086Z</v>
+      </c>
+      <c r="F301" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>TC-GEN-1292</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Password with special characters: !#$%^&amp;*</v>
+      </c>
+      <c r="C302" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D302" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E302" t="str">
+        <v>2026-07-31T11:18:41.101Z</v>
+      </c>
+      <c r="F302" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>TC-GEN-1293</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Fuzzing password field with DB query injection (293)</v>
+      </c>
+      <c r="C303" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D303" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E303" t="str">
+        <v>2026-07-31T11:18:41.117Z</v>
+      </c>
+      <c r="F303" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>TC-GEN-1294</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Invalid registered user test case (294)</v>
+      </c>
+      <c r="C304" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D304" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E304" t="str">
+        <v>2026-07-31T11:18:41.132Z</v>
+      </c>
+      <c r="F304" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>TC-GEN-1295</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Leading/trailing whitespace inputs (295)</v>
+      </c>
+      <c r="C305" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D305" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E305" t="str">
+        <v>2026-07-31T11:18:41.148Z</v>
+      </c>
+      <c r="F305" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>TC-GEN-1296</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Alias email address with incorrect password (296)</v>
+      </c>
+      <c r="C306" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D306" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E306" t="str">
+        <v>2026-07-31T11:18:41.163Z</v>
+      </c>
+      <c r="F306" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>TC-GEN-1297</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Varying length generated inputs (297)</v>
+      </c>
+      <c r="C307" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D307" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E307" t="str">
+        <v>2026-07-31T11:18:41.179Z</v>
+      </c>
+      <c r="F307" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>TC-GEN-1298</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C308" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D308" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E308" t="str">
+        <v>2026-07-31T11:18:41.194Z</v>
+      </c>
+      <c r="F308" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>TC-GEN-1299</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Fuzzing password field with DB query injection (299)</v>
+      </c>
+      <c r="C309" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D309" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E309" t="str">
+        <v>2026-07-31T11:18:41.209Z</v>
+      </c>
+      <c r="F309" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>TC-GEN-1300</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Invalid registered user test case (300)</v>
+      </c>
+      <c r="C310" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D310" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E310" t="str">
+        <v>2026-07-31T11:18:41.224Z</v>
+      </c>
+      <c r="F310" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>TC-GEN-1301</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Leading/trailing whitespace inputs (301)</v>
+      </c>
+      <c r="C311" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D311" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E311" t="str">
+        <v>2026-07-31T11:18:41.239Z</v>
+      </c>
+      <c r="F311" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>TC-GEN-1302</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Alias email address with incorrect password (302)</v>
+      </c>
+      <c r="C312" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D312" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E312" t="str">
+        <v>2026-07-31T11:18:41.255Z</v>
+      </c>
+      <c r="F312" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>TC-GEN-1303</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Varying length generated inputs (303)</v>
+      </c>
+      <c r="C313" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D313" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E313" t="str">
+        <v>2026-07-31T11:18:41.270Z</v>
+      </c>
+      <c r="F313" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>TC-GEN-1304</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Password with special characters: !#$%^&amp;</v>
+      </c>
+      <c r="C314" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D314" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E314" t="str">
+        <v>2026-07-31T11:18:41.286Z</v>
+      </c>
+      <c r="F314" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>TC-GEN-1305</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Fuzzing password field with DB query injection (305)</v>
+      </c>
+      <c r="C315" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D315" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E315" t="str">
+        <v>2026-07-31T11:18:41.302Z</v>
+      </c>
+      <c r="F315" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>TC-GEN-1306</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Invalid registered user test case (306)</v>
+      </c>
+      <c r="C316" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D316" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E316" t="str">
+        <v>2026-07-31T11:18:41.317Z</v>
+      </c>
+      <c r="F316" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>TC-GEN-1307</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Leading/trailing whitespace inputs (307)</v>
+      </c>
+      <c r="C317" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D317" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E317" t="str">
+        <v>2026-07-31T11:18:41.332Z</v>
+      </c>
+      <c r="F317" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>TC-GEN-1308</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Alias email address with incorrect password (308)</v>
+      </c>
+      <c r="C318" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D318" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E318" t="str">
+        <v>2026-07-31T11:18:41.348Z</v>
+      </c>
+      <c r="F318" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>TC-GEN-1309</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Varying length generated inputs (309)</v>
+      </c>
+      <c r="C319" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D319" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E319" t="str">
+        <v>2026-07-31T11:18:41.363Z</v>
+      </c>
+      <c r="F319" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>TC-GEN-1310</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C320" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D320" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E320" t="str">
+        <v>2026-07-31T11:18:41.379Z</v>
+      </c>
+      <c r="F320" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>TC-GEN-1311</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Fuzzing password field with DB query injection (311)</v>
+      </c>
+      <c r="C321" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D321" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E321" t="str">
+        <v>2026-07-31T11:18:41.394Z</v>
+      </c>
+      <c r="F321" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>TC-GEN-1312</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Invalid registered user test case (312)</v>
+      </c>
+      <c r="C322" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D322" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E322" t="str">
+        <v>2026-07-31T11:18:41.410Z</v>
+      </c>
+      <c r="F322" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>TC-GEN-1313</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Leading/trailing whitespace inputs (313)</v>
+      </c>
+      <c r="C323" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D323" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E323" t="str">
+        <v>2026-07-31T11:18:41.426Z</v>
+      </c>
+      <c r="F323" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>TC-GEN-1314</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Alias email address with incorrect password (314)</v>
+      </c>
+      <c r="C324" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D324" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E324" t="str">
+        <v>2026-07-31T11:18:41.441Z</v>
+      </c>
+      <c r="F324" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>TC-GEN-1315</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Varying length generated inputs (315)</v>
+      </c>
+      <c r="C325" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D325" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E325" t="str">
+        <v>2026-07-31T11:18:41.456Z</v>
+      </c>
+      <c r="F325" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>TC-GEN-1316</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Password with special characters: !#$%^</v>
+      </c>
+      <c r="C326" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D326" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E326" t="str">
+        <v>2026-07-31T11:18:41.472Z</v>
+      </c>
+      <c r="F326" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>TC-GEN-1317</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Fuzzing password field with DB query injection (317)</v>
+      </c>
+      <c r="C327" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D327" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E327" t="str">
+        <v>2026-07-31T11:18:41.488Z</v>
+      </c>
+      <c r="F327" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>TC-GEN-1318</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Invalid registered user test case (318)</v>
+      </c>
+      <c r="C328" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D328" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E328" t="str">
+        <v>2026-07-31T11:18:41.504Z</v>
+      </c>
+      <c r="F328" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>TC-GEN-1319</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Leading/trailing whitespace inputs (319)</v>
+      </c>
+      <c r="C329" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D329" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E329" t="str">
+        <v>2026-07-31T11:18:41.519Z</v>
+      </c>
+      <c r="F329" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>TC-GEN-1320</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Alias email address with incorrect password (320)</v>
+      </c>
+      <c r="C330" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D330" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E330" t="str">
+        <v>2026-07-31T11:18:41.536Z</v>
+      </c>
+      <c r="F330" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>TC-GEN-1321</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Varying length generated inputs (321)</v>
+      </c>
+      <c r="C331" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D331" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E331" t="str">
+        <v>2026-07-31T11:18:41.551Z</v>
+      </c>
+      <c r="F331" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>TC-GEN-1322</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C332" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D332" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E332" t="str">
+        <v>2026-07-31T11:18:41.566Z</v>
+      </c>
+      <c r="F332" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>TC-GEN-1323</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Fuzzing password field with DB query injection (323)</v>
+      </c>
+      <c r="C333" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D333" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E333" t="str">
+        <v>2026-07-31T11:18:41.582Z</v>
+      </c>
+      <c r="F333" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>TC-GEN-1324</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Invalid registered user test case (324)</v>
+      </c>
+      <c r="C334" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D334" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E334" t="str">
+        <v>2026-07-31T11:18:41.597Z</v>
+      </c>
+      <c r="F334" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>TC-GEN-1325</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Leading/trailing whitespace inputs (325)</v>
+      </c>
+      <c r="C335" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D335" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E335" t="str">
+        <v>2026-07-31T11:18:41.612Z</v>
+      </c>
+      <c r="F335" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>TC-GEN-1326</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Alias email address with incorrect password (326)</v>
+      </c>
+      <c r="C336" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D336" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E336" t="str">
+        <v>2026-07-31T11:18:41.628Z</v>
+      </c>
+      <c r="F336" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>TC-GEN-1327</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Varying length generated inputs (327)</v>
+      </c>
+      <c r="C337" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D337" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E337" t="str">
+        <v>2026-07-31T11:18:41.644Z</v>
+      </c>
+      <c r="F337" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>TC-GEN-1328</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Password with special characters: !#$%</v>
+      </c>
+      <c r="C338" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D338" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E338" t="str">
+        <v>2026-07-31T11:18:41.659Z</v>
+      </c>
+      <c r="F338" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>TC-GEN-1329</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Fuzzing password field with DB query injection (329)</v>
+      </c>
+      <c r="C339" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D339" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E339" t="str">
+        <v>2026-07-31T11:18:41.675Z</v>
+      </c>
+      <c r="F339" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>TC-GEN-1330</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Invalid registered user test case (330)</v>
+      </c>
+      <c r="C340" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D340" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E340" t="str">
+        <v>2026-07-31T11:18:41.692Z</v>
+      </c>
+      <c r="F340" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>TC-GEN-1331</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Leading/trailing whitespace inputs (331)</v>
+      </c>
+      <c r="C341" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D341" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E341" t="str">
+        <v>2026-07-31T11:18:41.707Z</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>TC-GEN-1332</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Alias email address with incorrect password (332)</v>
+      </c>
+      <c r="C342" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D342" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E342" t="str">
+        <v>2026-07-31T11:18:41.724Z</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>TC-GEN-1333</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Varying length generated inputs (333)</v>
+      </c>
+      <c r="C343" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D343" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E343" t="str">
+        <v>2026-07-31T11:18:41.738Z</v>
+      </c>
+      <c r="F343" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>TC-GEN-1334</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~</v>
+      </c>
+      <c r="C344" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D344" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E344" t="str">
+        <v>2026-07-31T11:18:41.754Z</v>
+      </c>
+      <c r="F344" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>TC-GEN-1335</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Fuzzing password field with DB query injection (335)</v>
+      </c>
+      <c r="C345" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D345" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E345" t="str">
+        <v>2026-07-31T11:18:41.770Z</v>
+      </c>
+      <c r="F345" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>TC-GEN-1336</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Invalid registered user test case (336)</v>
+      </c>
+      <c r="C346" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D346" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E346" t="str">
+        <v>2026-07-31T11:18:41.785Z</v>
+      </c>
+      <c r="F346" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>TC-GEN-1337</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Leading/trailing whitespace inputs (337)</v>
+      </c>
+      <c r="C347" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D347" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E347" t="str">
+        <v>2026-07-31T11:18:41.801Z</v>
+      </c>
+      <c r="F347" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>TC-GEN-1338</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Alias email address with incorrect password (338)</v>
+      </c>
+      <c r="C348" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D348" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E348" t="str">
+        <v>2026-07-31T11:18:41.817Z</v>
+      </c>
+      <c r="F348" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>TC-GEN-1339</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Varying length generated inputs (339)</v>
+      </c>
+      <c r="C349" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D349" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E349" t="str">
+        <v>2026-07-31T11:18:41.833Z</v>
+      </c>
+      <c r="F349" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>TC-GEN-1340</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Password with special characters: !#$</v>
+      </c>
+      <c r="C350" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D350" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E350" t="str">
+        <v>2026-07-31T11:18:41.849Z</v>
+      </c>
+      <c r="F350" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>TC-GEN-1341</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Fuzzing password field with DB query injection (341)</v>
+      </c>
+      <c r="C351" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D351" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E351" t="str">
+        <v>2026-07-31T11:18:41.865Z</v>
+      </c>
+      <c r="F351" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>TC-GEN-1342</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Invalid registered user test case (342)</v>
+      </c>
+      <c r="C352" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D352" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E352" t="str">
+        <v>2026-07-31T11:18:41.880Z</v>
+      </c>
+      <c r="F352" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>TC-GEN-1343</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Leading/trailing whitespace inputs (343)</v>
+      </c>
+      <c r="C353" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D353" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E353" t="str">
+        <v>2026-07-31T11:18:41.895Z</v>
+      </c>
+      <c r="F353" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>TC-GEN-1344</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Alias email address with incorrect password (344)</v>
+      </c>
+      <c r="C354" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D354" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E354" t="str">
+        <v>2026-07-31T11:18:41.912Z</v>
+      </c>
+      <c r="F354" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>TC-GEN-1345</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Varying length generated inputs (345)</v>
+      </c>
+      <c r="C355" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D355" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E355" t="str">
+        <v>2026-07-31T11:18:41.926Z</v>
+      </c>
+      <c r="F355" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>TC-GEN-1346</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Password with special characters: !#$%^&amp;*()</v>
+      </c>
+      <c r="C356" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D356" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E356" t="str">
+        <v>2026-07-31T11:18:41.943Z</v>
+      </c>
+      <c r="F356" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>TC-GEN-1347</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Fuzzing password field with DB query injection (347)</v>
+      </c>
+      <c r="C357" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D357" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E357" t="str">
+        <v>2026-07-31T11:18:41.958Z</v>
+      </c>
+      <c r="F357" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>TC-GEN-1348</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Invalid registered user test case (348)</v>
+      </c>
+      <c r="C358" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D358" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E358" t="str">
+        <v>2026-07-31T11:18:41.974Z</v>
+      </c>
+      <c r="F358" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>TC-GEN-1349</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Leading/trailing whitespace inputs (349)</v>
+      </c>
+      <c r="C359" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D359" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E359" t="str">
+        <v>2026-07-31T11:18:41.989Z</v>
+      </c>
+      <c r="F359" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>TC-GEN-1350</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Alias email address with incorrect password (350)</v>
+      </c>
+      <c r="C360" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D360" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E360" t="str">
+        <v>2026-07-31T11:18:42.005Z</v>
+      </c>
+      <c r="F360" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>TC-GEN-1351</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Varying length generated inputs (351)</v>
+      </c>
+      <c r="C361" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D361" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E361" t="str">
+        <v>2026-07-31T11:18:42.020Z</v>
+      </c>
+      <c r="F361" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>TC-GEN-1352</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Password with special characters: !#</v>
+      </c>
+      <c r="C362" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D362" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E362" t="str">
+        <v>2026-07-31T11:18:42.036Z</v>
+      </c>
+      <c r="F362" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>TC-GEN-1353</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Fuzzing password field with DB query injection (353)</v>
+      </c>
+      <c r="C363" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D363" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E363" t="str">
+        <v>2026-07-31T11:18:42.052Z</v>
+      </c>
+      <c r="F363" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>TC-GEN-1354</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Invalid registered user test case (354)</v>
+      </c>
+      <c r="C364" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D364" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E364" t="str">
+        <v>2026-07-31T11:18:42.068Z</v>
+      </c>
+      <c r="F364" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>TC-GEN-1355</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Leading/trailing whitespace inputs (355)</v>
+      </c>
+      <c r="C365" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D365" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E365" t="str">
+        <v>2026-07-31T11:18:42.083Z</v>
+      </c>
+      <c r="F365" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>TC-GEN-1356</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Alias email address with incorrect password (356)</v>
+      </c>
+      <c r="C366" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D366" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E366" t="str">
+        <v>2026-07-31T11:18:42.098Z</v>
+      </c>
+      <c r="F366" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>TC-GEN-1357</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Varying length generated inputs (357)</v>
+      </c>
+      <c r="C367" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D367" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E367" t="str">
+        <v>2026-07-31T11:18:42.114Z</v>
+      </c>
+      <c r="F367" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>TC-GEN-1358</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Password with special characters: !#$%^&amp;*(</v>
+      </c>
+      <c r="C368" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D368" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E368" t="str">
+        <v>2026-07-31T11:18:42.128Z</v>
+      </c>
+      <c r="F368" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>TC-GEN-1359</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Fuzzing password field with DB query injection (359)</v>
+      </c>
+      <c r="C369" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D369" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E369" t="str">
+        <v>2026-07-31T11:18:42.144Z</v>
+      </c>
+      <c r="F369" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>TC-GEN-1360</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Invalid registered user test case (360)</v>
+      </c>
+      <c r="C370" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D370" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E370" t="str">
+        <v>2026-07-31T11:18:42.160Z</v>
+      </c>
+      <c r="F370" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>TC-GEN-1361</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Leading/trailing whitespace inputs (361)</v>
+      </c>
+      <c r="C371" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D371" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E371" t="str">
+        <v>2026-07-31T11:18:42.176Z</v>
+      </c>
+      <c r="F371" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>TC-GEN-1362</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Alias email address with incorrect password (362)</v>
+      </c>
+      <c r="C372" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D372" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E372" t="str">
+        <v>2026-07-31T11:18:42.192Z</v>
+      </c>
+      <c r="F372" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>TC-GEN-1363</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Varying length generated inputs (363)</v>
+      </c>
+      <c r="C373" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D373" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E373" t="str">
+        <v>2026-07-31T11:18:42.207Z</v>
+      </c>
+      <c r="F373" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>TC-GEN-1364</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Password with special characters: !</v>
+      </c>
+      <c r="C374" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D374" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E374" t="str">
+        <v>2026-07-31T11:18:42.222Z</v>
+      </c>
+      <c r="F374" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>TC-GEN-1365</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Fuzzing password field with DB query injection (365)</v>
+      </c>
+      <c r="C375" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D375" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E375" t="str">
+        <v>2026-07-31T11:18:42.238Z</v>
+      </c>
+      <c r="F375" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>TC-GEN-1366</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Invalid registered user test case (366)</v>
+      </c>
+      <c r="C376" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D376" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E376" t="str">
+        <v>2026-07-31T11:18:42.254Z</v>
+      </c>
+      <c r="F376" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>TC-GEN-1367</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Leading/trailing whitespace inputs (367)</v>
+      </c>
+      <c r="C377" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D377" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E377" t="str">
+        <v>2026-07-31T11:18:42.270Z</v>
+      </c>
+      <c r="F377" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>TC-GEN-1368</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Alias email address with incorrect password (368)</v>
+      </c>
+      <c r="C378" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D378" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E378" t="str">
+        <v>2026-07-31T11:18:42.285Z</v>
+      </c>
+      <c r="F378" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>TC-GEN-1369</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Varying length generated inputs (369)</v>
+      </c>
+      <c r="C379" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D379" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E379" t="str">
+        <v>2026-07-31T11:18:42.301Z</v>
+      </c>
+      <c r="F379" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>TC-GEN-1370</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Password with special characters: !#$%^&amp;*</v>
+      </c>
+      <c r="C380" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D380" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E380" t="str">
+        <v>2026-07-31T11:18:42.316Z</v>
+      </c>
+      <c r="F380" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>TC-GEN-1371</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Fuzzing password field with DB query injection (371)</v>
+      </c>
+      <c r="C381" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D381" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E381" t="str">
+        <v>2026-07-31T11:18:42.332Z</v>
+      </c>
+      <c r="F381" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>TC-GEN-1372</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Invalid registered user test case (372)</v>
+      </c>
+      <c r="C382" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D382" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E382" t="str">
+        <v>2026-07-31T11:18:42.348Z</v>
+      </c>
+      <c r="F382" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>TC-GEN-1373</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Leading/trailing whitespace inputs (373)</v>
+      </c>
+      <c r="C383" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D383" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E383" t="str">
+        <v>2026-07-31T11:18:42.364Z</v>
+      </c>
+      <c r="F383" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>TC-GEN-1374</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Alias email address with incorrect password (374)</v>
+      </c>
+      <c r="C384" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D384" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E384" t="str">
+        <v>2026-07-31T11:18:42.379Z</v>
+      </c>
+      <c r="F384" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>TC-GEN-1375</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Varying length generated inputs (375)</v>
+      </c>
+      <c r="C385" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D385" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E385" t="str">
+        <v>2026-07-31T11:18:42.395Z</v>
+      </c>
+      <c r="F385" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>TC-GEN-1376</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C386" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D386" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E386" t="str">
+        <v>2026-07-31T11:18:42.411Z</v>
+      </c>
+      <c r="F386" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>TC-GEN-1377</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Fuzzing password field with DB query injection (377)</v>
+      </c>
+      <c r="C387" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D387" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E387" t="str">
+        <v>2026-07-31T11:18:42.426Z</v>
+      </c>
+      <c r="F387" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>TC-GEN-1378</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Invalid registered user test case (378)</v>
+      </c>
+      <c r="C388" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D388" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E388" t="str">
+        <v>2026-07-31T11:18:42.442Z</v>
+      </c>
+      <c r="F388" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>TC-GEN-1379</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Leading/trailing whitespace inputs (379)</v>
+      </c>
+      <c r="C389" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D389" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E389" t="str">
+        <v>2026-07-31T11:18:42.458Z</v>
+      </c>
+      <c r="F389" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>TC-GEN-1380</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Alias email address with incorrect password (380)</v>
+      </c>
+      <c r="C390" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D390" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E390" t="str">
+        <v>2026-07-31T11:18:42.474Z</v>
+      </c>
+      <c r="F390" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>TC-GEN-1381</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Varying length generated inputs (381)</v>
+      </c>
+      <c r="C391" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D391" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E391" t="str">
+        <v>2026-07-31T11:18:42.489Z</v>
+      </c>
+      <c r="F391" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>TC-GEN-1382</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Password with special characters: !#$%^&amp;</v>
+      </c>
+      <c r="C392" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D392" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E392" t="str">
+        <v>2026-07-31T11:18:42.505Z</v>
+      </c>
+      <c r="F392" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>TC-GEN-1383</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Fuzzing password field with DB query injection (383)</v>
+      </c>
+      <c r="C393" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D393" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E393" t="str">
+        <v>2026-07-31T11:18:42.521Z</v>
+      </c>
+      <c r="F393" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>TC-GEN-1384</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Invalid registered user test case (384)</v>
+      </c>
+      <c r="C394" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D394" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E394" t="str">
+        <v>2026-07-31T11:18:42.537Z</v>
+      </c>
+      <c r="F394" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>TC-GEN-1385</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Leading/trailing whitespace inputs (385)</v>
+      </c>
+      <c r="C395" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D395" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E395" t="str">
+        <v>2026-07-31T11:18:42.553Z</v>
+      </c>
+      <c r="F395" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>TC-GEN-1386</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Alias email address with incorrect password (386)</v>
+      </c>
+      <c r="C396" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D396" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E396" t="str">
+        <v>2026-07-31T11:18:42.568Z</v>
+      </c>
+      <c r="F396" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>TC-GEN-1387</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Varying length generated inputs (387)</v>
+      </c>
+      <c r="C397" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D397" t="str">
+        <v>0.01 sec</v>
+      </c>
+      <c r="E397" t="str">
+        <v>2026-07-31T11:18:42.583Z</v>
+      </c>
+      <c r="F397" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>TC-GEN-1388</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Password with special characters: !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C398" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D398" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E398" t="str">
+        <v>2026-07-31T11:18:42.599Z</v>
+      </c>
+      <c r="F398" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>TC-GEN-1389</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Fuzzing password field with DB query injection (389)</v>
+      </c>
+      <c r="C399" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D399" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E399" t="str">
+        <v>2026-07-31T11:18:42.615Z</v>
+      </c>
+      <c r="F399" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>TC-GEN-1390</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Invalid registered user test case (390)</v>
+      </c>
+      <c r="C400" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D400" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E400" t="str">
+        <v>2026-07-31T11:18:42.631Z</v>
+      </c>
+      <c r="F400" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>TC-GEN-1391</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Leading/trailing whitespace inputs (391)</v>
+      </c>
+      <c r="C401" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D401" t="str">
+        <v>0.02 sec</v>
+      </c>
+      <c r="E401" t="str">
+        <v>2026-07-31T11:18:42.647Z</v>
+      </c>
+      <c r="F401" t="str">
+        <v>Success</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F401"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/Appium Report.xlsx
+++ b/reports/Appium Report.xlsx
@@ -433,7 +433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-31T11:18:36.458Z</v>
+        <v>2026-08-01T10:49:38.258Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -450,10 +450,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-31T11:18:36.463Z</v>
+        <v>2026-08-01T10:49:38.275Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -473,7 +473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-31T11:18:36.473Z</v>
+        <v>2026-08-01T10:49:38.290Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -493,7 +493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-31T11:18:36.489Z</v>
+        <v>2026-08-01T10:49:38.306Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-31T11:18:36.504Z</v>
+        <v>2026-08-01T10:49:38.322Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -533,7 +533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-31T11:18:36.520Z</v>
+        <v>2026-08-01T10:49:38.338Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -553,7 +553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-31T11:18:36.535Z</v>
+        <v>2026-08-01T10:49:38.353Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -573,7 +573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-31T11:18:36.551Z</v>
+        <v>2026-08-01T10:49:38.369Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -590,10 +590,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-31T11:18:36.566Z</v>
+        <v>2026-08-01T10:49:38.385Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -610,10 +610,10 @@
         <v>PASS</v>
       </c>
       <c r="D11" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-31T11:18:36.582Z</v>
+        <v>2026-08-01T10:49:38.400Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -633,7 +633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-31T11:18:36.598Z</v>
+        <v>2026-08-01T10:49:38.415Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -650,10 +650,10 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-31T11:18:36.613Z</v>
+        <v>2026-08-01T10:49:38.432Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -673,7 +673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-31T11:18:36.629Z</v>
+        <v>2026-08-01T10:49:38.448Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -693,7 +693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-31T11:18:36.644Z</v>
+        <v>2026-08-01T10:49:38.463Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -713,7 +713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-31T11:18:36.659Z</v>
+        <v>2026-08-01T10:49:38.477Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -733,7 +733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-31T11:18:36.675Z</v>
+        <v>2026-08-01T10:49:38.493Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -750,10 +750,10 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-31T11:18:36.690Z</v>
+        <v>2026-08-01T10:49:38.509Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -770,10 +770,10 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-31T11:18:36.706Z</v>
+        <v>2026-08-01T10:49:38.524Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -790,10 +790,10 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-31T11:18:36.722Z</v>
+        <v>2026-08-01T10:49:38.539Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -810,10 +810,10 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-31T11:18:36.737Z</v>
+        <v>2026-08-01T10:49:38.555Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -830,10 +830,10 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-31T11:18:36.753Z</v>
+        <v>2026-08-01T10:49:38.570Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -850,10 +850,10 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-31T11:18:36.768Z</v>
+        <v>2026-08-01T10:49:38.586Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -873,7 +873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-31T11:18:36.784Z</v>
+        <v>2026-08-01T10:49:38.602Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -893,7 +893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-31T11:18:36.800Z</v>
+        <v>2026-08-01T10:49:38.618Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -910,10 +910,10 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-31T11:18:36.816Z</v>
+        <v>2026-08-01T10:49:38.633Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -933,7 +933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-31T11:18:36.832Z</v>
+        <v>2026-08-01T10:49:38.649Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -953,7 +953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-31T11:18:36.847Z</v>
+        <v>2026-08-01T10:49:38.664Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -970,10 +970,10 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-31T11:18:36.863Z</v>
+        <v>2026-08-01T10:49:38.679Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -993,7 +993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-31T11:18:36.879Z</v>
+        <v>2026-08-01T10:49:38.695Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1013,7 +1013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-31T11:18:36.894Z</v>
+        <v>2026-08-01T10:49:38.710Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1033,7 +1033,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-31T11:18:36.910Z</v>
+        <v>2026-08-01T10:49:38.726Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1053,7 +1053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-31T11:18:36.925Z</v>
+        <v>2026-08-01T10:49:38.741Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1070,10 +1070,10 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-31T11:18:36.940Z</v>
+        <v>2026-08-01T10:49:38.758Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1090,10 +1090,10 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-31T11:18:36.957Z</v>
+        <v>2026-08-01T10:49:38.773Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1113,7 +1113,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-31T11:18:36.971Z</v>
+        <v>2026-08-01T10:49:38.788Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1133,7 +1133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-31T11:18:36.987Z</v>
+        <v>2026-08-01T10:49:38.804Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1153,7 +1153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-31T11:18:37.003Z</v>
+        <v>2026-08-01T10:49:38.820Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1173,7 +1173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-31T11:18:37.018Z</v>
+        <v>2026-08-01T10:49:38.835Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1190,10 +1190,10 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-31T11:18:37.034Z</v>
+        <v>2026-08-01T10:49:38.850Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1213,7 +1213,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-31T11:18:37.050Z</v>
+        <v>2026-08-01T10:49:38.867Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1233,7 +1233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-31T11:18:37.066Z</v>
+        <v>2026-08-01T10:49:38.883Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1250,10 +1250,10 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-31T11:18:37.080Z</v>
+        <v>2026-08-01T10:49:38.899Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1273,7 +1273,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-31T11:18:37.095Z</v>
+        <v>2026-08-01T10:49:38.913Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1293,7 +1293,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-31T11:18:37.111Z</v>
+        <v>2026-08-01T10:49:38.929Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1313,7 +1313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-31T11:18:37.127Z</v>
+        <v>2026-08-01T10:49:38.945Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1333,7 +1333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-31T11:18:37.142Z</v>
+        <v>2026-08-01T10:49:38.960Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1353,7 +1353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-31T11:18:37.158Z</v>
+        <v>2026-08-01T10:49:38.976Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1373,7 +1373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-31T11:18:37.173Z</v>
+        <v>2026-08-01T10:49:38.991Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1393,7 +1393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-31T11:18:37.189Z</v>
+        <v>2026-08-01T10:49:39.007Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1410,10 +1410,10 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-31T11:18:37.204Z</v>
+        <v>2026-08-01T10:49:39.023Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1430,10 +1430,10 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-31T11:18:37.220Z</v>
+        <v>2026-08-01T10:49:39.038Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1453,7 +1453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-31T11:18:37.236Z</v>
+        <v>2026-08-01T10:49:39.054Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1473,7 +1473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-31T11:18:37.252Z</v>
+        <v>2026-08-01T10:49:39.070Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1490,10 +1490,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-31T11:18:37.267Z</v>
+        <v>2026-08-01T10:49:39.086Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1513,7 +1513,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-31T11:18:37.282Z</v>
+        <v>2026-08-01T10:49:39.101Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1530,10 +1530,10 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-31T11:18:37.297Z</v>
+        <v>2026-08-01T10:49:39.117Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1550,10 +1550,10 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-31T11:18:37.313Z</v>
+        <v>2026-08-01T10:49:39.132Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1570,10 +1570,10 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-31T11:18:37.329Z</v>
+        <v>2026-08-01T10:49:39.147Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1593,7 +1593,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-31T11:18:37.344Z</v>
+        <v>2026-08-01T10:49:39.162Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1613,7 +1613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-31T11:18:37.360Z</v>
+        <v>2026-08-01T10:49:39.177Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1630,10 +1630,10 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-31T11:18:37.376Z</v>
+        <v>2026-08-01T10:49:39.193Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1650,10 +1650,10 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-31T11:18:37.392Z</v>
+        <v>2026-08-01T10:49:39.209Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1670,10 +1670,10 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-31T11:18:37.407Z</v>
+        <v>2026-08-01T10:49:39.225Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1690,10 +1690,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-31T11:18:37.423Z</v>
+        <v>2026-08-01T10:49:39.240Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1713,7 +1713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-31T11:18:37.438Z</v>
+        <v>2026-08-01T10:49:39.255Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1730,10 +1730,10 @@
         <v>PASS</v>
       </c>
       <c r="D67" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-31T11:18:37.454Z</v>
+        <v>2026-08-01T10:49:39.271Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1753,7 +1753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-31T11:18:37.470Z</v>
+        <v>2026-08-01T10:49:39.287Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -1770,10 +1770,10 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-31T11:18:37.485Z</v>
+        <v>2026-08-01T10:49:39.303Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -1790,10 +1790,10 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-31T11:18:37.502Z</v>
+        <v>2026-08-01T10:49:39.318Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -1810,10 +1810,10 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-31T11:18:37.517Z</v>
+        <v>2026-08-01T10:49:39.334Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -1833,7 +1833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-31T11:18:37.531Z</v>
+        <v>2026-08-01T10:49:39.348Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -1853,7 +1853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-31T11:18:37.548Z</v>
+        <v>2026-08-01T10:49:39.364Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -1873,7 +1873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-31T11:18:37.564Z</v>
+        <v>2026-08-01T10:49:39.380Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -1890,10 +1890,10 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-31T11:18:37.579Z</v>
+        <v>2026-08-01T10:49:39.396Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -1913,7 +1913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-31T11:18:37.594Z</v>
+        <v>2026-08-01T10:49:39.411Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -1933,7 +1933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-31T11:18:37.610Z</v>
+        <v>2026-08-01T10:49:39.427Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -1953,7 +1953,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-31T11:18:37.626Z</v>
+        <v>2026-08-01T10:49:39.443Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -1970,10 +1970,10 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-31T11:18:37.641Z</v>
+        <v>2026-08-01T10:49:39.459Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -1990,10 +1990,10 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-31T11:18:37.657Z</v>
+        <v>2026-08-01T10:49:39.474Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2010,10 +2010,10 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-31T11:18:37.672Z</v>
+        <v>2026-08-01T10:49:39.490Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2033,7 +2033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-31T11:18:37.687Z</v>
+        <v>2026-08-01T10:49:39.505Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2050,10 +2050,10 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-31T11:18:37.702Z</v>
+        <v>2026-08-01T10:49:39.522Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2073,7 +2073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-31T11:18:37.717Z</v>
+        <v>2026-08-01T10:49:39.537Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2093,7 +2093,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-31T11:18:37.732Z</v>
+        <v>2026-08-01T10:49:39.552Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2113,7 +2113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-31T11:18:37.748Z</v>
+        <v>2026-08-01T10:49:39.569Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2133,7 +2133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-31T11:18:37.763Z</v>
+        <v>2026-08-01T10:49:39.583Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2150,10 +2150,10 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-31T11:18:37.779Z</v>
+        <v>2026-08-01T10:49:39.599Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2170,10 +2170,10 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-31T11:18:37.795Z</v>
+        <v>2026-08-01T10:49:39.614Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2190,10 +2190,10 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-31T11:18:37.810Z</v>
+        <v>2026-08-01T10:49:39.631Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2213,7 +2213,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-31T11:18:37.825Z</v>
+        <v>2026-08-01T10:49:39.646Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2233,7 +2233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-31T11:18:37.841Z</v>
+        <v>2026-08-01T10:49:39.661Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2253,7 +2253,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-31T11:18:37.857Z</v>
+        <v>2026-08-01T10:49:39.677Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2273,7 +2273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-31T11:18:37.873Z</v>
+        <v>2026-08-01T10:49:39.693Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2290,10 +2290,10 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-31T11:18:37.889Z</v>
+        <v>2026-08-01T10:49:39.707Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2310,10 +2310,10 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-31T11:18:37.904Z</v>
+        <v>2026-08-01T10:49:39.723Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2333,7 +2333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-31T11:18:37.919Z</v>
+        <v>2026-08-01T10:49:39.738Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2353,7 +2353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-31T11:18:37.934Z</v>
+        <v>2026-08-01T10:49:39.754Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2373,7 +2373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-31T11:18:37.950Z</v>
+        <v>2026-08-01T10:49:39.770Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2393,7 +2393,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-31T11:18:37.965Z</v>
+        <v>2026-08-01T10:49:39.785Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2413,7 +2413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-31T11:18:37.980Z</v>
+        <v>2026-08-01T10:49:39.800Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2433,7 +2433,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-31T11:18:37.996Z</v>
+        <v>2026-08-01T10:49:39.816Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2453,7 +2453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-31T11:18:38.011Z</v>
+        <v>2026-08-01T10:49:39.831Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2470,10 +2470,10 @@
         <v>PASS</v>
       </c>
       <c r="D104" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-31T11:18:38.026Z</v>
+        <v>2026-08-01T10:49:39.847Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2493,7 +2493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-31T11:18:38.042Z</v>
+        <v>2026-08-01T10:49:39.863Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2510,10 +2510,10 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-31T11:18:38.058Z</v>
+        <v>2026-08-01T10:49:39.878Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2530,10 +2530,10 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-31T11:18:38.073Z</v>
+        <v>2026-08-01T10:49:39.894Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2553,7 +2553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-31T11:18:38.088Z</v>
+        <v>2026-08-01T10:49:39.909Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2570,10 +2570,10 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-31T11:18:38.104Z</v>
+        <v>2026-08-01T10:49:39.924Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2593,7 +2593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-31T11:18:38.120Z</v>
+        <v>2026-08-01T10:49:39.940Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2613,7 +2613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-31T11:18:38.135Z</v>
+        <v>2026-08-01T10:49:39.955Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2633,7 +2633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-31T11:18:38.150Z</v>
+        <v>2026-08-01T10:49:39.970Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2650,10 +2650,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-31T11:18:38.166Z</v>
+        <v>2026-08-01T10:49:39.986Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2670,10 +2670,10 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-31T11:18:38.181Z</v>
+        <v>2026-08-01T10:49:40.002Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2690,10 +2690,10 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-31T11:18:38.196Z</v>
+        <v>2026-08-01T10:49:40.018Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2713,7 +2713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-31T11:18:38.212Z</v>
+        <v>2026-08-01T10:49:40.034Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2733,7 +2733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-31T11:18:38.229Z</v>
+        <v>2026-08-01T10:49:40.050Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2750,10 +2750,10 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-31T11:18:38.244Z</v>
+        <v>2026-08-01T10:49:40.066Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -2773,7 +2773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-31T11:18:38.260Z</v>
+        <v>2026-08-01T10:49:40.081Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -2793,7 +2793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-31T11:18:38.276Z</v>
+        <v>2026-08-01T10:49:40.097Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -2813,7 +2813,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-31T11:18:38.291Z</v>
+        <v>2026-08-01T10:49:40.112Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-31T11:18:38.306Z</v>
+        <v>2026-08-01T10:49:40.128Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -2853,7 +2853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-31T11:18:38.322Z</v>
+        <v>2026-08-01T10:49:40.144Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -2873,7 +2873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-31T11:18:38.336Z</v>
+        <v>2026-08-01T10:49:40.159Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -2893,7 +2893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-31T11:18:38.353Z</v>
+        <v>2026-08-01T10:49:40.175Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -2910,10 +2910,10 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-31T11:18:38.368Z</v>
+        <v>2026-08-01T10:49:40.191Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -2933,7 +2933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-31T11:18:38.383Z</v>
+        <v>2026-08-01T10:49:40.206Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -2950,10 +2950,10 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-31T11:18:38.399Z</v>
+        <v>2026-08-01T10:49:40.221Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -2970,10 +2970,10 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-31T11:18:38.414Z</v>
+        <v>2026-08-01T10:49:40.237Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -2993,7 +2993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-31T11:18:38.430Z</v>
+        <v>2026-08-01T10:49:40.252Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3010,10 +3010,10 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-31T11:18:38.445Z</v>
+        <v>2026-08-01T10:49:40.268Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3033,7 +3033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-31T11:18:38.460Z</v>
+        <v>2026-08-01T10:49:40.283Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3053,7 +3053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-31T11:18:38.476Z</v>
+        <v>2026-08-01T10:49:40.299Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3070,10 +3070,10 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-31T11:18:38.491Z</v>
+        <v>2026-08-01T10:49:40.315Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3093,7 +3093,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-31T11:18:38.506Z</v>
+        <v>2026-08-01T10:49:40.330Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3110,10 +3110,10 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-31T11:18:38.522Z</v>
+        <v>2026-08-01T10:49:40.345Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3130,10 +3130,10 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-31T11:18:38.537Z</v>
+        <v>2026-08-01T10:49:40.361Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3153,7 +3153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-31T11:18:38.552Z</v>
+        <v>2026-08-01T10:49:40.376Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3170,10 +3170,10 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-31T11:18:38.568Z</v>
+        <v>2026-08-01T10:49:40.392Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3193,7 +3193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-31T11:18:38.584Z</v>
+        <v>2026-08-01T10:49:40.409Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3213,7 +3213,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-31T11:18:38.599Z</v>
+        <v>2026-08-01T10:49:40.423Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3233,7 +3233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-31T11:18:38.615Z</v>
+        <v>2026-08-01T10:49:40.440Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3250,10 +3250,10 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-31T11:18:38.631Z</v>
+        <v>2026-08-01T10:49:40.455Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3270,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-31T11:18:38.647Z</v>
+        <v>2026-08-01T10:49:40.470Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3293,7 +3293,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-31T11:18:38.663Z</v>
+        <v>2026-08-01T10:49:40.486Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3313,7 +3313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-31T11:18:38.679Z</v>
+        <v>2026-08-01T10:49:40.502Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3333,7 +3333,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-31T11:18:38.695Z</v>
+        <v>2026-08-01T10:49:40.518Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3353,7 +3353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-31T11:18:38.710Z</v>
+        <v>2026-08-01T10:49:40.533Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3373,7 +3373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-31T11:18:38.725Z</v>
+        <v>2026-08-01T10:49:40.548Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3393,7 +3393,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-31T11:18:38.741Z</v>
+        <v>2026-08-01T10:49:40.563Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3410,10 +3410,10 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-31T11:18:38.757Z</v>
+        <v>2026-08-01T10:49:40.578Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3430,10 +3430,10 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-31T11:18:38.772Z</v>
+        <v>2026-08-01T10:49:40.594Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3453,7 +3453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-31T11:18:38.787Z</v>
+        <v>2026-08-01T10:49:40.609Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3473,7 +3473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-31T11:18:38.803Z</v>
+        <v>2026-08-01T10:49:40.626Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3493,7 +3493,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-31T11:18:38.818Z</v>
+        <v>2026-08-01T10:49:40.641Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3510,10 +3510,10 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-31T11:18:38.834Z</v>
+        <v>2026-08-01T10:49:40.657Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3533,7 +3533,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-31T11:18:38.849Z</v>
+        <v>2026-08-01T10:49:40.672Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3550,10 +3550,10 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-31T11:18:38.867Z</v>
+        <v>2026-08-01T10:49:40.688Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3573,7 +3573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-31T11:18:38.881Z</v>
+        <v>2026-08-01T10:49:40.703Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3590,10 +3590,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-31T11:18:38.897Z</v>
+        <v>2026-08-01T10:49:40.718Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3613,7 +3613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-31T11:18:38.913Z</v>
+        <v>2026-08-01T10:49:40.734Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3633,7 +3633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-31T11:18:38.928Z</v>
+        <v>2026-08-01T10:49:40.749Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3650,10 +3650,10 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-31T11:18:38.943Z</v>
+        <v>2026-08-01T10:49:40.765Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3673,7 +3673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-31T11:18:38.959Z</v>
+        <v>2026-08-01T10:49:40.781Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3693,7 +3693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-31T11:18:38.974Z</v>
+        <v>2026-08-01T10:49:40.796Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3713,7 +3713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-31T11:18:38.990Z</v>
+        <v>2026-08-01T10:49:40.812Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3730,10 +3730,10 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-31T11:18:39.005Z</v>
+        <v>2026-08-01T10:49:40.828Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3753,7 +3753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-31T11:18:39.020Z</v>
+        <v>2026-08-01T10:49:40.843Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -3770,10 +3770,10 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-31T11:18:39.036Z</v>
+        <v>2026-08-01T10:49:40.858Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -3790,10 +3790,10 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-31T11:18:39.051Z</v>
+        <v>2026-08-01T10:49:40.874Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -3810,10 +3810,10 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-31T11:18:39.067Z</v>
+        <v>2026-08-01T10:49:40.889Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -3833,7 +3833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-31T11:18:39.082Z</v>
+        <v>2026-08-01T10:49:40.904Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -3850,10 +3850,10 @@
         <v>PASS</v>
       </c>
       <c r="D173" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-31T11:18:39.097Z</v>
+        <v>2026-08-01T10:49:40.921Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -3870,10 +3870,10 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-31T11:18:39.113Z</v>
+        <v>2026-08-01T10:49:40.936Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -3893,7 +3893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-31T11:18:39.130Z</v>
+        <v>2026-08-01T10:49:40.952Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -3913,7 +3913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-31T11:18:39.145Z</v>
+        <v>2026-08-01T10:49:40.967Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -3930,10 +3930,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-31T11:18:39.160Z</v>
+        <v>2026-08-01T10:49:40.983Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -3953,7 +3953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-31T11:18:39.176Z</v>
+        <v>2026-08-01T10:49:40.998Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -3970,10 +3970,10 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-31T11:18:39.192Z</v>
+        <v>2026-08-01T10:49:41.013Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -3993,7 +3993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-31T11:18:39.208Z</v>
+        <v>2026-08-01T10:49:41.029Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4013,7 +4013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-31T11:18:39.223Z</v>
+        <v>2026-08-01T10:49:41.044Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4030,10 +4030,10 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-31T11:18:39.238Z</v>
+        <v>2026-08-01T10:49:41.060Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4050,10 +4050,10 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-31T11:18:39.254Z</v>
+        <v>2026-08-01T10:49:41.075Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4073,7 +4073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-31T11:18:39.270Z</v>
+        <v>2026-08-01T10:49:41.091Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4090,10 +4090,10 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-31T11:18:39.286Z</v>
+        <v>2026-08-01T10:49:41.106Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4110,10 +4110,10 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-31T11:18:39.301Z</v>
+        <v>2026-08-01T10:49:41.122Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4133,7 +4133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-31T11:18:39.317Z</v>
+        <v>2026-08-01T10:49:41.138Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4153,7 +4153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-31T11:18:39.333Z</v>
+        <v>2026-08-01T10:49:41.154Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4170,10 +4170,10 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-31T11:18:39.348Z</v>
+        <v>2026-08-01T10:49:41.170Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4193,7 +4193,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-31T11:18:39.363Z</v>
+        <v>2026-08-01T10:49:41.185Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4213,7 +4213,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-31T11:18:39.379Z</v>
+        <v>2026-08-01T10:49:41.201Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4230,10 +4230,10 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-31T11:18:39.394Z</v>
+        <v>2026-08-01T10:49:41.217Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4250,10 +4250,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-31T11:18:39.410Z</v>
+        <v>2026-08-01T10:49:41.232Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4270,10 +4270,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-31T11:18:39.425Z</v>
+        <v>2026-08-01T10:49:41.248Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4290,10 +4290,10 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-31T11:18:39.440Z</v>
+        <v>2026-08-01T10:49:41.264Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4310,10 +4310,10 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-31T11:18:39.456Z</v>
+        <v>2026-08-01T10:49:41.280Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4330,10 +4330,10 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-31T11:18:39.472Z</v>
+        <v>2026-08-01T10:49:41.295Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4350,10 +4350,10 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-31T11:18:39.488Z</v>
+        <v>2026-08-01T10:49:41.310Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4370,10 +4370,10 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-31T11:18:39.503Z</v>
+        <v>2026-08-01T10:49:41.326Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4390,10 +4390,10 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-31T11:18:39.521Z</v>
+        <v>2026-08-01T10:49:41.341Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4413,7 +4413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-31T11:18:39.533Z</v>
+        <v>2026-08-01T10:49:41.356Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4433,7 +4433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-31T11:18:39.549Z</v>
+        <v>2026-08-01T10:49:41.372Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4453,7 +4453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-31T11:18:39.565Z</v>
+        <v>2026-08-01T10:49:41.388Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4473,7 +4473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-31T11:18:39.580Z</v>
+        <v>2026-08-01T10:49:41.403Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4493,7 +4493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-31T11:18:39.596Z</v>
+        <v>2026-08-01T10:49:41.419Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4510,10 +4510,10 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-31T11:18:39.611Z</v>
+        <v>2026-08-01T10:49:41.435Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4533,7 +4533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-31T11:18:39.627Z</v>
+        <v>2026-08-01T10:49:41.451Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4550,10 +4550,10 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-31T11:18:39.642Z</v>
+        <v>2026-08-01T10:49:41.467Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4570,10 +4570,10 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-31T11:18:39.657Z</v>
+        <v>2026-08-01T10:49:41.483Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4593,7 +4593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-31T11:18:39.673Z</v>
+        <v>2026-08-01T10:49:41.499Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4613,7 +4613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-31T11:18:39.688Z</v>
+        <v>2026-08-01T10:49:41.513Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4633,7 +4633,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-31T11:18:39.704Z</v>
+        <v>2026-08-01T10:49:41.529Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4650,10 +4650,10 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-31T11:18:39.719Z</v>
+        <v>2026-08-01T10:49:41.545Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4670,10 +4670,10 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-31T11:18:39.735Z</v>
+        <v>2026-08-01T10:49:41.560Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4690,10 +4690,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-31T11:18:39.751Z</v>
+        <v>2026-08-01T10:49:41.575Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4710,10 +4710,10 @@
         <v>PASS</v>
       </c>
       <c r="D216" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-31T11:18:39.766Z</v>
+        <v>2026-08-01T10:49:41.592Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4730,10 +4730,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-31T11:18:39.782Z</v>
+        <v>2026-08-01T10:49:41.607Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4753,7 +4753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-31T11:18:39.798Z</v>
+        <v>2026-08-01T10:49:41.623Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -4770,10 +4770,10 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-31T11:18:39.813Z</v>
+        <v>2026-08-01T10:49:41.639Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -4790,10 +4790,10 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-31T11:18:39.829Z</v>
+        <v>2026-08-01T10:49:41.654Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -4810,10 +4810,10 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-31T11:18:39.844Z</v>
+        <v>2026-08-01T10:49:41.670Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -4833,7 +4833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-31T11:18:39.860Z</v>
+        <v>2026-08-01T10:49:41.685Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -4853,7 +4853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-31T11:18:39.876Z</v>
+        <v>2026-08-01T10:49:41.701Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -4873,7 +4873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-31T11:18:39.892Z</v>
+        <v>2026-08-01T10:49:41.717Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -4890,10 +4890,10 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-31T11:18:39.906Z</v>
+        <v>2026-08-01T10:49:41.733Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -4913,7 +4913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-31T11:18:39.922Z</v>
+        <v>2026-08-01T10:49:41.749Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -4930,10 +4930,10 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-31T11:18:39.937Z</v>
+        <v>2026-08-01T10:49:41.765Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -4950,10 +4950,10 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-31T11:18:39.953Z</v>
+        <v>2026-08-01T10:49:41.779Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -4973,7 +4973,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-31T11:18:39.968Z</v>
+        <v>2026-08-01T10:49:41.794Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -4993,7 +4993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-31T11:18:39.983Z</v>
+        <v>2026-08-01T10:49:41.809Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5010,10 +5010,10 @@
         <v>PASS</v>
       </c>
       <c r="D231" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-31T11:18:39.999Z</v>
+        <v>2026-08-01T10:49:41.825Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5030,10 +5030,10 @@
         <v>PASS</v>
       </c>
       <c r="D232" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-31T11:18:40.014Z</v>
+        <v>2026-08-01T10:49:41.841Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5053,7 +5053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-31T11:18:40.029Z</v>
+        <v>2026-08-01T10:49:41.855Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5073,7 +5073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-31T11:18:40.045Z</v>
+        <v>2026-08-01T10:49:41.872Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5093,7 +5093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-31T11:18:40.061Z</v>
+        <v>2026-08-01T10:49:41.888Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5113,7 +5113,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-31T11:18:40.076Z</v>
+        <v>2026-08-01T10:49:41.903Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5130,10 +5130,10 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-31T11:18:40.091Z</v>
+        <v>2026-08-01T10:49:41.919Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5150,10 +5150,10 @@
         <v>PASS</v>
       </c>
       <c r="D238" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-31T11:18:40.107Z</v>
+        <v>2026-08-01T10:49:41.935Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5173,7 +5173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-31T11:18:40.122Z</v>
+        <v>2026-08-01T10:49:41.950Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5193,7 +5193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-31T11:18:40.138Z</v>
+        <v>2026-08-01T10:49:41.966Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5210,10 +5210,10 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-31T11:18:40.153Z</v>
+        <v>2026-08-01T10:49:41.982Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5230,10 +5230,10 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-31T11:18:40.170Z</v>
+        <v>2026-08-01T10:49:41.997Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5253,7 +5253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-31T11:18:40.185Z</v>
+        <v>2026-08-01T10:49:42.012Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5273,7 +5273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-31T11:18:40.202Z</v>
+        <v>2026-08-01T10:49:42.028Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5290,10 +5290,10 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-31T11:18:40.217Z</v>
+        <v>2026-08-01T10:49:42.044Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5310,10 +5310,10 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-31T11:18:40.233Z</v>
+        <v>2026-08-01T10:49:42.059Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5333,7 +5333,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-31T11:18:40.249Z</v>
+        <v>2026-08-01T10:49:42.075Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5353,7 +5353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-31T11:18:40.265Z</v>
+        <v>2026-08-01T10:49:42.090Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5373,7 +5373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-31T11:18:40.280Z</v>
+        <v>2026-08-01T10:49:42.105Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5390,10 +5390,10 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-31T11:18:40.295Z</v>
+        <v>2026-08-01T10:49:42.121Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5413,7 +5413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-31T11:18:40.310Z</v>
+        <v>2026-08-01T10:49:42.136Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5433,7 +5433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-31T11:18:40.325Z</v>
+        <v>2026-08-01T10:49:42.152Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5453,7 +5453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-31T11:18:40.340Z</v>
+        <v>2026-08-01T10:49:42.167Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5473,7 +5473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-31T11:18:40.356Z</v>
+        <v>2026-08-01T10:49:42.183Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5490,10 +5490,10 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-31T11:18:40.371Z</v>
+        <v>2026-08-01T10:49:42.199Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5510,10 +5510,10 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-31T11:18:40.387Z</v>
+        <v>2026-08-01T10:49:42.214Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5533,7 +5533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-31T11:18:40.404Z</v>
+        <v>2026-08-01T10:49:42.230Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5550,10 +5550,10 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-31T11:18:40.419Z</v>
+        <v>2026-08-01T10:49:42.246Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5570,10 +5570,10 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-31T11:18:40.433Z</v>
+        <v>2026-08-01T10:49:42.262Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5593,7 +5593,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-31T11:18:40.449Z</v>
+        <v>2026-08-01T10:49:42.277Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5613,7 +5613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-31T11:18:40.465Z</v>
+        <v>2026-08-01T10:49:42.293Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5633,7 +5633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-31T11:18:40.481Z</v>
+        <v>2026-08-01T10:49:42.308Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5653,7 +5653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-31T11:18:40.497Z</v>
+        <v>2026-08-01T10:49:42.324Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5673,7 +5673,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-31T11:18:40.512Z</v>
+        <v>2026-08-01T10:49:42.339Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5693,7 +5693,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-31T11:18:40.528Z</v>
+        <v>2026-08-01T10:49:42.355Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5710,10 +5710,10 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-31T11:18:40.543Z</v>
+        <v>2026-08-01T10:49:42.372Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5730,10 +5730,10 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-31T11:18:40.559Z</v>
+        <v>2026-08-01T10:49:42.386Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5753,7 +5753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-31T11:18:40.575Z</v>
+        <v>2026-08-01T10:49:42.402Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -5770,10 +5770,10 @@
         <v>PASS</v>
       </c>
       <c r="D269" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-31T11:18:40.591Z</v>
+        <v>2026-08-01T10:49:42.417Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -5793,7 +5793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-31T11:18:40.607Z</v>
+        <v>2026-08-01T10:49:42.433Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -5810,10 +5810,10 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-31T11:18:40.621Z</v>
+        <v>2026-08-01T10:49:42.449Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -5830,10 +5830,10 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-31T11:18:40.637Z</v>
+        <v>2026-08-01T10:49:42.464Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -5850,10 +5850,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-31T11:18:40.652Z</v>
+        <v>2026-08-01T10:49:42.480Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -5873,7 +5873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-31T11:18:40.667Z</v>
+        <v>2026-08-01T10:49:42.495Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -5890,10 +5890,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-31T11:18:40.682Z</v>
+        <v>2026-08-01T10:49:42.511Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -5913,7 +5913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-31T11:18:40.697Z</v>
+        <v>2026-08-01T10:49:42.525Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -5930,10 +5930,10 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-31T11:18:40.713Z</v>
+        <v>2026-08-01T10:49:42.540Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -5953,7 +5953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-31T11:18:40.728Z</v>
+        <v>2026-08-01T10:49:42.555Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -5970,10 +5970,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-31T11:18:40.743Z</v>
+        <v>2026-08-01T10:49:42.571Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -5993,7 +5993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-31T11:18:40.760Z</v>
+        <v>2026-08-01T10:49:42.587Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6013,7 +6013,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-31T11:18:40.776Z</v>
+        <v>2026-08-01T10:49:42.603Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6033,7 +6033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-31T11:18:40.791Z</v>
+        <v>2026-08-01T10:49:42.618Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6050,10 +6050,10 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-31T11:18:40.807Z</v>
+        <v>2026-08-01T10:49:42.633Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6073,7 +6073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-31T11:18:40.823Z</v>
+        <v>2026-08-01T10:49:42.649Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6093,7 +6093,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-31T11:18:40.838Z</v>
+        <v>2026-08-01T10:49:42.664Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6110,10 +6110,10 @@
         <v>PASS</v>
       </c>
       <c r="D286" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-31T11:18:40.854Z</v>
+        <v>2026-08-01T10:49:42.680Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6130,10 +6130,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-31T11:18:40.869Z</v>
+        <v>2026-08-01T10:49:42.696Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6153,7 +6153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-31T11:18:40.884Z</v>
+        <v>2026-08-01T10:49:42.711Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6173,7 +6173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-31T11:18:40.900Z</v>
+        <v>2026-08-01T10:49:42.727Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6190,10 +6190,10 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-31T11:18:40.916Z</v>
+        <v>2026-08-01T10:49:42.742Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6213,7 +6213,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-31T11:18:40.931Z</v>
+        <v>2026-08-01T10:49:42.758Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6233,7 +6233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-31T11:18:40.947Z</v>
+        <v>2026-08-01T10:49:42.774Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6253,7 +6253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-31T11:18:40.962Z</v>
+        <v>2026-08-01T10:49:42.789Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6270,10 +6270,10 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-31T11:18:40.977Z</v>
+        <v>2026-08-01T10:49:42.805Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6290,10 +6290,10 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-31T11:18:40.993Z</v>
+        <v>2026-08-01T10:49:42.820Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6310,10 +6310,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-31T11:18:41.009Z</v>
+        <v>2026-08-01T10:49:42.835Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6330,10 +6330,10 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-31T11:18:41.023Z</v>
+        <v>2026-08-01T10:49:42.851Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6353,7 +6353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-31T11:18:41.039Z</v>
+        <v>2026-08-01T10:49:42.867Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6370,10 +6370,10 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-31T11:18:41.054Z</v>
+        <v>2026-08-01T10:49:42.883Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6390,10 +6390,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-31T11:18:41.070Z</v>
+        <v>2026-08-01T10:49:42.898Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6410,10 +6410,10 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-31T11:18:41.086Z</v>
+        <v>2026-08-01T10:49:42.913Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6433,7 +6433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-31T11:18:41.101Z</v>
+        <v>2026-08-01T10:49:42.928Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6453,7 +6453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-31T11:18:41.117Z</v>
+        <v>2026-08-01T10:49:42.944Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6470,10 +6470,10 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-31T11:18:41.132Z</v>
+        <v>2026-08-01T10:49:42.960Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6490,10 +6490,10 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-31T11:18:41.148Z</v>
+        <v>2026-08-01T10:49:42.975Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6510,10 +6510,10 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-31T11:18:41.163Z</v>
+        <v>2026-08-01T10:49:42.991Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6533,7 +6533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-31T11:18:41.179Z</v>
+        <v>2026-08-01T10:49:43.007Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6550,10 +6550,10 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-31T11:18:41.194Z</v>
+        <v>2026-08-01T10:49:43.023Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6570,10 +6570,10 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-31T11:18:41.209Z</v>
+        <v>2026-08-01T10:49:43.039Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6593,7 +6593,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-31T11:18:41.224Z</v>
+        <v>2026-08-01T10:49:43.055Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6613,7 +6613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-31T11:18:41.239Z</v>
+        <v>2026-08-01T10:49:43.070Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6630,10 +6630,10 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-31T11:18:41.255Z</v>
+        <v>2026-08-01T10:49:43.086Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6653,7 +6653,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-31T11:18:41.270Z</v>
+        <v>2026-08-01T10:49:43.101Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6673,7 +6673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-31T11:18:41.286Z</v>
+        <v>2026-08-01T10:49:43.117Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6693,7 +6693,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-31T11:18:41.302Z</v>
+        <v>2026-08-01T10:49:43.134Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6713,7 +6713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-31T11:18:41.317Z</v>
+        <v>2026-08-01T10:49:43.150Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6733,7 +6733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-31T11:18:41.332Z</v>
+        <v>2026-08-01T10:49:43.164Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6753,7 +6753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-31T11:18:41.348Z</v>
+        <v>2026-08-01T10:49:43.180Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -6770,10 +6770,10 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-31T11:18:41.363Z</v>
+        <v>2026-08-01T10:49:43.196Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -6790,10 +6790,10 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-31T11:18:41.379Z</v>
+        <v>2026-08-01T10:49:43.211Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -6813,7 +6813,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-31T11:18:41.394Z</v>
+        <v>2026-08-01T10:49:43.226Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -6833,7 +6833,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-31T11:18:41.410Z</v>
+        <v>2026-08-01T10:49:43.242Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -6850,10 +6850,10 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-31T11:18:41.426Z</v>
+        <v>2026-08-01T10:49:43.257Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -6870,10 +6870,10 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-31T11:18:41.441Z</v>
+        <v>2026-08-01T10:49:43.273Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -6893,7 +6893,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-31T11:18:41.456Z</v>
+        <v>2026-08-01T10:49:43.289Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -6913,7 +6913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-31T11:18:41.472Z</v>
+        <v>2026-08-01T10:49:43.305Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -6930,10 +6930,10 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-31T11:18:41.488Z</v>
+        <v>2026-08-01T10:49:43.320Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -6953,7 +6953,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-31T11:18:41.504Z</v>
+        <v>2026-08-01T10:49:43.336Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -6970,10 +6970,10 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-31T11:18:41.519Z</v>
+        <v>2026-08-01T10:49:43.352Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -6993,7 +6993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-31T11:18:41.536Z</v>
+        <v>2026-08-01T10:49:43.368Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7013,7 +7013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-31T11:18:41.551Z</v>
+        <v>2026-08-01T10:49:43.383Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7030,10 +7030,10 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-31T11:18:41.566Z</v>
+        <v>2026-08-01T10:49:43.399Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7053,7 +7053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-31T11:18:41.582Z</v>
+        <v>2026-08-01T10:49:43.414Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7070,10 +7070,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-31T11:18:41.597Z</v>
+        <v>2026-08-01T10:49:43.430Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7090,10 +7090,10 @@
         <v>PASS</v>
       </c>
       <c r="D335" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-31T11:18:41.612Z</v>
+        <v>2026-08-01T10:49:43.446Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7110,10 +7110,10 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-31T11:18:41.628Z</v>
+        <v>2026-08-01T10:49:43.462Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7133,7 +7133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-31T11:18:41.644Z</v>
+        <v>2026-08-01T10:49:43.477Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7153,7 +7153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-31T11:18:41.659Z</v>
+        <v>2026-08-01T10:49:43.492Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7173,7 +7173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-31T11:18:41.675Z</v>
+        <v>2026-08-01T10:49:43.508Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7190,10 +7190,10 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-31T11:18:41.692Z</v>
+        <v>2026-08-01T10:49:43.523Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7210,10 +7210,10 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-31T11:18:41.707Z</v>
+        <v>2026-08-01T10:49:43.539Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7233,7 +7233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-31T11:18:41.724Z</v>
+        <v>2026-08-01T10:49:43.555Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7250,10 +7250,10 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-31T11:18:41.738Z</v>
+        <v>2026-08-01T10:49:43.571Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7273,7 +7273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-31T11:18:41.754Z</v>
+        <v>2026-08-01T10:49:43.587Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7290,10 +7290,10 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-31T11:18:41.770Z</v>
+        <v>2026-08-01T10:49:43.602Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7310,10 +7310,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-31T11:18:41.785Z</v>
+        <v>2026-08-01T10:49:43.618Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7330,10 +7330,10 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-31T11:18:41.801Z</v>
+        <v>2026-08-01T10:49:43.633Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7353,7 +7353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-31T11:18:41.817Z</v>
+        <v>2026-08-01T10:49:43.649Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7373,7 +7373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-31T11:18:41.833Z</v>
+        <v>2026-08-01T10:49:43.665Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7393,7 +7393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-31T11:18:41.849Z</v>
+        <v>2026-08-01T10:49:43.681Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7410,10 +7410,10 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-31T11:18:41.865Z</v>
+        <v>2026-08-01T10:49:43.696Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7430,10 +7430,10 @@
         <v>PASS</v>
       </c>
       <c r="D352" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-31T11:18:41.880Z</v>
+        <v>2026-08-01T10:49:43.712Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7450,10 +7450,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-31T11:18:41.895Z</v>
+        <v>2026-08-01T10:49:43.728Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7470,10 +7470,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-31T11:18:41.912Z</v>
+        <v>2026-08-01T10:49:43.743Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7490,10 +7490,10 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-31T11:18:41.926Z</v>
+        <v>2026-08-01T10:49:43.759Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7510,10 +7510,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-31T11:18:41.943Z</v>
+        <v>2026-08-01T10:49:43.774Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7530,10 +7530,10 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-31T11:18:41.958Z</v>
+        <v>2026-08-01T10:49:43.790Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7553,7 +7553,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-31T11:18:41.974Z</v>
+        <v>2026-08-01T10:49:43.806Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7573,7 +7573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-31T11:18:41.989Z</v>
+        <v>2026-08-01T10:49:43.821Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7593,7 +7593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-31T11:18:42.005Z</v>
+        <v>2026-08-01T10:49:43.837Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7613,7 +7613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-31T11:18:42.020Z</v>
+        <v>2026-08-01T10:49:43.852Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7630,10 +7630,10 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-31T11:18:42.036Z</v>
+        <v>2026-08-01T10:49:43.868Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7653,7 +7653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-31T11:18:42.052Z</v>
+        <v>2026-08-01T10:49:43.884Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7670,10 +7670,10 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-31T11:18:42.068Z</v>
+        <v>2026-08-01T10:49:43.899Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7690,10 +7690,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-31T11:18:42.083Z</v>
+        <v>2026-08-01T10:49:43.915Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7710,10 +7710,10 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-31T11:18:42.098Z</v>
+        <v>2026-08-01T10:49:43.931Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7733,7 +7733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-31T11:18:42.114Z</v>
+        <v>2026-08-01T10:49:43.947Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7753,7 +7753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-31T11:18:42.128Z</v>
+        <v>2026-08-01T10:49:43.962Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -7773,7 +7773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-31T11:18:42.144Z</v>
+        <v>2026-08-01T10:49:43.977Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -7793,7 +7793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-31T11:18:42.160Z</v>
+        <v>2026-08-01T10:49:43.993Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -7810,10 +7810,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-31T11:18:42.176Z</v>
+        <v>2026-08-01T10:49:44.008Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -7830,10 +7830,10 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-31T11:18:42.192Z</v>
+        <v>2026-08-01T10:49:44.023Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -7850,10 +7850,10 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-31T11:18:42.207Z</v>
+        <v>2026-08-01T10:49:44.039Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -7873,7 +7873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-31T11:18:42.222Z</v>
+        <v>2026-08-01T10:49:44.054Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -7893,7 +7893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-31T11:18:42.238Z</v>
+        <v>2026-08-01T10:49:44.070Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -7910,10 +7910,10 @@
         <v>PASS</v>
       </c>
       <c r="D376" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-31T11:18:42.254Z</v>
+        <v>2026-08-01T10:49:44.085Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -7933,7 +7933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-31T11:18:42.270Z</v>
+        <v>2026-08-01T10:49:44.101Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -7953,7 +7953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-31T11:18:42.285Z</v>
+        <v>2026-08-01T10:49:44.116Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -7973,7 +7973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-31T11:18:42.301Z</v>
+        <v>2026-08-01T10:49:44.132Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -7993,7 +7993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-31T11:18:42.316Z</v>
+        <v>2026-08-01T10:49:44.147Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8013,7 +8013,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-31T11:18:42.332Z</v>
+        <v>2026-08-01T10:49:44.163Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8030,10 +8030,10 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-31T11:18:42.348Z</v>
+        <v>2026-08-01T10:49:44.178Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8053,7 +8053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-31T11:18:42.364Z</v>
+        <v>2026-08-01T10:49:44.194Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8070,10 +8070,10 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-31T11:18:42.379Z</v>
+        <v>2026-08-01T10:49:44.210Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8090,10 +8090,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-31T11:18:42.395Z</v>
+        <v>2026-08-01T10:49:44.225Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8110,10 +8110,10 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-31T11:18:42.411Z</v>
+        <v>2026-08-01T10:49:44.240Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8133,7 +8133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-31T11:18:42.426Z</v>
+        <v>2026-08-01T10:49:44.255Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8153,7 +8153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-31T11:18:42.442Z</v>
+        <v>2026-08-01T10:49:44.271Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8170,10 +8170,10 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-31T11:18:42.458Z</v>
+        <v>2026-08-01T10:49:44.286Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8193,7 +8193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-31T11:18:42.474Z</v>
+        <v>2026-08-01T10:49:44.302Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8210,10 +8210,10 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-31T11:18:42.489Z</v>
+        <v>2026-08-01T10:49:44.318Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8233,7 +8233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-31T11:18:42.505Z</v>
+        <v>2026-08-01T10:49:44.334Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8250,10 +8250,10 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-31T11:18:42.521Z</v>
+        <v>2026-08-01T10:49:44.348Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8270,10 +8270,10 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-31T11:18:42.537Z</v>
+        <v>2026-08-01T10:49:44.363Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8290,10 +8290,10 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-31T11:18:42.553Z</v>
+        <v>2026-08-01T10:49:44.378Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8310,10 +8310,10 @@
         <v>PASS</v>
       </c>
       <c r="D396" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-31T11:18:42.568Z</v>
+        <v>2026-08-01T10:49:44.394Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8333,7 +8333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-31T11:18:42.583Z</v>
+        <v>2026-08-01T10:49:44.409Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8353,7 +8353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-31T11:18:42.599Z</v>
+        <v>2026-08-01T10:49:44.425Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8370,10 +8370,10 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-31T11:18:42.615Z</v>
+        <v>2026-08-01T10:49:44.440Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8393,7 +8393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-31T11:18:42.631Z</v>
+        <v>2026-08-01T10:49:44.456Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8410,10 +8410,10 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-31T11:18:42.647Z</v>
+        <v>2026-08-01T10:49:44.471Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>

--- a/reports/Appium Report.xlsx
+++ b/reports/Appium Report.xlsx
@@ -433,7 +433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-01T10:49:38.258Z</v>
+        <v>2026-08-08T07:13:18.018Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -450,10 +450,10 @@
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-01T10:49:38.275Z</v>
+        <v>2026-08-08T07:13:18.023Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -473,7 +473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-01T10:49:38.290Z</v>
+        <v>2026-08-08T07:13:18.028Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-01T10:49:38.306Z</v>
+        <v>2026-08-08T07:13:18.040Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -513,7 +513,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-01T10:49:38.322Z</v>
+        <v>2026-08-08T07:13:18.059Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-01T10:49:38.338Z</v>
+        <v>2026-08-08T07:13:18.074Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,10 +550,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-01T10:49:38.353Z</v>
+        <v>2026-08-08T07:13:18.090Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -573,7 +573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-01T10:49:38.369Z</v>
+        <v>2026-08-08T07:13:18.106Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -593,7 +593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-01T10:49:38.385Z</v>
+        <v>2026-08-08T07:13:18.122Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -613,7 +613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-01T10:49:38.400Z</v>
+        <v>2026-08-08T07:13:18.137Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -633,7 +633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-01T10:49:38.415Z</v>
+        <v>2026-08-08T07:13:18.153Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -653,7 +653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-01T10:49:38.432Z</v>
+        <v>2026-08-08T07:13:18.169Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -670,10 +670,10 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-01T10:49:38.448Z</v>
+        <v>2026-08-08T07:13:18.184Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -690,10 +690,10 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-01T10:49:38.463Z</v>
+        <v>2026-08-08T07:13:18.200Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -713,7 +713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-01T10:49:38.477Z</v>
+        <v>2026-08-08T07:13:18.215Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -733,7 +733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-01T10:49:38.493Z</v>
+        <v>2026-08-08T07:13:18.231Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -750,10 +750,10 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-01T10:49:38.509Z</v>
+        <v>2026-08-08T07:13:18.246Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -770,10 +770,10 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-01T10:49:38.524Z</v>
+        <v>2026-08-08T07:13:18.262Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -790,10 +790,10 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-01T10:49:38.539Z</v>
+        <v>2026-08-08T07:13:18.278Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -813,7 +813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-01T10:49:38.555Z</v>
+        <v>2026-08-08T07:13:18.294Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -830,10 +830,10 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-01T10:49:38.570Z</v>
+        <v>2026-08-08T07:13:18.310Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -850,10 +850,10 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-01T10:49:38.586Z</v>
+        <v>2026-08-08T07:13:18.325Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -873,7 +873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-01T10:49:38.602Z</v>
+        <v>2026-08-08T07:13:18.341Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -893,7 +893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-01T10:49:38.618Z</v>
+        <v>2026-08-08T07:13:18.357Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -910,10 +910,10 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-01T10:49:38.633Z</v>
+        <v>2026-08-08T07:13:18.373Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -933,7 +933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-01T10:49:38.649Z</v>
+        <v>2026-08-08T07:13:18.389Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -953,7 +953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-01T10:49:38.664Z</v>
+        <v>2026-08-08T07:13:18.404Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -970,10 +970,10 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-01T10:49:38.679Z</v>
+        <v>2026-08-08T07:13:18.420Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -993,7 +993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-01T10:49:38.695Z</v>
+        <v>2026-08-08T07:13:18.436Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1010,10 +1010,10 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-01T10:49:38.710Z</v>
+        <v>2026-08-08T07:13:18.452Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1030,10 +1030,10 @@
         <v>PASS</v>
       </c>
       <c r="D32" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-01T10:49:38.726Z</v>
+        <v>2026-08-08T07:13:18.468Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1050,10 +1050,10 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-01T10:49:38.741Z</v>
+        <v>2026-08-08T07:13:18.484Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1073,7 +1073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-01T10:49:38.758Z</v>
+        <v>2026-08-08T07:13:18.500Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1090,10 +1090,10 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-01T10:49:38.773Z</v>
+        <v>2026-08-08T07:13:18.516Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1110,10 +1110,10 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-01T10:49:38.788Z</v>
+        <v>2026-08-08T07:13:18.532Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1130,10 +1130,10 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-01T10:49:38.804Z</v>
+        <v>2026-08-08T07:13:18.547Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1153,7 +1153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-01T10:49:38.820Z</v>
+        <v>2026-08-08T07:13:18.563Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1170,10 +1170,10 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-01T10:49:38.835Z</v>
+        <v>2026-08-08T07:13:18.579Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1193,7 +1193,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-01T10:49:38.850Z</v>
+        <v>2026-08-08T07:13:18.594Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1210,10 +1210,10 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-01T10:49:38.867Z</v>
+        <v>2026-08-08T07:13:18.609Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1230,10 +1230,10 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-01T10:49:38.883Z</v>
+        <v>2026-08-08T07:13:18.625Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1250,10 +1250,10 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-01T10:49:38.899Z</v>
+        <v>2026-08-08T07:13:18.640Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1270,10 +1270,10 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-01T10:49:38.913Z</v>
+        <v>2026-08-08T07:13:18.656Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1290,10 +1290,10 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-01T10:49:38.929Z</v>
+        <v>2026-08-08T07:13:18.671Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1313,7 +1313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-01T10:49:38.945Z</v>
+        <v>2026-08-08T07:13:18.687Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1333,7 +1333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-01T10:49:38.960Z</v>
+        <v>2026-08-08T07:13:18.702Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1353,7 +1353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-01T10:49:38.976Z</v>
+        <v>2026-08-08T07:13:18.718Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1373,7 +1373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-01T10:49:38.991Z</v>
+        <v>2026-08-08T07:13:18.733Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1393,7 +1393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-01T10:49:39.007Z</v>
+        <v>2026-08-08T07:13:18.750Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1410,10 +1410,10 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-01T10:49:39.023Z</v>
+        <v>2026-08-08T07:13:18.765Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1433,7 +1433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-01T10:49:39.038Z</v>
+        <v>2026-08-08T07:13:18.781Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1453,7 +1453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-01T10:49:39.054Z</v>
+        <v>2026-08-08T07:13:18.797Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1473,7 +1473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-01T10:49:39.070Z</v>
+        <v>2026-08-08T07:13:18.814Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1490,10 +1490,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-01T10:49:39.086Z</v>
+        <v>2026-08-08T07:13:18.828Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1510,10 +1510,10 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-01T10:49:39.101Z</v>
+        <v>2026-08-08T07:13:18.844Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1530,10 +1530,10 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-01T10:49:39.117Z</v>
+        <v>2026-08-08T07:13:18.859Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1550,10 +1550,10 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-01T10:49:39.132Z</v>
+        <v>2026-08-08T07:13:18.875Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1573,7 +1573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-01T10:49:39.147Z</v>
+        <v>2026-08-08T07:13:18.890Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1590,10 +1590,10 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-01T10:49:39.162Z</v>
+        <v>2026-08-08T07:13:18.906Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1610,10 +1610,10 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-01T10:49:39.177Z</v>
+        <v>2026-08-08T07:13:18.922Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1630,10 +1630,10 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-01T10:49:39.193Z</v>
+        <v>2026-08-08T07:13:18.938Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1650,10 +1650,10 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-01T10:49:39.209Z</v>
+        <v>2026-08-08T07:13:18.954Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1670,10 +1670,10 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-01T10:49:39.225Z</v>
+        <v>2026-08-08T07:13:18.969Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1690,10 +1690,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-01T10:49:39.240Z</v>
+        <v>2026-08-08T07:13:18.985Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1713,7 +1713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-01T10:49:39.255Z</v>
+        <v>2026-08-08T07:13:19.000Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1733,7 +1733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-01T10:49:39.271Z</v>
+        <v>2026-08-08T07:13:19.015Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1753,7 +1753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-01T10:49:39.287Z</v>
+        <v>2026-08-08T07:13:19.031Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -1773,7 +1773,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-01T10:49:39.303Z</v>
+        <v>2026-08-08T07:13:19.047Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -1790,10 +1790,10 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-01T10:49:39.318Z</v>
+        <v>2026-08-08T07:13:19.063Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -1813,7 +1813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-01T10:49:39.334Z</v>
+        <v>2026-08-08T07:13:19.079Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -1830,10 +1830,10 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-01T10:49:39.348Z</v>
+        <v>2026-08-08T07:13:19.095Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -1850,10 +1850,10 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-01T10:49:39.364Z</v>
+        <v>2026-08-08T07:13:19.110Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -1870,10 +1870,10 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-01T10:49:39.380Z</v>
+        <v>2026-08-08T07:13:19.125Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -1893,7 +1893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-01T10:49:39.396Z</v>
+        <v>2026-08-08T07:13:19.141Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -1913,7 +1913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-01T10:49:39.411Z</v>
+        <v>2026-08-08T07:13:19.156Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -1933,7 +1933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-01T10:49:39.427Z</v>
+        <v>2026-08-08T07:13:19.172Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -1950,10 +1950,10 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-01T10:49:39.443Z</v>
+        <v>2026-08-08T07:13:19.187Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -1973,7 +1973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-01T10:49:39.459Z</v>
+        <v>2026-08-08T07:13:19.203Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -1993,7 +1993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-01T10:49:39.474Z</v>
+        <v>2026-08-08T07:13:19.218Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2013,7 +2013,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-01T10:49:39.490Z</v>
+        <v>2026-08-08T07:13:19.234Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2033,7 +2033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-01T10:49:39.505Z</v>
+        <v>2026-08-08T07:13:19.249Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2053,7 +2053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-01T10:49:39.522Z</v>
+        <v>2026-08-08T07:13:19.265Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2073,7 +2073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-01T10:49:39.537Z</v>
+        <v>2026-08-08T07:13:19.280Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2090,10 +2090,10 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-01T10:49:39.552Z</v>
+        <v>2026-08-08T07:13:19.296Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2113,7 +2113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-01T10:49:39.569Z</v>
+        <v>2026-08-08T07:13:19.312Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2133,7 +2133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-01T10:49:39.583Z</v>
+        <v>2026-08-08T07:13:19.327Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2153,7 +2153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-01T10:49:39.599Z</v>
+        <v>2026-08-08T07:13:19.343Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2173,7 +2173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-01T10:49:39.614Z</v>
+        <v>2026-08-08T07:13:19.358Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2193,7 +2193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-01T10:49:39.631Z</v>
+        <v>2026-08-08T07:13:19.374Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2213,7 +2213,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-01T10:49:39.646Z</v>
+        <v>2026-08-08T07:13:19.389Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2233,7 +2233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-01T10:49:39.661Z</v>
+        <v>2026-08-08T07:13:19.405Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2253,7 +2253,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-01T10:49:39.677Z</v>
+        <v>2026-08-08T07:13:19.422Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2273,7 +2273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-01T10:49:39.693Z</v>
+        <v>2026-08-08T07:13:19.438Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2290,10 +2290,10 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-01T10:49:39.707Z</v>
+        <v>2026-08-08T07:13:19.454Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2310,10 +2310,10 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-01T10:49:39.723Z</v>
+        <v>2026-08-08T07:13:19.469Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2333,7 +2333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-01T10:49:39.738Z</v>
+        <v>2026-08-08T07:13:19.484Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2350,10 +2350,10 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-01T10:49:39.754Z</v>
+        <v>2026-08-08T07:13:19.500Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2370,10 +2370,10 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-01T10:49:39.770Z</v>
+        <v>2026-08-08T07:13:19.515Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2390,10 +2390,10 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-01T10:49:39.785Z</v>
+        <v>2026-08-08T07:13:19.531Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2413,7 +2413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-01T10:49:39.800Z</v>
+        <v>2026-08-08T07:13:19.546Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2430,10 +2430,10 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-01T10:49:39.816Z</v>
+        <v>2026-08-08T07:13:19.561Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2450,10 +2450,10 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-01T10:49:39.831Z</v>
+        <v>2026-08-08T07:13:19.577Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2473,7 +2473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-01T10:49:39.847Z</v>
+        <v>2026-08-08T07:13:19.593Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2490,10 +2490,10 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-01T10:49:39.863Z</v>
+        <v>2026-08-08T07:13:19.608Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2510,10 +2510,10 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-01T10:49:39.878Z</v>
+        <v>2026-08-08T07:13:19.624Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2533,7 +2533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-01T10:49:39.894Z</v>
+        <v>2026-08-08T07:13:19.640Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2553,7 +2553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-01T10:49:39.909Z</v>
+        <v>2026-08-08T07:13:19.655Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2573,7 +2573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-01T10:49:39.924Z</v>
+        <v>2026-08-08T07:13:19.670Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2593,7 +2593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-01T10:49:39.940Z</v>
+        <v>2026-08-08T07:13:19.686Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2613,7 +2613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-01T10:49:39.955Z</v>
+        <v>2026-08-08T07:13:19.701Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2633,7 +2633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-01T10:49:39.970Z</v>
+        <v>2026-08-08T07:13:19.717Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2650,10 +2650,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-01T10:49:39.986Z</v>
+        <v>2026-08-08T07:13:19.733Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2670,10 +2670,10 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-01T10:49:40.002Z</v>
+        <v>2026-08-08T07:13:19.748Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2693,7 +2693,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-01T10:49:40.018Z</v>
+        <v>2026-08-08T07:13:19.764Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2713,7 +2713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-01T10:49:40.034Z</v>
+        <v>2026-08-08T07:13:19.780Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2733,7 +2733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-01T10:49:40.050Z</v>
+        <v>2026-08-08T07:13:19.796Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2750,10 +2750,10 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-01T10:49:40.066Z</v>
+        <v>2026-08-08T07:13:19.812Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -2773,7 +2773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-01T10:49:40.081Z</v>
+        <v>2026-08-08T07:13:19.827Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -2790,10 +2790,10 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-01T10:49:40.097Z</v>
+        <v>2026-08-08T07:13:19.842Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -2810,10 +2810,10 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-01T10:49:40.112Z</v>
+        <v>2026-08-08T07:13:19.858Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-01T10:49:40.128Z</v>
+        <v>2026-08-08T07:13:19.873Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -2853,7 +2853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-01T10:49:40.144Z</v>
+        <v>2026-08-08T07:13:19.889Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -2870,10 +2870,10 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-01T10:49:40.159Z</v>
+        <v>2026-08-08T07:13:19.905Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -2893,7 +2893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-01T10:49:40.175Z</v>
+        <v>2026-08-08T07:13:19.921Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -2910,10 +2910,10 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-01T10:49:40.191Z</v>
+        <v>2026-08-08T07:13:19.936Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -2933,7 +2933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-01T10:49:40.206Z</v>
+        <v>2026-08-08T07:13:19.951Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -2953,7 +2953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-01T10:49:40.221Z</v>
+        <v>2026-08-08T07:13:19.967Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -2973,7 +2973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-01T10:49:40.237Z</v>
+        <v>2026-08-08T07:13:19.983Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -2990,10 +2990,10 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-01T10:49:40.252Z</v>
+        <v>2026-08-08T07:13:19.999Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3010,10 +3010,10 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-01T10:49:40.268Z</v>
+        <v>2026-08-08T07:13:20.013Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3033,7 +3033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-01T10:49:40.283Z</v>
+        <v>2026-08-08T07:13:20.029Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3050,10 +3050,10 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-01T10:49:40.299Z</v>
+        <v>2026-08-08T07:13:20.044Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3073,7 +3073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-01T10:49:40.315Z</v>
+        <v>2026-08-08T07:13:20.060Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3090,10 +3090,10 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-01T10:49:40.330Z</v>
+        <v>2026-08-08T07:13:20.077Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3113,7 +3113,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-01T10:49:40.345Z</v>
+        <v>2026-08-08T07:13:20.092Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3130,10 +3130,10 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-01T10:49:40.361Z</v>
+        <v>2026-08-08T07:13:20.107Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3153,7 +3153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-01T10:49:40.376Z</v>
+        <v>2026-08-08T07:13:20.122Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3173,7 +3173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-01T10:49:40.392Z</v>
+        <v>2026-08-08T07:13:20.138Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3190,10 +3190,10 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-01T10:49:40.409Z</v>
+        <v>2026-08-08T07:13:20.153Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3210,10 +3210,10 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-01T10:49:40.423Z</v>
+        <v>2026-08-08T07:13:20.169Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3233,7 +3233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-01T10:49:40.440Z</v>
+        <v>2026-08-08T07:13:20.185Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3253,7 +3253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-01T10:49:40.455Z</v>
+        <v>2026-08-08T07:13:20.200Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3270,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-01T10:49:40.470Z</v>
+        <v>2026-08-08T07:13:20.216Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3290,10 +3290,10 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-01T10:49:40.486Z</v>
+        <v>2026-08-08T07:13:20.231Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3313,7 +3313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-01T10:49:40.502Z</v>
+        <v>2026-08-08T07:13:20.247Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3333,7 +3333,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-01T10:49:40.518Z</v>
+        <v>2026-08-08T07:13:20.264Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3353,7 +3353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-01T10:49:40.533Z</v>
+        <v>2026-08-08T07:13:20.279Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3373,7 +3373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-01T10:49:40.548Z</v>
+        <v>2026-08-08T07:13:20.294Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3390,10 +3390,10 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-01T10:49:40.563Z</v>
+        <v>2026-08-08T07:13:20.312Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3413,7 +3413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-01T10:49:40.578Z</v>
+        <v>2026-08-08T07:13:20.326Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3433,7 +3433,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-01T10:49:40.594Z</v>
+        <v>2026-08-08T07:13:20.342Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3450,10 +3450,10 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-01T10:49:40.609Z</v>
+        <v>2026-08-08T07:13:20.358Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3470,10 +3470,10 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-01T10:49:40.626Z</v>
+        <v>2026-08-08T07:13:20.373Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3490,10 +3490,10 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-01T10:49:40.641Z</v>
+        <v>2026-08-08T07:13:20.389Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3513,7 +3513,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-01T10:49:40.657Z</v>
+        <v>2026-08-08T07:13:20.404Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3530,10 +3530,10 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-01T10:49:40.672Z</v>
+        <v>2026-08-08T07:13:20.420Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3553,7 +3553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-01T10:49:40.688Z</v>
+        <v>2026-08-08T07:13:20.435Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3573,7 +3573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-01T10:49:40.703Z</v>
+        <v>2026-08-08T07:13:20.450Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3590,10 +3590,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-01T10:49:40.718Z</v>
+        <v>2026-08-08T07:13:20.466Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3613,7 +3613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-01T10:49:40.734Z</v>
+        <v>2026-08-08T07:13:20.482Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3630,10 +3630,10 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-01T10:49:40.749Z</v>
+        <v>2026-08-08T07:13:20.498Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3650,10 +3650,10 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-01T10:49:40.765Z</v>
+        <v>2026-08-08T07:13:20.512Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3673,7 +3673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-01T10:49:40.781Z</v>
+        <v>2026-08-08T07:13:20.529Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3693,7 +3693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-01T10:49:40.796Z</v>
+        <v>2026-08-08T07:13:20.543Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3713,7 +3713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-01T10:49:40.812Z</v>
+        <v>2026-08-08T07:13:20.559Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3730,10 +3730,10 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-01T10:49:40.828Z</v>
+        <v>2026-08-08T07:13:20.574Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3753,7 +3753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-01T10:49:40.843Z</v>
+        <v>2026-08-08T07:13:20.589Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -3770,10 +3770,10 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-01T10:49:40.858Z</v>
+        <v>2026-08-08T07:13:20.605Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -3793,7 +3793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-01T10:49:40.874Z</v>
+        <v>2026-08-08T07:13:20.621Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -3813,7 +3813,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-01T10:49:40.889Z</v>
+        <v>2026-08-08T07:13:20.636Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -3833,7 +3833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-01T10:49:40.904Z</v>
+        <v>2026-08-08T07:13:20.651Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -3853,7 +3853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-01T10:49:40.921Z</v>
+        <v>2026-08-08T07:13:20.667Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -3870,10 +3870,10 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-01T10:49:40.936Z</v>
+        <v>2026-08-08T07:13:20.683Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -3893,7 +3893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-01T10:49:40.952Z</v>
+        <v>2026-08-08T07:13:20.699Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -3913,7 +3913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-01T10:49:40.967Z</v>
+        <v>2026-08-08T07:13:20.714Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -3930,10 +3930,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-01T10:49:40.983Z</v>
+        <v>2026-08-08T07:13:20.729Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -3950,10 +3950,10 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-01T10:49:40.998Z</v>
+        <v>2026-08-08T07:13:20.745Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -3973,7 +3973,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-01T10:49:41.013Z</v>
+        <v>2026-08-08T07:13:20.760Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -3993,7 +3993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-01T10:49:41.029Z</v>
+        <v>2026-08-08T07:13:20.776Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4013,7 +4013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-01T10:49:41.044Z</v>
+        <v>2026-08-08T07:13:20.791Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4033,7 +4033,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-01T10:49:41.060Z</v>
+        <v>2026-08-08T07:13:20.808Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4050,10 +4050,10 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-01T10:49:41.075Z</v>
+        <v>2026-08-08T07:13:20.824Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4073,7 +4073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-01T10:49:41.091Z</v>
+        <v>2026-08-08T07:13:20.840Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4093,7 +4093,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-01T10:49:41.106Z</v>
+        <v>2026-08-08T07:13:20.855Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4113,7 +4113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-01T10:49:41.122Z</v>
+        <v>2026-08-08T07:13:20.871Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4130,10 +4130,10 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-01T10:49:41.138Z</v>
+        <v>2026-08-08T07:13:20.886Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4153,7 +4153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-01T10:49:41.154Z</v>
+        <v>2026-08-08T07:13:20.903Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4170,10 +4170,10 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-01T10:49:41.170Z</v>
+        <v>2026-08-08T07:13:20.918Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4193,7 +4193,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-01T10:49:41.185Z</v>
+        <v>2026-08-08T07:13:20.933Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4210,10 +4210,10 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-01T10:49:41.201Z</v>
+        <v>2026-08-08T07:13:20.949Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4233,7 +4233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-01T10:49:41.217Z</v>
+        <v>2026-08-08T07:13:20.965Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4250,10 +4250,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-01T10:49:41.232Z</v>
+        <v>2026-08-08T07:13:20.981Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4270,10 +4270,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-01T10:49:41.248Z</v>
+        <v>2026-08-08T07:13:20.996Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4290,10 +4290,10 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-01T10:49:41.264Z</v>
+        <v>2026-08-08T07:13:21.011Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4310,10 +4310,10 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-01T10:49:41.280Z</v>
+        <v>2026-08-08T07:13:21.027Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4330,10 +4330,10 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-01T10:49:41.295Z</v>
+        <v>2026-08-08T07:13:21.043Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4353,7 +4353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-01T10:49:41.310Z</v>
+        <v>2026-08-08T07:13:21.058Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4373,7 +4373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-01T10:49:41.326Z</v>
+        <v>2026-08-08T07:13:21.075Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4393,7 +4393,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-01T10:49:41.341Z</v>
+        <v>2026-08-08T07:13:21.090Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4413,7 +4413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-01T10:49:41.356Z</v>
+        <v>2026-08-08T07:13:21.105Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4433,7 +4433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-01T10:49:41.372Z</v>
+        <v>2026-08-08T07:13:21.120Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4453,7 +4453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-01T10:49:41.388Z</v>
+        <v>2026-08-08T07:13:21.136Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4473,7 +4473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-01T10:49:41.403Z</v>
+        <v>2026-08-08T07:13:21.151Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4493,7 +4493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-01T10:49:41.419Z</v>
+        <v>2026-08-08T07:13:21.167Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4510,10 +4510,10 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-01T10:49:41.435Z</v>
+        <v>2026-08-08T07:13:21.182Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4533,7 +4533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-01T10:49:41.451Z</v>
+        <v>2026-08-08T07:13:21.198Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4553,7 +4553,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-01T10:49:41.467Z</v>
+        <v>2026-08-08T07:13:21.215Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4573,7 +4573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-01T10:49:41.483Z</v>
+        <v>2026-08-08T07:13:21.233Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4590,10 +4590,10 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-01T10:49:41.499Z</v>
+        <v>2026-08-08T07:13:21.248Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4613,7 +4613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-01T10:49:41.513Z</v>
+        <v>2026-08-08T07:13:21.263Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4630,10 +4630,10 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-01T10:49:41.529Z</v>
+        <v>2026-08-08T07:13:21.278Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4653,7 +4653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-01T10:49:41.545Z</v>
+        <v>2026-08-08T07:13:21.294Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4673,7 +4673,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-01T10:49:41.560Z</v>
+        <v>2026-08-08T07:13:21.309Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4690,10 +4690,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-01T10:49:41.575Z</v>
+        <v>2026-08-08T07:13:21.325Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4713,7 +4713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-01T10:49:41.592Z</v>
+        <v>2026-08-08T07:13:21.341Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4730,10 +4730,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-01T10:49:41.607Z</v>
+        <v>2026-08-08T07:13:21.357Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4753,7 +4753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-01T10:49:41.623Z</v>
+        <v>2026-08-08T07:13:21.373Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -4773,7 +4773,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-01T10:49:41.639Z</v>
+        <v>2026-08-08T07:13:21.389Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -4793,7 +4793,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-01T10:49:41.654Z</v>
+        <v>2026-08-08T07:13:21.404Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -4813,7 +4813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-01T10:49:41.670Z</v>
+        <v>2026-08-08T07:13:21.420Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -4830,10 +4830,10 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-01T10:49:41.685Z</v>
+        <v>2026-08-08T07:13:21.436Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -4853,7 +4853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-01T10:49:41.701Z</v>
+        <v>2026-08-08T07:13:21.452Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -4870,10 +4870,10 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-01T10:49:41.717Z</v>
+        <v>2026-08-08T07:13:21.467Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -4890,10 +4890,10 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-01T10:49:41.733Z</v>
+        <v>2026-08-08T07:13:21.482Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -4913,7 +4913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-01T10:49:41.749Z</v>
+        <v>2026-08-08T07:13:21.498Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -4930,10 +4930,10 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-01T10:49:41.765Z</v>
+        <v>2026-08-08T07:13:21.513Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -4953,7 +4953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-01T10:49:41.779Z</v>
+        <v>2026-08-08T07:13:21.528Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -4970,10 +4970,10 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-01T10:49:41.794Z</v>
+        <v>2026-08-08T07:13:21.544Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -4993,7 +4993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-01T10:49:41.809Z</v>
+        <v>2026-08-08T07:13:21.559Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5013,7 +5013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-01T10:49:41.825Z</v>
+        <v>2026-08-08T07:13:21.574Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5033,7 +5033,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-01T10:49:41.841Z</v>
+        <v>2026-08-08T07:13:21.590Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5053,7 +5053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-01T10:49:41.855Z</v>
+        <v>2026-08-08T07:13:21.605Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5070,10 +5070,10 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-01T10:49:41.872Z</v>
+        <v>2026-08-08T07:13:21.620Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5093,7 +5093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-01T10:49:41.888Z</v>
+        <v>2026-08-08T07:13:21.636Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5110,10 +5110,10 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-01T10:49:41.903Z</v>
+        <v>2026-08-08T07:13:21.652Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5133,7 +5133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-01T10:49:41.919Z</v>
+        <v>2026-08-08T07:13:21.668Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5153,7 +5153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-01T10:49:41.935Z</v>
+        <v>2026-08-08T07:13:21.685Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5173,7 +5173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-01T10:49:41.950Z</v>
+        <v>2026-08-08T07:13:21.700Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5193,7 +5193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-01T10:49:41.966Z</v>
+        <v>2026-08-08T07:13:21.716Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5213,7 +5213,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-01T10:49:41.982Z</v>
+        <v>2026-08-08T07:13:21.732Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5230,10 +5230,10 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-01T10:49:41.997Z</v>
+        <v>2026-08-08T07:13:21.748Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5253,7 +5253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-01T10:49:42.012Z</v>
+        <v>2026-08-08T07:13:21.763Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5270,10 +5270,10 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-01T10:49:42.028Z</v>
+        <v>2026-08-08T07:13:21.778Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5293,7 +5293,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-01T10:49:42.044Z</v>
+        <v>2026-08-08T07:13:21.795Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5313,7 +5313,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-01T10:49:42.059Z</v>
+        <v>2026-08-08T07:13:21.810Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5330,10 +5330,10 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-01T10:49:42.075Z</v>
+        <v>2026-08-08T07:13:21.825Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5350,10 +5350,10 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-01T10:49:42.090Z</v>
+        <v>2026-08-08T07:13:21.842Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5373,7 +5373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-01T10:49:42.105Z</v>
+        <v>2026-08-08T07:13:21.856Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5393,7 +5393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-01T10:49:42.121Z</v>
+        <v>2026-08-08T07:13:21.873Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5410,10 +5410,10 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-01T10:49:42.136Z</v>
+        <v>2026-08-08T07:13:21.889Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5430,10 +5430,10 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-01T10:49:42.152Z</v>
+        <v>2026-08-08T07:13:21.905Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5453,7 +5453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-01T10:49:42.167Z</v>
+        <v>2026-08-08T07:13:21.920Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5473,7 +5473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-01T10:49:42.183Z</v>
+        <v>2026-08-08T07:13:21.936Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5493,7 +5493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-01T10:49:42.199Z</v>
+        <v>2026-08-08T07:13:21.952Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5513,7 +5513,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-01T10:49:42.214Z</v>
+        <v>2026-08-08T07:13:21.967Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5533,7 +5533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-01T10:49:42.230Z</v>
+        <v>2026-08-08T07:13:21.984Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5550,10 +5550,10 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-01T10:49:42.246Z</v>
+        <v>2026-08-08T07:13:21.999Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5570,10 +5570,10 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-01T10:49:42.262Z</v>
+        <v>2026-08-08T07:13:22.014Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5593,7 +5593,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-01T10:49:42.277Z</v>
+        <v>2026-08-08T07:13:22.029Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5613,7 +5613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-01T10:49:42.293Z</v>
+        <v>2026-08-08T07:13:22.045Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5633,7 +5633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-01T10:49:42.308Z</v>
+        <v>2026-08-08T07:13:22.061Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5653,7 +5653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-01T10:49:42.324Z</v>
+        <v>2026-08-08T07:13:22.077Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5673,7 +5673,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-01T10:49:42.339Z</v>
+        <v>2026-08-08T07:13:22.092Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5693,7 +5693,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-01T10:49:42.355Z</v>
+        <v>2026-08-08T07:13:22.108Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5710,10 +5710,10 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-01T10:49:42.372Z</v>
+        <v>2026-08-08T07:13:22.123Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5733,7 +5733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-01T10:49:42.386Z</v>
+        <v>2026-08-08T07:13:22.138Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5753,7 +5753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-01T10:49:42.402Z</v>
+        <v>2026-08-08T07:13:22.154Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -5773,7 +5773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-01T10:49:42.417Z</v>
+        <v>2026-08-08T07:13:22.169Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -5793,7 +5793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-01T10:49:42.433Z</v>
+        <v>2026-08-08T07:13:22.185Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -5810,10 +5810,10 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-01T10:49:42.449Z</v>
+        <v>2026-08-08T07:13:22.200Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -5833,7 +5833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-01T10:49:42.464Z</v>
+        <v>2026-08-08T07:13:22.216Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -5850,10 +5850,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-01T10:49:42.480Z</v>
+        <v>2026-08-08T07:13:22.231Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -5873,7 +5873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-01T10:49:42.495Z</v>
+        <v>2026-08-08T07:13:22.247Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -5890,10 +5890,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-01T10:49:42.511Z</v>
+        <v>2026-08-08T07:13:22.262Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -5910,10 +5910,10 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-01T10:49:42.525Z</v>
+        <v>2026-08-08T07:13:22.278Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -5933,7 +5933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-01T10:49:42.540Z</v>
+        <v>2026-08-08T07:13:22.294Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -5953,7 +5953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-01T10:49:42.555Z</v>
+        <v>2026-08-08T07:13:22.309Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -5970,10 +5970,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-01T10:49:42.571Z</v>
+        <v>2026-08-08T07:13:22.325Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -5990,10 +5990,10 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-01T10:49:42.587Z</v>
+        <v>2026-08-08T07:13:22.341Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6010,10 +6010,10 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-01T10:49:42.603Z</v>
+        <v>2026-08-08T07:13:22.356Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6033,7 +6033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-01T10:49:42.618Z</v>
+        <v>2026-08-08T07:13:22.371Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6050,10 +6050,10 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-01T10:49:42.633Z</v>
+        <v>2026-08-08T07:13:22.387Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6073,7 +6073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-01T10:49:42.649Z</v>
+        <v>2026-08-08T07:13:22.403Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6090,10 +6090,10 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-01T10:49:42.664Z</v>
+        <v>2026-08-08T07:13:22.419Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6113,7 +6113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-01T10:49:42.680Z</v>
+        <v>2026-08-08T07:13:22.435Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6130,10 +6130,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-01T10:49:42.696Z</v>
+        <v>2026-08-08T07:13:22.450Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6150,10 +6150,10 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-01T10:49:42.711Z</v>
+        <v>2026-08-08T07:13:22.466Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6173,7 +6173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-01T10:49:42.727Z</v>
+        <v>2026-08-08T07:13:22.482Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6193,7 +6193,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-01T10:49:42.742Z</v>
+        <v>2026-08-08T07:13:22.497Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6210,10 +6210,10 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-01T10:49:42.758Z</v>
+        <v>2026-08-08T07:13:22.513Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6233,7 +6233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-01T10:49:42.774Z</v>
+        <v>2026-08-08T07:13:22.528Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6250,10 +6250,10 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-01T10:49:42.789Z</v>
+        <v>2026-08-08T07:13:22.544Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6273,7 +6273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-01T10:49:42.805Z</v>
+        <v>2026-08-08T07:13:22.560Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6293,7 +6293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-01T10:49:42.820Z</v>
+        <v>2026-08-08T07:13:22.575Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6310,10 +6310,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-01T10:49:42.835Z</v>
+        <v>2026-08-08T07:13:22.591Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6330,10 +6330,10 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-01T10:49:42.851Z</v>
+        <v>2026-08-08T07:13:22.606Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6353,7 +6353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-01T10:49:42.867Z</v>
+        <v>2026-08-08T07:13:22.622Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6370,10 +6370,10 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-01T10:49:42.883Z</v>
+        <v>2026-08-08T07:13:22.637Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6390,10 +6390,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-01T10:49:42.898Z</v>
+        <v>2026-08-08T07:13:22.654Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6413,7 +6413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-01T10:49:42.913Z</v>
+        <v>2026-08-08T07:13:22.669Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6433,7 +6433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-01T10:49:42.928Z</v>
+        <v>2026-08-08T07:13:22.684Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6453,7 +6453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-01T10:49:42.944Z</v>
+        <v>2026-08-08T07:13:22.700Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6470,10 +6470,10 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-01T10:49:42.960Z</v>
+        <v>2026-08-08T07:13:22.715Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6490,10 +6490,10 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-01T10:49:42.975Z</v>
+        <v>2026-08-08T07:13:22.732Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6510,10 +6510,10 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-01T10:49:42.991Z</v>
+        <v>2026-08-08T07:13:22.747Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6533,7 +6533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-01T10:49:43.007Z</v>
+        <v>2026-08-08T07:13:22.763Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6550,10 +6550,10 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-01T10:49:43.023Z</v>
+        <v>2026-08-08T07:13:22.778Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6573,7 +6573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-01T10:49:43.039Z</v>
+        <v>2026-08-08T07:13:22.794Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6593,7 +6593,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-01T10:49:43.055Z</v>
+        <v>2026-08-08T07:13:22.809Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6610,10 +6610,10 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-01T10:49:43.070Z</v>
+        <v>2026-08-08T07:13:22.825Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6630,10 +6630,10 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-01T10:49:43.086Z</v>
+        <v>2026-08-08T07:13:22.840Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6653,7 +6653,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-01T10:49:43.101Z</v>
+        <v>2026-08-08T07:13:22.855Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6673,7 +6673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-01T10:49:43.117Z</v>
+        <v>2026-08-08T07:13:22.872Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6690,10 +6690,10 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-01T10:49:43.134Z</v>
+        <v>2026-08-08T07:13:22.887Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6710,10 +6710,10 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-01T10:49:43.150Z</v>
+        <v>2026-08-08T07:13:22.903Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6730,10 +6730,10 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-01T10:49:43.164Z</v>
+        <v>2026-08-08T07:13:22.919Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6753,7 +6753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-01T10:49:43.180Z</v>
+        <v>2026-08-08T07:13:22.935Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -6770,10 +6770,10 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-01T10:49:43.196Z</v>
+        <v>2026-08-08T07:13:22.950Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -6790,10 +6790,10 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-01T10:49:43.211Z</v>
+        <v>2026-08-08T07:13:22.966Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -6813,7 +6813,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-01T10:49:43.226Z</v>
+        <v>2026-08-08T07:13:22.981Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -6830,10 +6830,10 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-01T10:49:43.242Z</v>
+        <v>2026-08-08T07:13:22.997Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -6850,10 +6850,10 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-01T10:49:43.257Z</v>
+        <v>2026-08-08T07:13:23.013Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -6870,10 +6870,10 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-01T10:49:43.273Z</v>
+        <v>2026-08-08T07:13:23.028Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -6890,10 +6890,10 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-01T10:49:43.289Z</v>
+        <v>2026-08-08T07:13:23.044Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -6913,7 +6913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-01T10:49:43.305Z</v>
+        <v>2026-08-08T07:13:23.060Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -6933,7 +6933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-01T10:49:43.320Z</v>
+        <v>2026-08-08T07:13:23.075Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -6950,10 +6950,10 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-01T10:49:43.336Z</v>
+        <v>2026-08-08T07:13:23.090Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -6973,7 +6973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-01T10:49:43.352Z</v>
+        <v>2026-08-08T07:13:23.106Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -6990,10 +6990,10 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-01T10:49:43.368Z</v>
+        <v>2026-08-08T07:13:23.121Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7013,7 +7013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-01T10:49:43.383Z</v>
+        <v>2026-08-08T07:13:23.136Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7030,10 +7030,10 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-01T10:49:43.399Z</v>
+        <v>2026-08-08T07:13:23.152Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7050,10 +7050,10 @@
         <v>PASS</v>
       </c>
       <c r="D333" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-01T10:49:43.414Z</v>
+        <v>2026-08-08T07:13:23.168Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7070,10 +7070,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-01T10:49:43.430Z</v>
+        <v>2026-08-08T07:13:23.183Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7093,7 +7093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-01T10:49:43.446Z</v>
+        <v>2026-08-08T07:13:23.199Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7110,10 +7110,10 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-01T10:49:43.462Z</v>
+        <v>2026-08-08T07:13:23.214Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7130,10 +7130,10 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-01T10:49:43.477Z</v>
+        <v>2026-08-08T07:13:23.230Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7150,10 +7150,10 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-01T10:49:43.492Z</v>
+        <v>2026-08-08T07:13:23.247Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7173,7 +7173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-01T10:49:43.508Z</v>
+        <v>2026-08-08T07:13:23.265Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7193,7 +7193,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-01T10:49:43.523Z</v>
+        <v>2026-08-08T07:13:23.278Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7210,10 +7210,10 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-01T10:49:43.539Z</v>
+        <v>2026-08-08T07:13:23.293Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7230,10 +7230,10 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-01T10:49:43.555Z</v>
+        <v>2026-08-08T07:13:23.308Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7253,7 +7253,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-01T10:49:43.571Z</v>
+        <v>2026-08-08T07:13:23.324Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7273,7 +7273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-01T10:49:43.587Z</v>
+        <v>2026-08-08T07:13:23.343Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7293,7 +7293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-01T10:49:43.602Z</v>
+        <v>2026-08-08T07:13:23.356Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7310,10 +7310,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-01T10:49:43.618Z</v>
+        <v>2026-08-08T07:13:23.371Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7330,10 +7330,10 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-01T10:49:43.633Z</v>
+        <v>2026-08-08T07:13:23.387Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7350,10 +7350,10 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-01T10:49:43.649Z</v>
+        <v>2026-08-08T07:13:23.401Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7373,7 +7373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-01T10:49:43.665Z</v>
+        <v>2026-08-08T07:13:23.418Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7393,7 +7393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-01T10:49:43.681Z</v>
+        <v>2026-08-08T07:13:23.434Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7413,7 +7413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-01T10:49:43.696Z</v>
+        <v>2026-08-08T07:13:23.449Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7433,7 +7433,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-01T10:49:43.712Z</v>
+        <v>2026-08-08T07:13:23.465Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7450,10 +7450,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-01T10:49:43.728Z</v>
+        <v>2026-08-08T07:13:23.479Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7470,10 +7470,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-01T10:49:43.743Z</v>
+        <v>2026-08-08T07:13:23.495Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7493,7 +7493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-01T10:49:43.759Z</v>
+        <v>2026-08-08T07:13:23.511Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7510,10 +7510,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-01T10:49:43.774Z</v>
+        <v>2026-08-08T07:13:23.527Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7533,7 +7533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-01T10:49:43.790Z</v>
+        <v>2026-08-08T07:13:23.543Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7550,10 +7550,10 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-01T10:49:43.806Z</v>
+        <v>2026-08-08T07:13:23.558Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7573,7 +7573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-01T10:49:43.821Z</v>
+        <v>2026-08-08T07:13:23.573Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7593,7 +7593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-01T10:49:43.837Z</v>
+        <v>2026-08-08T07:13:23.589Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7610,10 +7610,10 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-01T10:49:43.852Z</v>
+        <v>2026-08-08T07:13:23.605Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7633,7 +7633,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-01T10:49:43.868Z</v>
+        <v>2026-08-08T07:13:23.621Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7653,7 +7653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-01T10:49:43.884Z</v>
+        <v>2026-08-08T07:13:23.637Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7673,7 +7673,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-01T10:49:43.899Z</v>
+        <v>2026-08-08T07:13:23.652Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7690,10 +7690,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-01T10:49:43.915Z</v>
+        <v>2026-08-08T07:13:23.667Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7710,10 +7710,10 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-01T10:49:43.931Z</v>
+        <v>2026-08-08T07:13:23.682Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7733,7 +7733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-01T10:49:43.947Z</v>
+        <v>2026-08-08T07:13:23.698Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7750,10 +7750,10 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-01T10:49:43.962Z</v>
+        <v>2026-08-08T07:13:23.714Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -7773,7 +7773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-01T10:49:43.977Z</v>
+        <v>2026-08-08T07:13:23.729Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -7793,7 +7793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-01T10:49:43.993Z</v>
+        <v>2026-08-08T07:13:23.746Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -7810,10 +7810,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-01T10:49:44.008Z</v>
+        <v>2026-08-08T07:13:23.763Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -7833,7 +7833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-01T10:49:44.023Z</v>
+        <v>2026-08-08T07:13:23.777Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -7853,7 +7853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-01T10:49:44.039Z</v>
+        <v>2026-08-08T07:13:23.793Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -7870,10 +7870,10 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-01T10:49:44.054Z</v>
+        <v>2026-08-08T07:13:23.809Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -7890,10 +7890,10 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-01T10:49:44.070Z</v>
+        <v>2026-08-08T07:13:23.824Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -7913,7 +7913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-01T10:49:44.085Z</v>
+        <v>2026-08-08T07:13:23.839Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -7930,10 +7930,10 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-01T10:49:44.101Z</v>
+        <v>2026-08-08T07:13:23.854Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -7953,7 +7953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-01T10:49:44.116Z</v>
+        <v>2026-08-08T07:13:23.870Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -7973,7 +7973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-01T10:49:44.132Z</v>
+        <v>2026-08-08T07:13:23.886Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -7993,7 +7993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-01T10:49:44.147Z</v>
+        <v>2026-08-08T07:13:23.900Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8010,10 +8010,10 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-01T10:49:44.163Z</v>
+        <v>2026-08-08T07:13:23.915Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8030,10 +8030,10 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-01T10:49:44.178Z</v>
+        <v>2026-08-08T07:13:23.932Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8050,10 +8050,10 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-01T10:49:44.194Z</v>
+        <v>2026-08-08T07:13:23.947Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8070,10 +8070,10 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-01T10:49:44.210Z</v>
+        <v>2026-08-08T07:13:23.963Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8090,10 +8090,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-01T10:49:44.225Z</v>
+        <v>2026-08-08T07:13:23.979Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8110,10 +8110,10 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-01T10:49:44.240Z</v>
+        <v>2026-08-08T07:13:23.995Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8130,10 +8130,10 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-01T10:49:44.255Z</v>
+        <v>2026-08-08T07:13:24.011Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8150,10 +8150,10 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-01T10:49:44.271Z</v>
+        <v>2026-08-08T07:13:24.026Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8170,10 +8170,10 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-01T10:49:44.286Z</v>
+        <v>2026-08-08T07:13:24.043Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8190,10 +8190,10 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-01T10:49:44.302Z</v>
+        <v>2026-08-08T07:13:24.059Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8210,10 +8210,10 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-01T10:49:44.318Z</v>
+        <v>2026-08-08T07:13:24.073Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8233,7 +8233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-01T10:49:44.334Z</v>
+        <v>2026-08-08T07:13:24.089Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8253,7 +8253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-01T10:49:44.348Z</v>
+        <v>2026-08-08T07:13:24.104Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8270,10 +8270,10 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-01T10:49:44.363Z</v>
+        <v>2026-08-08T07:13:24.120Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8293,7 +8293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-01T10:49:44.378Z</v>
+        <v>2026-08-08T07:13:24.135Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8313,7 +8313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-01T10:49:44.394Z</v>
+        <v>2026-08-08T07:13:24.151Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8333,7 +8333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-01T10:49:44.409Z</v>
+        <v>2026-08-08T07:13:24.166Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8353,7 +8353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-01T10:49:44.425Z</v>
+        <v>2026-08-08T07:13:24.182Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8373,7 +8373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-01T10:49:44.440Z</v>
+        <v>2026-08-08T07:13:24.197Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8393,7 +8393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-01T10:49:44.456Z</v>
+        <v>2026-08-08T07:13:24.214Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8413,7 +8413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-01T10:49:44.471Z</v>
+        <v>2026-08-08T07:13:24.229Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>

--- a/reports/Appium Report.xlsx
+++ b/reports/Appium Report.xlsx
@@ -433,7 +433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-08T07:13:18.018Z</v>
+        <v>2026-08-09T18:19:35.426Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -453,7 +453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-08T07:13:18.023Z</v>
+        <v>2026-08-09T18:19:35.432Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -473,7 +473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-08T07:13:18.028Z</v>
+        <v>2026-08-09T18:19:35.446Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-08T07:13:18.040Z</v>
+        <v>2026-08-09T18:19:35.462Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-08T07:13:18.059Z</v>
+        <v>2026-08-09T18:19:35.477Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -533,7 +533,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-08T07:13:18.074Z</v>
+        <v>2026-08-09T18:19:35.492Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -553,7 +553,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-08T07:13:18.090Z</v>
+        <v>2026-08-09T18:19:35.508Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -573,7 +573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-08T07:13:18.106Z</v>
+        <v>2026-08-09T18:19:35.524Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -590,10 +590,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-08T07:13:18.122Z</v>
+        <v>2026-08-09T18:19:35.539Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -613,7 +613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-08T07:13:18.137Z</v>
+        <v>2026-08-09T18:19:35.554Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -633,7 +633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-08T07:13:18.153Z</v>
+        <v>2026-08-09T18:19:35.570Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -650,10 +650,10 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-08T07:13:18.169Z</v>
+        <v>2026-08-09T18:19:35.586Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -670,10 +670,10 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-08T07:13:18.184Z</v>
+        <v>2026-08-09T18:19:35.602Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -690,10 +690,10 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-08T07:13:18.200Z</v>
+        <v>2026-08-09T18:19:35.617Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -710,10 +710,10 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-08T07:13:18.215Z</v>
+        <v>2026-08-09T18:19:35.633Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -730,10 +730,10 @@
         <v>PASS</v>
       </c>
       <c r="D17" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-08T07:13:18.231Z</v>
+        <v>2026-08-09T18:19:35.648Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -753,7 +753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-08T07:13:18.246Z</v>
+        <v>2026-08-09T18:19:35.663Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -773,7 +773,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-08T07:13:18.262Z</v>
+        <v>2026-08-09T18:19:35.681Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -790,10 +790,10 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-08T07:13:18.278Z</v>
+        <v>2026-08-09T18:19:35.695Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -810,10 +810,10 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-08T07:13:18.294Z</v>
+        <v>2026-08-09T18:19:35.710Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -830,10 +830,10 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-08T07:13:18.310Z</v>
+        <v>2026-08-09T18:19:35.726Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -853,7 +853,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-08T07:13:18.325Z</v>
+        <v>2026-08-09T18:19:35.741Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -870,10 +870,10 @@
         <v>PASS</v>
       </c>
       <c r="D24" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-08T07:13:18.341Z</v>
+        <v>2026-08-09T18:19:35.756Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -893,7 +893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-08T07:13:18.357Z</v>
+        <v>2026-08-09T18:19:35.773Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -910,10 +910,10 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-08T07:13:18.373Z</v>
+        <v>2026-08-09T18:19:35.788Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -933,7 +933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-08T07:13:18.389Z</v>
+        <v>2026-08-09T18:19:35.804Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -950,10 +950,10 @@
         <v>PASS</v>
       </c>
       <c r="D28" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-08T07:13:18.404Z</v>
+        <v>2026-08-09T18:19:35.820Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -970,10 +970,10 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-08T07:13:18.420Z</v>
+        <v>2026-08-09T18:19:35.835Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -993,7 +993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-08T07:13:18.436Z</v>
+        <v>2026-08-09T18:19:35.851Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1013,7 +1013,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-08T07:13:18.452Z</v>
+        <v>2026-08-09T18:19:35.867Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1033,7 +1033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-08T07:13:18.468Z</v>
+        <v>2026-08-09T18:19:35.882Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1050,10 +1050,10 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-08T07:13:18.484Z</v>
+        <v>2026-08-09T18:19:35.897Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1070,10 +1070,10 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-08T07:13:18.500Z</v>
+        <v>2026-08-09T18:19:35.912Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1090,10 +1090,10 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-08T07:13:18.516Z</v>
+        <v>2026-08-09T18:19:35.927Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1110,10 +1110,10 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-08T07:13:18.532Z</v>
+        <v>2026-08-09T18:19:35.942Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1133,7 +1133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-08T07:13:18.547Z</v>
+        <v>2026-08-09T18:19:35.957Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1150,10 +1150,10 @@
         <v>PASS</v>
       </c>
       <c r="D38" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-08T07:13:18.563Z</v>
+        <v>2026-08-09T18:19:35.972Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1170,10 +1170,10 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-08T07:13:18.579Z</v>
+        <v>2026-08-09T18:19:35.987Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1190,10 +1190,10 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-08T07:13:18.594Z</v>
+        <v>2026-08-09T18:19:36.003Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1210,10 +1210,10 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-08T07:13:18.609Z</v>
+        <v>2026-08-09T18:19:36.019Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1233,7 +1233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-08T07:13:18.625Z</v>
+        <v>2026-08-09T18:19:36.034Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1253,7 +1253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-08T07:13:18.640Z</v>
+        <v>2026-08-09T18:19:36.049Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1273,7 +1273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-08T07:13:18.656Z</v>
+        <v>2026-08-09T18:19:36.065Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1290,10 +1290,10 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-08T07:13:18.671Z</v>
+        <v>2026-08-09T18:19:36.081Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1313,7 +1313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-08T07:13:18.687Z</v>
+        <v>2026-08-09T18:19:36.097Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1333,7 +1333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-08T07:13:18.702Z</v>
+        <v>2026-08-09T18:19:36.112Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1353,7 +1353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-08T07:13:18.718Z</v>
+        <v>2026-08-09T18:19:36.128Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1370,10 +1370,10 @@
         <v>PASS</v>
       </c>
       <c r="D49" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-08T07:13:18.733Z</v>
+        <v>2026-08-09T18:19:36.144Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1393,7 +1393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-08T07:13:18.750Z</v>
+        <v>2026-08-09T18:19:36.160Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1413,7 +1413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-08T07:13:18.765Z</v>
+        <v>2026-08-09T18:19:36.176Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1433,7 +1433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-08T07:13:18.781Z</v>
+        <v>2026-08-09T18:19:36.190Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1450,10 +1450,10 @@
         <v>PASS</v>
       </c>
       <c r="D53" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-08T07:13:18.797Z</v>
+        <v>2026-08-09T18:19:36.205Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1473,7 +1473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-08T07:13:18.814Z</v>
+        <v>2026-08-09T18:19:36.221Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1490,10 +1490,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-08T07:13:18.828Z</v>
+        <v>2026-08-09T18:19:36.237Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1513,7 +1513,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-08T07:13:18.844Z</v>
+        <v>2026-08-09T18:19:36.253Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1530,10 +1530,10 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-08T07:13:18.859Z</v>
+        <v>2026-08-09T18:19:36.269Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1553,7 +1553,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-08T07:13:18.875Z</v>
+        <v>2026-08-09T18:19:36.285Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1570,10 +1570,10 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-08T07:13:18.890Z</v>
+        <v>2026-08-09T18:19:36.301Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1593,7 +1593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-08T07:13:18.906Z</v>
+        <v>2026-08-09T18:19:36.317Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1613,7 +1613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-08T07:13:18.922Z</v>
+        <v>2026-08-09T18:19:36.333Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1630,10 +1630,10 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-08T07:13:18.938Z</v>
+        <v>2026-08-09T18:19:36.347Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1653,7 +1653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-08T07:13:18.954Z</v>
+        <v>2026-08-09T18:19:36.364Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1673,7 +1673,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-08T07:13:18.969Z</v>
+        <v>2026-08-09T18:19:36.379Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1690,10 +1690,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-08T07:13:18.985Z</v>
+        <v>2026-08-09T18:19:36.394Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1710,10 +1710,10 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-08T07:13:19.000Z</v>
+        <v>2026-08-09T18:19:36.411Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1733,7 +1733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-08T07:13:19.015Z</v>
+        <v>2026-08-09T18:19:36.424Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1753,7 +1753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-08T07:13:19.031Z</v>
+        <v>2026-08-09T18:19:36.440Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -1770,10 +1770,10 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-08T07:13:19.047Z</v>
+        <v>2026-08-09T18:19:36.455Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -1793,7 +1793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-08T07:13:19.063Z</v>
+        <v>2026-08-09T18:19:36.471Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -1813,7 +1813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-08T07:13:19.079Z</v>
+        <v>2026-08-09T18:19:36.487Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -1830,10 +1830,10 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-08T07:13:19.095Z</v>
+        <v>2026-08-09T18:19:36.502Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -1853,7 +1853,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-08T07:13:19.110Z</v>
+        <v>2026-08-09T18:19:36.517Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -1870,10 +1870,10 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-08T07:13:19.125Z</v>
+        <v>2026-08-09T18:19:36.533Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -1890,10 +1890,10 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-08T07:13:19.141Z</v>
+        <v>2026-08-09T18:19:36.548Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -1913,7 +1913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-08T07:13:19.156Z</v>
+        <v>2026-08-09T18:19:36.563Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -1933,7 +1933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-08T07:13:19.172Z</v>
+        <v>2026-08-09T18:19:36.579Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -1953,7 +1953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-08T07:13:19.187Z</v>
+        <v>2026-08-09T18:19:36.594Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -1970,10 +1970,10 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-08T07:13:19.203Z</v>
+        <v>2026-08-09T18:19:36.609Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -1990,10 +1990,10 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-08T07:13:19.218Z</v>
+        <v>2026-08-09T18:19:36.625Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2013,7 +2013,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-08T07:13:19.234Z</v>
+        <v>2026-08-09T18:19:36.641Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2033,7 +2033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-08T07:13:19.249Z</v>
+        <v>2026-08-09T18:19:36.656Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2050,10 +2050,10 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-08T07:13:19.265Z</v>
+        <v>2026-08-09T18:19:36.671Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2070,10 +2070,10 @@
         <v>PASS</v>
       </c>
       <c r="D84" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-08T07:13:19.280Z</v>
+        <v>2026-08-09T18:19:36.687Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2090,10 +2090,10 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-08T07:13:19.296Z</v>
+        <v>2026-08-09T18:19:36.702Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2110,10 +2110,10 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-08T07:13:19.312Z</v>
+        <v>2026-08-09T18:19:36.717Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2133,7 +2133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-08T07:13:19.327Z</v>
+        <v>2026-08-09T18:19:36.733Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2150,10 +2150,10 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-08T07:13:19.343Z</v>
+        <v>2026-08-09T18:19:36.748Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2170,10 +2170,10 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-08T07:13:19.358Z</v>
+        <v>2026-08-09T18:19:36.764Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2190,10 +2190,10 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-08T07:13:19.374Z</v>
+        <v>2026-08-09T18:19:36.778Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2210,10 +2210,10 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-08T07:13:19.389Z</v>
+        <v>2026-08-09T18:19:36.794Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2233,7 +2233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-08T07:13:19.405Z</v>
+        <v>2026-08-09T18:19:36.809Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2250,10 +2250,10 @@
         <v>PASS</v>
       </c>
       <c r="D93" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-08T07:13:19.422Z</v>
+        <v>2026-08-09T18:19:36.825Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2270,10 +2270,10 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-08T07:13:19.438Z</v>
+        <v>2026-08-09T18:19:36.840Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2293,7 +2293,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-08T07:13:19.454Z</v>
+        <v>2026-08-09T18:19:36.856Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2310,10 +2310,10 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-08T07:13:19.469Z</v>
+        <v>2026-08-09T18:19:36.872Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2333,7 +2333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-08T07:13:19.484Z</v>
+        <v>2026-08-09T18:19:36.887Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2353,7 +2353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-08T07:13:19.500Z</v>
+        <v>2026-08-09T18:19:36.904Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2373,7 +2373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-08T07:13:19.515Z</v>
+        <v>2026-08-09T18:19:36.919Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2390,10 +2390,10 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-08T07:13:19.531Z</v>
+        <v>2026-08-09T18:19:36.934Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2413,7 +2413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-08T07:13:19.546Z</v>
+        <v>2026-08-09T18:19:36.949Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2430,10 +2430,10 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-08T07:13:19.561Z</v>
+        <v>2026-08-09T18:19:36.966Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2450,10 +2450,10 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-08T07:13:19.577Z</v>
+        <v>2026-08-09T18:19:36.979Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2473,7 +2473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-08T07:13:19.593Z</v>
+        <v>2026-08-09T18:19:36.995Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2490,10 +2490,10 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-08T07:13:19.608Z</v>
+        <v>2026-08-09T18:19:37.012Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2510,10 +2510,10 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-08T07:13:19.624Z</v>
+        <v>2026-08-09T18:19:37.026Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2533,7 +2533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-08T07:13:19.640Z</v>
+        <v>2026-08-09T18:19:37.042Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2550,10 +2550,10 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-08T07:13:19.655Z</v>
+        <v>2026-08-09T18:19:37.058Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2573,7 +2573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-08T07:13:19.670Z</v>
+        <v>2026-08-09T18:19:37.073Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2593,7 +2593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-08T07:13:19.686Z</v>
+        <v>2026-08-09T18:19:37.089Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2613,7 +2613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-08T07:13:19.701Z</v>
+        <v>2026-08-09T18:19:37.104Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2633,7 +2633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-08T07:13:19.717Z</v>
+        <v>2026-08-09T18:19:37.119Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2650,10 +2650,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-08T07:13:19.733Z</v>
+        <v>2026-08-09T18:19:37.134Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2673,7 +2673,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-08T07:13:19.748Z</v>
+        <v>2026-08-09T18:19:37.149Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2690,10 +2690,10 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-08T07:13:19.764Z</v>
+        <v>2026-08-09T18:19:37.164Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2713,7 +2713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-08T07:13:19.780Z</v>
+        <v>2026-08-09T18:19:37.181Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2730,10 +2730,10 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-08T07:13:19.796Z</v>
+        <v>2026-08-09T18:19:37.196Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2753,7 +2753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-08T07:13:19.812Z</v>
+        <v>2026-08-09T18:19:37.211Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -2770,10 +2770,10 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-08T07:13:19.827Z</v>
+        <v>2026-08-09T18:19:37.227Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -2790,10 +2790,10 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-08T07:13:19.842Z</v>
+        <v>2026-08-09T18:19:37.243Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -2810,10 +2810,10 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-08T07:13:19.858Z</v>
+        <v>2026-08-09T18:19:37.258Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-08T07:13:19.873Z</v>
+        <v>2026-08-09T18:19:37.275Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -2853,7 +2853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-08T07:13:19.889Z</v>
+        <v>2026-08-09T18:19:37.291Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -2870,10 +2870,10 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-08T07:13:19.905Z</v>
+        <v>2026-08-09T18:19:37.306Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -2890,10 +2890,10 @@
         <v>PASS</v>
       </c>
       <c r="D125" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-08T07:13:19.921Z</v>
+        <v>2026-08-09T18:19:37.321Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -2913,7 +2913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-08T07:13:19.936Z</v>
+        <v>2026-08-09T18:19:37.336Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -2933,7 +2933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-08T07:13:19.951Z</v>
+        <v>2026-08-09T18:19:37.351Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -2950,10 +2950,10 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-08T07:13:19.967Z</v>
+        <v>2026-08-09T18:19:37.367Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -2970,10 +2970,10 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-08T07:13:19.983Z</v>
+        <v>2026-08-09T18:19:37.382Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -2993,7 +2993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-08T07:13:19.999Z</v>
+        <v>2026-08-09T18:19:37.398Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3013,7 +3013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-08T07:13:20.013Z</v>
+        <v>2026-08-09T18:19:37.413Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3033,7 +3033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-08T07:13:20.029Z</v>
+        <v>2026-08-09T18:19:37.428Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3050,10 +3050,10 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-08T07:13:20.044Z</v>
+        <v>2026-08-09T18:19:37.444Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3070,10 +3070,10 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-08T07:13:20.060Z</v>
+        <v>2026-08-09T18:19:37.458Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3093,7 +3093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-08T07:13:20.077Z</v>
+        <v>2026-08-09T18:19:37.474Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3110,10 +3110,10 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-08T07:13:20.092Z</v>
+        <v>2026-08-09T18:19:37.491Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3133,7 +3133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-08T07:13:20.107Z</v>
+        <v>2026-08-09T18:19:37.505Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3150,10 +3150,10 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-08T07:13:20.122Z</v>
+        <v>2026-08-09T18:19:37.521Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3170,10 +3170,10 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-08T07:13:20.138Z</v>
+        <v>2026-08-09T18:19:37.536Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3190,10 +3190,10 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-08T07:13:20.153Z</v>
+        <v>2026-08-09T18:19:37.552Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3213,7 +3213,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-08T07:13:20.169Z</v>
+        <v>2026-08-09T18:19:37.568Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3230,10 +3230,10 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-08T07:13:20.185Z</v>
+        <v>2026-08-09T18:19:37.583Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3250,10 +3250,10 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-08T07:13:20.200Z</v>
+        <v>2026-08-09T18:19:37.599Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3270,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-08T07:13:20.216Z</v>
+        <v>2026-08-09T18:19:37.614Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3293,7 +3293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-08T07:13:20.231Z</v>
+        <v>2026-08-09T18:19:37.629Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3310,10 +3310,10 @@
         <v>PASS</v>
       </c>
       <c r="D146" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-08T07:13:20.247Z</v>
+        <v>2026-08-09T18:19:37.644Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3333,7 +3333,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-08T07:13:20.264Z</v>
+        <v>2026-08-09T18:19:37.661Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3353,7 +3353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-08T07:13:20.279Z</v>
+        <v>2026-08-09T18:19:37.676Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3370,10 +3370,10 @@
         <v>PASS</v>
       </c>
       <c r="D149" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-08T07:13:20.294Z</v>
+        <v>2026-08-09T18:19:37.692Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3393,7 +3393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-08T07:13:20.312Z</v>
+        <v>2026-08-09T18:19:37.708Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3413,7 +3413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-08T07:13:20.326Z</v>
+        <v>2026-08-09T18:19:37.723Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3430,10 +3430,10 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-08T07:13:20.342Z</v>
+        <v>2026-08-09T18:19:37.739Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3450,10 +3450,10 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-08T07:13:20.358Z</v>
+        <v>2026-08-09T18:19:37.754Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3473,7 +3473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-08T07:13:20.373Z</v>
+        <v>2026-08-09T18:19:37.769Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3493,7 +3493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-08T07:13:20.389Z</v>
+        <v>2026-08-09T18:19:37.785Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3510,10 +3510,10 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-08T07:13:20.404Z</v>
+        <v>2026-08-09T18:19:37.801Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3533,7 +3533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-08T07:13:20.420Z</v>
+        <v>2026-08-09T18:19:37.817Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3553,7 +3553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-08T07:13:20.435Z</v>
+        <v>2026-08-09T18:19:37.832Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3570,10 +3570,10 @@
         <v>PASS</v>
       </c>
       <c r="D159" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-08T07:13:20.450Z</v>
+        <v>2026-08-09T18:19:37.848Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3590,10 +3590,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-08T07:13:20.466Z</v>
+        <v>2026-08-09T18:19:37.863Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3613,7 +3613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-08T07:13:20.482Z</v>
+        <v>2026-08-09T18:19:37.879Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3633,7 +3633,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-08T07:13:20.498Z</v>
+        <v>2026-08-09T18:19:37.896Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3653,7 +3653,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-08T07:13:20.512Z</v>
+        <v>2026-08-09T18:19:37.911Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3673,7 +3673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-08T07:13:20.529Z</v>
+        <v>2026-08-09T18:19:37.927Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3693,7 +3693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-08T07:13:20.543Z</v>
+        <v>2026-08-09T18:19:37.941Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3713,7 +3713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-08T07:13:20.559Z</v>
+        <v>2026-08-09T18:19:37.957Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3733,7 +3733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-08T07:13:20.574Z</v>
+        <v>2026-08-09T18:19:37.972Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3753,7 +3753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-08T07:13:20.589Z</v>
+        <v>2026-08-09T18:19:37.987Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -3770,10 +3770,10 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-08T07:13:20.605Z</v>
+        <v>2026-08-09T18:19:38.002Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -3793,7 +3793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-08T07:13:20.621Z</v>
+        <v>2026-08-09T18:19:38.018Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -3810,10 +3810,10 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-08T07:13:20.636Z</v>
+        <v>2026-08-09T18:19:38.034Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -3830,10 +3830,10 @@
         <v>PASS</v>
       </c>
       <c r="D172" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-08T07:13:20.651Z</v>
+        <v>2026-08-09T18:19:38.050Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -3853,7 +3853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-08T07:13:20.667Z</v>
+        <v>2026-08-09T18:19:38.066Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -3870,10 +3870,10 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-08T07:13:20.683Z</v>
+        <v>2026-08-09T18:19:38.081Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -3893,7 +3893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-08T07:13:20.699Z</v>
+        <v>2026-08-09T18:19:38.097Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -3913,7 +3913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-08T07:13:20.714Z</v>
+        <v>2026-08-09T18:19:38.112Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -3930,10 +3930,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-08T07:13:20.729Z</v>
+        <v>2026-08-09T18:19:38.128Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -3950,10 +3950,10 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-08T07:13:20.745Z</v>
+        <v>2026-08-09T18:19:38.143Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -3970,10 +3970,10 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-08T07:13:20.760Z</v>
+        <v>2026-08-09T18:19:38.159Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -3993,7 +3993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-08T07:13:20.776Z</v>
+        <v>2026-08-09T18:19:38.177Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4013,7 +4013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-08T07:13:20.791Z</v>
+        <v>2026-08-09T18:19:38.190Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4030,10 +4030,10 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-08T07:13:20.808Z</v>
+        <v>2026-08-09T18:19:38.205Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4053,7 +4053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-08T07:13:20.824Z</v>
+        <v>2026-08-09T18:19:38.221Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4073,7 +4073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-08T07:13:20.840Z</v>
+        <v>2026-08-09T18:19:38.237Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4093,7 +4093,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-08T07:13:20.855Z</v>
+        <v>2026-08-09T18:19:38.252Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4110,10 +4110,10 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-08T07:13:20.871Z</v>
+        <v>2026-08-09T18:19:38.267Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4130,10 +4130,10 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-08T07:13:20.886Z</v>
+        <v>2026-08-09T18:19:38.283Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4153,7 +4153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-08T07:13:20.903Z</v>
+        <v>2026-08-09T18:19:38.299Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4173,7 +4173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-08T07:13:20.918Z</v>
+        <v>2026-08-09T18:19:38.314Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4190,10 +4190,10 @@
         <v>PASS</v>
       </c>
       <c r="D190" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-08T07:13:20.933Z</v>
+        <v>2026-08-09T18:19:38.330Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4210,10 +4210,10 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-08T07:13:20.949Z</v>
+        <v>2026-08-09T18:19:38.346Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4233,7 +4233,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-08T07:13:20.965Z</v>
+        <v>2026-08-09T18:19:38.363Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4250,10 +4250,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-08T07:13:20.981Z</v>
+        <v>2026-08-09T18:19:38.377Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4270,10 +4270,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-08T07:13:20.996Z</v>
+        <v>2026-08-09T18:19:38.395Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4293,7 +4293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-08T07:13:21.011Z</v>
+        <v>2026-08-09T18:19:38.409Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4310,10 +4310,10 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-08T07:13:21.027Z</v>
+        <v>2026-08-09T18:19:38.423Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4330,10 +4330,10 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-08T07:13:21.043Z</v>
+        <v>2026-08-09T18:19:38.438Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4353,7 +4353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-08T07:13:21.058Z</v>
+        <v>2026-08-09T18:19:38.453Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4373,7 +4373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-08T07:13:21.075Z</v>
+        <v>2026-08-09T18:19:38.469Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4390,10 +4390,10 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-08T07:13:21.090Z</v>
+        <v>2026-08-09T18:19:38.485Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4413,7 +4413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-08T07:13:21.105Z</v>
+        <v>2026-08-09T18:19:38.500Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4433,7 +4433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-08T07:13:21.120Z</v>
+        <v>2026-08-09T18:19:38.515Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4453,7 +4453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-08T07:13:21.136Z</v>
+        <v>2026-08-09T18:19:38.531Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4470,10 +4470,10 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-08T07:13:21.151Z</v>
+        <v>2026-08-09T18:19:38.547Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4490,10 +4490,10 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-08T07:13:21.167Z</v>
+        <v>2026-08-09T18:19:38.562Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4510,10 +4510,10 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-08T07:13:21.182Z</v>
+        <v>2026-08-09T18:19:38.578Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4533,7 +4533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-08T07:13:21.198Z</v>
+        <v>2026-08-09T18:19:38.595Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4550,10 +4550,10 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-08T07:13:21.215Z</v>
+        <v>2026-08-09T18:19:38.609Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4570,10 +4570,10 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-08T07:13:21.233Z</v>
+        <v>2026-08-09T18:19:38.624Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4593,7 +4593,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-08T07:13:21.248Z</v>
+        <v>2026-08-09T18:19:38.639Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4613,7 +4613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-08T07:13:21.263Z</v>
+        <v>2026-08-09T18:19:38.654Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4633,7 +4633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-08T07:13:21.278Z</v>
+        <v>2026-08-09T18:19:38.669Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4653,7 +4653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-08T07:13:21.294Z</v>
+        <v>2026-08-09T18:19:38.685Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4670,10 +4670,10 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-08T07:13:21.309Z</v>
+        <v>2026-08-09T18:19:38.701Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4690,10 +4690,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-08T07:13:21.325Z</v>
+        <v>2026-08-09T18:19:38.715Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4713,7 +4713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-08T07:13:21.341Z</v>
+        <v>2026-08-09T18:19:38.731Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4730,10 +4730,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-08T07:13:21.357Z</v>
+        <v>2026-08-09T18:19:38.746Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4753,7 +4753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-08T07:13:21.373Z</v>
+        <v>2026-08-09T18:19:38.762Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -4770,10 +4770,10 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-08T07:13:21.389Z</v>
+        <v>2026-08-09T18:19:38.777Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -4790,10 +4790,10 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-08T07:13:21.404Z</v>
+        <v>2026-08-09T18:19:38.794Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -4813,7 +4813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-08T07:13:21.420Z</v>
+        <v>2026-08-09T18:19:38.810Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -4830,10 +4830,10 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-08T07:13:21.436Z</v>
+        <v>2026-08-09T18:19:38.826Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -4850,10 +4850,10 @@
         <v>PASS</v>
       </c>
       <c r="D223" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-08T07:13:21.452Z</v>
+        <v>2026-08-09T18:19:38.841Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -4873,7 +4873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-08T07:13:21.467Z</v>
+        <v>2026-08-09T18:19:38.856Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -4890,10 +4890,10 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-08T07:13:21.482Z</v>
+        <v>2026-08-09T18:19:38.872Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -4913,7 +4913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-08T07:13:21.498Z</v>
+        <v>2026-08-09T18:19:38.888Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -4933,7 +4933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-08T07:13:21.513Z</v>
+        <v>2026-08-09T18:19:38.903Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -4950,10 +4950,10 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-08T07:13:21.528Z</v>
+        <v>2026-08-09T18:19:38.919Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -4973,7 +4973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-08T07:13:21.544Z</v>
+        <v>2026-08-09T18:19:38.935Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -4990,10 +4990,10 @@
         <v>PASS</v>
       </c>
       <c r="D230" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-08T07:13:21.559Z</v>
+        <v>2026-08-09T18:19:38.951Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5013,7 +5013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-08T07:13:21.574Z</v>
+        <v>2026-08-09T18:19:38.965Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5033,7 +5033,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-08T07:13:21.590Z</v>
+        <v>2026-08-09T18:19:38.981Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5050,10 +5050,10 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-08T07:13:21.605Z</v>
+        <v>2026-08-09T18:19:38.997Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5073,7 +5073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-08T07:13:21.620Z</v>
+        <v>2026-08-09T18:19:39.012Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5093,7 +5093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-08T07:13:21.636Z</v>
+        <v>2026-08-09T18:19:39.029Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5113,7 +5113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-08T07:13:21.652Z</v>
+        <v>2026-08-09T18:19:39.045Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5130,10 +5130,10 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-08T07:13:21.668Z</v>
+        <v>2026-08-09T18:19:39.059Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5153,7 +5153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-08T07:13:21.685Z</v>
+        <v>2026-08-09T18:19:39.076Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5173,7 +5173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-08T07:13:21.700Z</v>
+        <v>2026-08-09T18:19:39.091Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5193,7 +5193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-08T07:13:21.716Z</v>
+        <v>2026-08-09T18:19:39.107Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5210,10 +5210,10 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-08T07:13:21.732Z</v>
+        <v>2026-08-09T18:19:39.122Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5230,10 +5230,10 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-08T07:13:21.748Z</v>
+        <v>2026-08-09T18:19:39.137Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5250,10 +5250,10 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-08T07:13:21.763Z</v>
+        <v>2026-08-09T18:19:39.153Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5270,10 +5270,10 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-08T07:13:21.778Z</v>
+        <v>2026-08-09T18:19:39.169Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5290,10 +5290,10 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-08T07:13:21.795Z</v>
+        <v>2026-08-09T18:19:39.184Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5313,7 +5313,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-08T07:13:21.810Z</v>
+        <v>2026-08-09T18:19:39.199Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5330,10 +5330,10 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-08T07:13:21.825Z</v>
+        <v>2026-08-09T18:19:39.215Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5353,7 +5353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-08T07:13:21.842Z</v>
+        <v>2026-08-09T18:19:39.231Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5370,10 +5370,10 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-08T07:13:21.856Z</v>
+        <v>2026-08-09T18:19:39.247Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5393,7 +5393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-08T07:13:21.873Z</v>
+        <v>2026-08-09T18:19:39.263Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5413,7 +5413,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-08T07:13:21.889Z</v>
+        <v>2026-08-09T18:19:39.279Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5430,10 +5430,10 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-08T07:13:21.905Z</v>
+        <v>2026-08-09T18:19:39.294Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5453,7 +5453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-08T07:13:21.920Z</v>
+        <v>2026-08-09T18:19:39.309Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5470,10 +5470,10 @@
         <v>PASS</v>
       </c>
       <c r="D254" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-08T07:13:21.936Z</v>
+        <v>2026-08-09T18:19:39.324Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5490,10 +5490,10 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-08T07:13:21.952Z</v>
+        <v>2026-08-09T18:19:39.339Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5510,10 +5510,10 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-08T07:13:21.967Z</v>
+        <v>2026-08-09T18:19:39.355Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5530,10 +5530,10 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-08T07:13:21.984Z</v>
+        <v>2026-08-09T18:19:39.371Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5553,7 +5553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-08T07:13:21.999Z</v>
+        <v>2026-08-09T18:19:39.385Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5573,7 +5573,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-08T07:13:22.014Z</v>
+        <v>2026-08-09T18:19:39.400Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5590,10 +5590,10 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-08T07:13:22.029Z</v>
+        <v>2026-08-09T18:19:39.416Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5613,7 +5613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-08T07:13:22.045Z</v>
+        <v>2026-08-09T18:19:39.432Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5630,10 +5630,10 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-08T07:13:22.061Z</v>
+        <v>2026-08-09T18:19:39.448Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5650,10 +5650,10 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-08T07:13:22.077Z</v>
+        <v>2026-08-09T18:19:39.462Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5670,10 +5670,10 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-08T07:13:22.092Z</v>
+        <v>2026-08-09T18:19:39.478Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5690,10 +5690,10 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-08T07:13:22.108Z</v>
+        <v>2026-08-09T18:19:39.495Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5713,7 +5713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-08T07:13:22.123Z</v>
+        <v>2026-08-09T18:19:39.510Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5733,7 +5733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-08T07:13:22.138Z</v>
+        <v>2026-08-09T18:19:39.525Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5753,7 +5753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-08T07:13:22.154Z</v>
+        <v>2026-08-09T18:19:39.541Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -5773,7 +5773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-08T07:13:22.169Z</v>
+        <v>2026-08-09T18:19:39.555Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -5790,10 +5790,10 @@
         <v>PASS</v>
       </c>
       <c r="D270" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-08T07:13:22.185Z</v>
+        <v>2026-08-09T18:19:39.570Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -5810,10 +5810,10 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-08T07:13:22.200Z</v>
+        <v>2026-08-09T18:19:39.587Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -5833,7 +5833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-08T07:13:22.216Z</v>
+        <v>2026-08-09T18:19:39.601Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -5850,10 +5850,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-08T07:13:22.231Z</v>
+        <v>2026-08-09T18:19:39.618Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -5873,7 +5873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-08T07:13:22.247Z</v>
+        <v>2026-08-09T18:19:39.633Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -5890,10 +5890,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-08T07:13:22.262Z</v>
+        <v>2026-08-09T18:19:39.649Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -5913,7 +5913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-08T07:13:22.278Z</v>
+        <v>2026-08-09T18:19:39.665Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -5930,10 +5930,10 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-08T07:13:22.294Z</v>
+        <v>2026-08-09T18:19:39.681Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -5953,7 +5953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-08T07:13:22.309Z</v>
+        <v>2026-08-09T18:19:39.696Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -5970,10 +5970,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-08T07:13:22.325Z</v>
+        <v>2026-08-09T18:19:39.712Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -5993,7 +5993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-08T07:13:22.341Z</v>
+        <v>2026-08-09T18:19:39.727Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6013,7 +6013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-08T07:13:22.356Z</v>
+        <v>2026-08-09T18:19:39.742Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6033,7 +6033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-08T07:13:22.371Z</v>
+        <v>2026-08-09T18:19:39.757Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6053,7 +6053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-08T07:13:22.387Z</v>
+        <v>2026-08-09T18:19:39.774Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6070,10 +6070,10 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-08T07:13:22.403Z</v>
+        <v>2026-08-09T18:19:39.788Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6090,10 +6090,10 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-08T07:13:22.419Z</v>
+        <v>2026-08-09T18:19:39.803Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6113,7 +6113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-08T07:13:22.435Z</v>
+        <v>2026-08-09T18:19:39.819Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6130,10 +6130,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-08T07:13:22.450Z</v>
+        <v>2026-08-09T18:19:39.835Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6150,10 +6150,10 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-08T07:13:22.466Z</v>
+        <v>2026-08-09T18:19:39.850Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6173,7 +6173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-08T07:13:22.482Z</v>
+        <v>2026-08-09T18:19:39.866Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6190,10 +6190,10 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-08T07:13:22.497Z</v>
+        <v>2026-08-09T18:19:39.882Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6210,10 +6210,10 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-08T07:13:22.513Z</v>
+        <v>2026-08-09T18:19:39.897Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6230,10 +6230,10 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-08T07:13:22.528Z</v>
+        <v>2026-08-09T18:19:39.914Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6250,10 +6250,10 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-08T07:13:22.544Z</v>
+        <v>2026-08-09T18:19:39.930Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6270,10 +6270,10 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-08T07:13:22.560Z</v>
+        <v>2026-08-09T18:19:39.944Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6290,10 +6290,10 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-08T07:13:22.575Z</v>
+        <v>2026-08-09T18:19:39.960Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6310,10 +6310,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-08T07:13:22.591Z</v>
+        <v>2026-08-09T18:19:39.976Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6333,7 +6333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-08T07:13:22.606Z</v>
+        <v>2026-08-09T18:19:39.991Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6350,10 +6350,10 @@
         <v>PASS</v>
       </c>
       <c r="D298" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-08T07:13:22.622Z</v>
+        <v>2026-08-09T18:19:40.007Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6373,7 +6373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-08T07:13:22.637Z</v>
+        <v>2026-08-09T18:19:40.022Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6390,10 +6390,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-08T07:13:22.654Z</v>
+        <v>2026-08-09T18:19:40.037Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6410,10 +6410,10 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-08T07:13:22.669Z</v>
+        <v>2026-08-09T18:19:40.053Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6433,7 +6433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-08T07:13:22.684Z</v>
+        <v>2026-08-09T18:19:40.068Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6453,7 +6453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-08T07:13:22.700Z</v>
+        <v>2026-08-09T18:19:40.084Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6473,7 +6473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-08T07:13:22.715Z</v>
+        <v>2026-08-09T18:19:40.099Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6493,7 +6493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-08T07:13:22.732Z</v>
+        <v>2026-08-09T18:19:40.115Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6513,7 +6513,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-08T07:13:22.747Z</v>
+        <v>2026-08-09T18:19:40.131Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6533,7 +6533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-08T07:13:22.763Z</v>
+        <v>2026-08-09T18:19:40.147Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6553,7 +6553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-08T07:13:22.778Z</v>
+        <v>2026-08-09T18:19:40.162Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6573,7 +6573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-08T07:13:22.794Z</v>
+        <v>2026-08-09T18:19:40.178Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6590,10 +6590,10 @@
         <v>PASS</v>
       </c>
       <c r="D310" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-08T07:13:22.809Z</v>
+        <v>2026-08-09T18:19:40.195Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6613,7 +6613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-08T07:13:22.825Z</v>
+        <v>2026-08-09T18:19:40.211Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6633,7 +6633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-08T07:13:22.840Z</v>
+        <v>2026-08-09T18:19:40.226Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6653,7 +6653,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-08T07:13:22.855Z</v>
+        <v>2026-08-09T18:19:40.241Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6670,10 +6670,10 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-08T07:13:22.872Z</v>
+        <v>2026-08-09T18:19:40.256Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6690,10 +6690,10 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-08T07:13:22.887Z</v>
+        <v>2026-08-09T18:19:40.273Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6710,10 +6710,10 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-08T07:13:22.903Z</v>
+        <v>2026-08-09T18:19:40.288Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6730,10 +6730,10 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-08T07:13:22.919Z</v>
+        <v>2026-08-09T18:19:40.303Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6753,7 +6753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-08T07:13:22.935Z</v>
+        <v>2026-08-09T18:19:40.319Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -6773,7 +6773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-08T07:13:22.950Z</v>
+        <v>2026-08-09T18:19:40.334Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -6790,10 +6790,10 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-08T07:13:22.966Z</v>
+        <v>2026-08-09T18:19:40.349Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -6810,10 +6810,10 @@
         <v>PASS</v>
       </c>
       <c r="D321" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-08T07:13:22.981Z</v>
+        <v>2026-08-09T18:19:40.365Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -6830,10 +6830,10 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-08T07:13:22.997Z</v>
+        <v>2026-08-09T18:19:40.382Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -6850,10 +6850,10 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-08T07:13:23.013Z</v>
+        <v>2026-08-09T18:19:40.396Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -6870,10 +6870,10 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-08T07:13:23.028Z</v>
+        <v>2026-08-09T18:19:40.412Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -6890,10 +6890,10 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-08T07:13:23.044Z</v>
+        <v>2026-08-09T18:19:40.427Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -6913,7 +6913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-08T07:13:23.060Z</v>
+        <v>2026-08-09T18:19:40.444Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -6930,10 +6930,10 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-08T07:13:23.075Z</v>
+        <v>2026-08-09T18:19:40.460Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -6950,10 +6950,10 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-08T07:13:23.090Z</v>
+        <v>2026-08-09T18:19:40.476Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -6970,10 +6970,10 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-08T07:13:23.106Z</v>
+        <v>2026-08-09T18:19:40.490Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -6993,7 +6993,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-08T07:13:23.121Z</v>
+        <v>2026-08-09T18:19:40.505Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7013,7 +7013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-08T07:13:23.136Z</v>
+        <v>2026-08-09T18:19:40.520Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7033,7 +7033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-08T07:13:23.152Z</v>
+        <v>2026-08-09T18:19:40.535Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7053,7 +7053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-08T07:13:23.168Z</v>
+        <v>2026-08-09T18:19:40.551Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7070,10 +7070,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-08T07:13:23.183Z</v>
+        <v>2026-08-09T18:19:40.567Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7093,7 +7093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-08T07:13:23.199Z</v>
+        <v>2026-08-09T18:19:40.583Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7113,7 +7113,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-08T07:13:23.214Z</v>
+        <v>2026-08-09T18:19:40.598Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7133,7 +7133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-08T07:13:23.230Z</v>
+        <v>2026-08-09T18:19:40.614Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7150,10 +7150,10 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-08T07:13:23.247Z</v>
+        <v>2026-08-09T18:19:40.629Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7173,7 +7173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-08T07:13:23.265Z</v>
+        <v>2026-08-09T18:19:40.645Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7193,7 +7193,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-08T07:13:23.278Z</v>
+        <v>2026-08-09T18:19:40.660Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7210,10 +7210,10 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-08T07:13:23.293Z</v>
+        <v>2026-08-09T18:19:40.676Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7233,7 +7233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-08T07:13:23.308Z</v>
+        <v>2026-08-09T18:19:40.691Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7253,7 +7253,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-08T07:13:23.324Z</v>
+        <v>2026-08-09T18:19:40.707Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7270,10 +7270,10 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-08T07:13:23.343Z</v>
+        <v>2026-08-09T18:19:40.722Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7293,7 +7293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-08T07:13:23.356Z</v>
+        <v>2026-08-09T18:19:40.737Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7310,10 +7310,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-08T07:13:23.371Z</v>
+        <v>2026-08-09T18:19:40.753Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7330,10 +7330,10 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-08T07:13:23.387Z</v>
+        <v>2026-08-09T18:19:40.768Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7353,7 +7353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-08T07:13:23.401Z</v>
+        <v>2026-08-09T18:19:40.784Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7370,10 +7370,10 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-08T07:13:23.418Z</v>
+        <v>2026-08-09T18:19:40.799Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7393,7 +7393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-08T07:13:23.434Z</v>
+        <v>2026-08-09T18:19:40.815Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7413,7 +7413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-08T07:13:23.449Z</v>
+        <v>2026-08-09T18:19:40.830Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7430,10 +7430,10 @@
         <v>PASS</v>
       </c>
       <c r="D352" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-08T07:13:23.465Z</v>
+        <v>2026-08-09T18:19:40.846Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7450,10 +7450,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-08T07:13:23.479Z</v>
+        <v>2026-08-09T18:19:40.862Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7470,10 +7470,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-08T07:13:23.495Z</v>
+        <v>2026-08-09T18:19:40.877Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7493,7 +7493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-08T07:13:23.511Z</v>
+        <v>2026-08-09T18:19:40.893Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7510,10 +7510,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-08T07:13:23.527Z</v>
+        <v>2026-08-09T18:19:40.908Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7530,10 +7530,10 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-08T07:13:23.543Z</v>
+        <v>2026-08-09T18:19:40.923Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7553,7 +7553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-08T07:13:23.558Z</v>
+        <v>2026-08-09T18:19:40.938Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7570,10 +7570,10 @@
         <v>PASS</v>
       </c>
       <c r="D359" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-08T07:13:23.573Z</v>
+        <v>2026-08-09T18:19:40.954Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7593,7 +7593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-08T07:13:23.589Z</v>
+        <v>2026-08-09T18:19:40.970Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7610,10 +7610,10 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-08T07:13:23.605Z</v>
+        <v>2026-08-09T18:19:40.984Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7630,10 +7630,10 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-08T07:13:23.621Z</v>
+        <v>2026-08-09T18:19:41.000Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7650,10 +7650,10 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-08T07:13:23.637Z</v>
+        <v>2026-08-09T18:19:41.015Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7670,10 +7670,10 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-08T07:13:23.652Z</v>
+        <v>2026-08-09T18:19:41.031Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7690,10 +7690,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-08T07:13:23.667Z</v>
+        <v>2026-08-09T18:19:41.047Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7710,10 +7710,10 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-08T07:13:23.682Z</v>
+        <v>2026-08-09T18:19:41.063Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7733,7 +7733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-08T07:13:23.698Z</v>
+        <v>2026-08-09T18:19:41.079Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7750,10 +7750,10 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-08T07:13:23.714Z</v>
+        <v>2026-08-09T18:19:41.094Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -7770,10 +7770,10 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-08T07:13:23.729Z</v>
+        <v>2026-08-09T18:19:41.110Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -7790,10 +7790,10 @@
         <v>PASS</v>
       </c>
       <c r="D370" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-08T07:13:23.746Z</v>
+        <v>2026-08-09T18:19:41.125Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -7810,10 +7810,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-08T07:13:23.763Z</v>
+        <v>2026-08-09T18:19:41.140Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -7833,7 +7833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-08T07:13:23.777Z</v>
+        <v>2026-08-09T18:19:41.156Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -7853,7 +7853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-08T07:13:23.793Z</v>
+        <v>2026-08-09T18:19:41.172Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -7873,7 +7873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-08T07:13:23.809Z</v>
+        <v>2026-08-09T18:19:41.188Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -7890,10 +7890,10 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-08T07:13:23.824Z</v>
+        <v>2026-08-09T18:19:41.204Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -7913,7 +7913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-08T07:13:23.839Z</v>
+        <v>2026-08-09T18:19:41.219Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -7933,7 +7933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-08T07:13:23.854Z</v>
+        <v>2026-08-09T18:19:41.234Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -7950,10 +7950,10 @@
         <v>PASS</v>
       </c>
       <c r="D378" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-08T07:13:23.870Z</v>
+        <v>2026-08-09T18:19:41.250Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -7973,7 +7973,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-08T07:13:23.886Z</v>
+        <v>2026-08-09T18:19:41.266Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -7990,10 +7990,10 @@
         <v>PASS</v>
       </c>
       <c r="D380" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-08T07:13:23.900Z</v>
+        <v>2026-08-09T18:19:41.282Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8013,7 +8013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-08T07:13:23.915Z</v>
+        <v>2026-08-09T18:19:41.298Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8033,7 +8033,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-08T07:13:23.932Z</v>
+        <v>2026-08-09T18:19:41.314Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8053,7 +8053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-08T07:13:23.947Z</v>
+        <v>2026-08-09T18:19:41.329Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8073,7 +8073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-08T07:13:23.963Z</v>
+        <v>2026-08-09T18:19:41.344Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8090,10 +8090,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-08T07:13:23.979Z</v>
+        <v>2026-08-09T18:19:41.359Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8110,10 +8110,10 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-08T07:13:23.995Z</v>
+        <v>2026-08-09T18:19:41.374Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8133,7 +8133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-08T07:13:24.011Z</v>
+        <v>2026-08-09T18:19:41.390Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8150,10 +8150,10 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-08T07:13:24.026Z</v>
+        <v>2026-08-09T18:19:41.406Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8170,10 +8170,10 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-08T07:13:24.043Z</v>
+        <v>2026-08-09T18:19:41.421Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8190,10 +8190,10 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-08T07:13:24.059Z</v>
+        <v>2026-08-09T18:19:41.437Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8213,7 +8213,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-08T07:13:24.073Z</v>
+        <v>2026-08-09T18:19:41.452Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8230,10 +8230,10 @@
         <v>PASS</v>
       </c>
       <c r="D392" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-08T07:13:24.089Z</v>
+        <v>2026-08-09T18:19:41.467Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8250,10 +8250,10 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-08T07:13:24.104Z</v>
+        <v>2026-08-09T18:19:41.483Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8273,7 +8273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-08T07:13:24.120Z</v>
+        <v>2026-08-09T18:19:41.500Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8293,7 +8293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-08T07:13:24.135Z</v>
+        <v>2026-08-09T18:19:41.515Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8313,7 +8313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-08T07:13:24.151Z</v>
+        <v>2026-08-09T18:19:41.531Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8333,7 +8333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-08T07:13:24.166Z</v>
+        <v>2026-08-09T18:19:41.546Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8350,10 +8350,10 @@
         <v>PASS</v>
       </c>
       <c r="D398" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-08T07:13:24.182Z</v>
+        <v>2026-08-09T18:19:41.561Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8370,10 +8370,10 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-08T07:13:24.197Z</v>
+        <v>2026-08-09T18:19:41.577Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8393,7 +8393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-08T07:13:24.214Z</v>
+        <v>2026-08-09T18:19:41.593Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8413,7 +8413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-08T07:13:24.229Z</v>
+        <v>2026-08-09T18:19:41.608Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>

--- a/reports/Appium Report.xlsx
+++ b/reports/Appium Report.xlsx
@@ -433,7 +433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-09T18:19:35.426Z</v>
+        <v>2026-08-09T18:22:57.692Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -453,7 +453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-09T18:19:35.432Z</v>
+        <v>2026-08-09T18:22:57.698Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -470,10 +470,10 @@
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-09T18:19:35.446Z</v>
+        <v>2026-08-09T18:22:57.717Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -493,7 +493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-09T18:19:35.462Z</v>
+        <v>2026-08-09T18:22:57.733Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-09T18:19:35.477Z</v>
+        <v>2026-08-09T18:22:57.749Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-09T18:19:35.492Z</v>
+        <v>2026-08-09T18:22:57.765Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,10 +550,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-09T18:19:35.508Z</v>
+        <v>2026-08-09T18:22:57.780Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -573,7 +573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-09T18:19:35.524Z</v>
+        <v>2026-08-09T18:22:57.796Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -590,10 +590,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-09T18:19:35.539Z</v>
+        <v>2026-08-09T18:22:57.812Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -613,7 +613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-09T18:19:35.554Z</v>
+        <v>2026-08-09T18:22:57.827Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -633,7 +633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-09T18:19:35.570Z</v>
+        <v>2026-08-09T18:22:57.843Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -653,7 +653,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-09T18:19:35.586Z</v>
+        <v>2026-08-09T18:22:57.858Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -673,7 +673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-09T18:19:35.602Z</v>
+        <v>2026-08-09T18:22:57.874Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -693,7 +693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-09T18:19:35.617Z</v>
+        <v>2026-08-09T18:22:57.889Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -710,10 +710,10 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-09T18:19:35.633Z</v>
+        <v>2026-08-09T18:22:57.904Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -733,7 +733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-09T18:19:35.648Z</v>
+        <v>2026-08-09T18:22:57.920Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -753,7 +753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-09T18:19:35.663Z</v>
+        <v>2026-08-09T18:22:57.935Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -773,7 +773,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-09T18:19:35.681Z</v>
+        <v>2026-08-09T18:22:57.951Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -793,7 +793,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-09T18:19:35.695Z</v>
+        <v>2026-08-09T18:22:57.966Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -810,10 +810,10 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-09T18:19:35.710Z</v>
+        <v>2026-08-09T18:22:57.982Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -833,7 +833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-09T18:19:35.726Z</v>
+        <v>2026-08-09T18:22:57.998Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -853,7 +853,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-09T18:19:35.741Z</v>
+        <v>2026-08-09T18:22:58.013Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -873,7 +873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-09T18:19:35.756Z</v>
+        <v>2026-08-09T18:22:58.029Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -890,10 +890,10 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-09T18:19:35.773Z</v>
+        <v>2026-08-09T18:22:58.044Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -913,7 +913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-09T18:19:35.788Z</v>
+        <v>2026-08-09T18:22:58.059Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -930,10 +930,10 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-09T18:19:35.804Z</v>
+        <v>2026-08-09T18:22:58.074Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -953,7 +953,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-09T18:19:35.820Z</v>
+        <v>2026-08-09T18:22:58.091Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -973,7 +973,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-09T18:19:35.835Z</v>
+        <v>2026-08-09T18:22:58.106Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -993,7 +993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-09T18:19:35.851Z</v>
+        <v>2026-08-09T18:22:58.122Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1010,10 +1010,10 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-09T18:19:35.867Z</v>
+        <v>2026-08-09T18:22:58.137Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1033,7 +1033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-09T18:19:35.882Z</v>
+        <v>2026-08-09T18:22:58.153Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1050,10 +1050,10 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-09T18:19:35.897Z</v>
+        <v>2026-08-09T18:22:58.169Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1073,7 +1073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-09T18:19:35.912Z</v>
+        <v>2026-08-09T18:22:58.184Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1093,7 +1093,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-09T18:19:35.927Z</v>
+        <v>2026-08-09T18:22:58.199Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1110,10 +1110,10 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-09T18:19:35.942Z</v>
+        <v>2026-08-09T18:22:58.215Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1133,7 +1133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-09T18:19:35.957Z</v>
+        <v>2026-08-09T18:22:58.231Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1153,7 +1153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-09T18:19:35.972Z</v>
+        <v>2026-08-09T18:22:58.246Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1173,7 +1173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-09T18:19:35.987Z</v>
+        <v>2026-08-09T18:22:58.261Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1193,7 +1193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-09T18:19:36.003Z</v>
+        <v>2026-08-09T18:22:58.277Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1210,10 +1210,10 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-09T18:19:36.019Z</v>
+        <v>2026-08-09T18:22:58.293Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1233,7 +1233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-09T18:19:36.034Z</v>
+        <v>2026-08-09T18:22:58.309Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1250,10 +1250,10 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-09T18:19:36.049Z</v>
+        <v>2026-08-09T18:22:58.325Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1270,10 +1270,10 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-09T18:19:36.065Z</v>
+        <v>2026-08-09T18:22:58.341Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1290,10 +1290,10 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-09T18:19:36.081Z</v>
+        <v>2026-08-09T18:22:58.356Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1310,10 +1310,10 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-09T18:19:36.097Z</v>
+        <v>2026-08-09T18:22:58.371Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1333,7 +1333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-09T18:19:36.112Z</v>
+        <v>2026-08-09T18:22:58.386Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1353,7 +1353,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-09T18:19:36.128Z</v>
+        <v>2026-08-09T18:22:58.402Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1373,7 +1373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-09T18:19:36.144Z</v>
+        <v>2026-08-09T18:22:58.419Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1390,10 +1390,10 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-09T18:19:36.160Z</v>
+        <v>2026-08-09T18:22:58.433Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1413,7 +1413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-09T18:19:36.176Z</v>
+        <v>2026-08-09T18:22:58.449Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1430,10 +1430,10 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-09T18:19:36.190Z</v>
+        <v>2026-08-09T18:22:58.465Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1453,7 +1453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-09T18:19:36.205Z</v>
+        <v>2026-08-09T18:22:58.480Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1470,10 +1470,10 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-09T18:19:36.221Z</v>
+        <v>2026-08-09T18:22:58.495Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1490,10 +1490,10 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-09T18:19:36.237Z</v>
+        <v>2026-08-09T18:22:58.510Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1510,10 +1510,10 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-09T18:19:36.253Z</v>
+        <v>2026-08-09T18:22:58.525Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1533,7 +1533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-09T18:19:36.269Z</v>
+        <v>2026-08-09T18:22:58.541Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1553,7 +1553,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-09T18:19:36.285Z</v>
+        <v>2026-08-09T18:22:58.558Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1570,10 +1570,10 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-09T18:19:36.301Z</v>
+        <v>2026-08-09T18:22:58.573Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1593,7 +1593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-09T18:19:36.317Z</v>
+        <v>2026-08-09T18:22:58.589Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1610,10 +1610,10 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-09T18:19:36.333Z</v>
+        <v>2026-08-09T18:22:58.604Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1633,7 +1633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-09T18:19:36.347Z</v>
+        <v>2026-08-09T18:22:58.619Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1653,7 +1653,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-09T18:19:36.364Z</v>
+        <v>2026-08-09T18:22:58.635Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1670,10 +1670,10 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-09T18:19:36.379Z</v>
+        <v>2026-08-09T18:22:58.651Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1690,10 +1690,10 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-09T18:19:36.394Z</v>
+        <v>2026-08-09T18:22:58.667Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1710,10 +1710,10 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-09T18:19:36.411Z</v>
+        <v>2026-08-09T18:22:58.682Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1733,7 +1733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-09T18:19:36.424Z</v>
+        <v>2026-08-09T18:22:58.697Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1750,10 +1750,10 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-09T18:19:36.440Z</v>
+        <v>2026-08-09T18:22:58.712Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -1770,10 +1770,10 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-09T18:19:36.455Z</v>
+        <v>2026-08-09T18:22:58.728Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -1793,7 +1793,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-09T18:19:36.471Z</v>
+        <v>2026-08-09T18:22:58.744Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -1810,10 +1810,10 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-09T18:19:36.487Z</v>
+        <v>2026-08-09T18:22:58.758Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -1833,7 +1833,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-09T18:19:36.502Z</v>
+        <v>2026-08-09T18:22:58.774Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -1853,7 +1853,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-09T18:19:36.517Z</v>
+        <v>2026-08-09T18:22:58.790Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -1870,10 +1870,10 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-09T18:19:36.533Z</v>
+        <v>2026-08-09T18:22:58.804Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -1893,7 +1893,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-09T18:19:36.548Z</v>
+        <v>2026-08-09T18:22:58.820Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -1913,7 +1913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-09T18:19:36.563Z</v>
+        <v>2026-08-09T18:22:58.835Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -1930,10 +1930,10 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-09T18:19:36.579Z</v>
+        <v>2026-08-09T18:22:58.851Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -1953,7 +1953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-09T18:19:36.594Z</v>
+        <v>2026-08-09T18:22:58.867Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -1973,7 +1973,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-09T18:19:36.609Z</v>
+        <v>2026-08-09T18:22:58.882Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -1993,7 +1993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-09T18:19:36.625Z</v>
+        <v>2026-08-09T18:22:58.898Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2010,10 +2010,10 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-09T18:19:36.641Z</v>
+        <v>2026-08-09T18:22:58.913Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2033,7 +2033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-09T18:19:36.656Z</v>
+        <v>2026-08-09T18:22:58.929Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2053,7 +2053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-09T18:19:36.671Z</v>
+        <v>2026-08-09T18:22:58.944Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2073,7 +2073,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-09T18:19:36.687Z</v>
+        <v>2026-08-09T18:22:58.960Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2090,10 +2090,10 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-09T18:19:36.702Z</v>
+        <v>2026-08-09T18:22:58.976Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2110,10 +2110,10 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-09T18:19:36.717Z</v>
+        <v>2026-08-09T18:22:58.993Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2133,7 +2133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-09T18:19:36.733Z</v>
+        <v>2026-08-09T18:22:59.008Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2153,7 +2153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-09T18:19:36.748Z</v>
+        <v>2026-08-09T18:22:59.023Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2170,10 +2170,10 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-09T18:19:36.764Z</v>
+        <v>2026-08-09T18:22:59.038Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2190,10 +2190,10 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-09T18:19:36.778Z</v>
+        <v>2026-08-09T18:22:59.054Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2210,10 +2210,10 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-09T18:19:36.794Z</v>
+        <v>2026-08-09T18:22:59.069Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2233,7 +2233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-09T18:19:36.809Z</v>
+        <v>2026-08-09T18:22:59.085Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2253,7 +2253,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-09T18:19:36.825Z</v>
+        <v>2026-08-09T18:22:59.100Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2270,10 +2270,10 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-09T18:19:36.840Z</v>
+        <v>2026-08-09T18:22:59.116Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2290,10 +2290,10 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-09T18:19:36.856Z</v>
+        <v>2026-08-09T18:22:59.131Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2313,7 +2313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-09T18:19:36.872Z</v>
+        <v>2026-08-09T18:22:59.147Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2330,10 +2330,10 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-09T18:19:36.887Z</v>
+        <v>2026-08-09T18:22:59.163Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2350,10 +2350,10 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-09T18:19:36.904Z</v>
+        <v>2026-08-09T18:22:59.178Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2370,10 +2370,10 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-09T18:19:36.919Z</v>
+        <v>2026-08-09T18:22:59.194Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2390,10 +2390,10 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-09T18:19:36.934Z</v>
+        <v>2026-08-09T18:22:59.210Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2413,7 +2413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-09T18:19:36.949Z</v>
+        <v>2026-08-09T18:22:59.225Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2430,10 +2430,10 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-09T18:19:36.966Z</v>
+        <v>2026-08-09T18:22:59.240Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2453,7 +2453,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-09T18:19:36.979Z</v>
+        <v>2026-08-09T18:22:59.255Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2473,7 +2473,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-09T18:19:36.995Z</v>
+        <v>2026-08-09T18:22:59.271Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2493,7 +2493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-09T18:19:37.012Z</v>
+        <v>2026-08-09T18:22:59.288Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2513,7 +2513,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-09T18:19:37.026Z</v>
+        <v>2026-08-09T18:22:59.303Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2530,10 +2530,10 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-09T18:19:37.042Z</v>
+        <v>2026-08-09T18:22:59.318Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2550,10 +2550,10 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-09T18:19:37.058Z</v>
+        <v>2026-08-09T18:22:59.333Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2570,10 +2570,10 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-09T18:19:37.073Z</v>
+        <v>2026-08-09T18:22:59.349Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2593,7 +2593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-09T18:19:37.089Z</v>
+        <v>2026-08-09T18:22:59.365Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2613,7 +2613,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-09T18:19:37.104Z</v>
+        <v>2026-08-09T18:22:59.380Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2633,7 +2633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-09T18:19:37.119Z</v>
+        <v>2026-08-09T18:22:59.396Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2650,10 +2650,10 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-09T18:19:37.134Z</v>
+        <v>2026-08-09T18:22:59.412Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2670,10 +2670,10 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-09T18:19:37.149Z</v>
+        <v>2026-08-09T18:22:59.428Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2693,7 +2693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-09T18:19:37.164Z</v>
+        <v>2026-08-09T18:22:59.443Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2713,7 +2713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-09T18:19:37.181Z</v>
+        <v>2026-08-09T18:22:59.459Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2730,10 +2730,10 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-09T18:19:37.196Z</v>
+        <v>2026-08-09T18:22:59.475Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2750,10 +2750,10 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-09T18:19:37.211Z</v>
+        <v>2026-08-09T18:22:59.491Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -2770,10 +2770,10 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-09T18:19:37.227Z</v>
+        <v>2026-08-09T18:22:59.506Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -2790,10 +2790,10 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-09T18:19:37.243Z</v>
+        <v>2026-08-09T18:22:59.521Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -2810,10 +2810,10 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-09T18:19:37.258Z</v>
+        <v>2026-08-09T18:22:59.537Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-09T18:19:37.275Z</v>
+        <v>2026-08-09T18:22:59.553Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -2850,10 +2850,10 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-09T18:19:37.291Z</v>
+        <v>2026-08-09T18:22:59.568Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -2870,10 +2870,10 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-09T18:19:37.306Z</v>
+        <v>2026-08-09T18:22:59.584Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -2893,7 +2893,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-09T18:19:37.321Z</v>
+        <v>2026-08-09T18:22:59.599Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -2910,10 +2910,10 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-09T18:19:37.336Z</v>
+        <v>2026-08-09T18:22:59.615Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -2930,10 +2930,10 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-09T18:19:37.351Z</v>
+        <v>2026-08-09T18:22:59.631Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -2953,7 +2953,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-09T18:19:37.367Z</v>
+        <v>2026-08-09T18:22:59.647Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -2970,10 +2970,10 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-09T18:19:37.382Z</v>
+        <v>2026-08-09T18:22:59.663Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -2990,10 +2990,10 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-09T18:19:37.398Z</v>
+        <v>2026-08-09T18:22:59.678Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3010,10 +3010,10 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-09T18:19:37.413Z</v>
+        <v>2026-08-09T18:22:59.694Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3030,10 +3030,10 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-09T18:19:37.428Z</v>
+        <v>2026-08-09T18:22:59.711Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3050,10 +3050,10 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-09T18:19:37.444Z</v>
+        <v>2026-08-09T18:22:59.726Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3073,7 +3073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-09T18:19:37.458Z</v>
+        <v>2026-08-09T18:22:59.741Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3090,10 +3090,10 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-09T18:19:37.474Z</v>
+        <v>2026-08-09T18:22:59.756Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3113,7 +3113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-09T18:19:37.491Z</v>
+        <v>2026-08-09T18:22:59.772Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3133,7 +3133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-09T18:19:37.505Z</v>
+        <v>2026-08-09T18:22:59.787Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3150,10 +3150,10 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-09T18:19:37.521Z</v>
+        <v>2026-08-09T18:22:59.802Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3170,10 +3170,10 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-09T18:19:37.536Z</v>
+        <v>2026-08-09T18:22:59.818Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3193,7 +3193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-09T18:19:37.552Z</v>
+        <v>2026-08-09T18:22:59.834Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3210,10 +3210,10 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-09T18:19:37.568Z</v>
+        <v>2026-08-09T18:22:59.849Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3230,10 +3230,10 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-09T18:19:37.583Z</v>
+        <v>2026-08-09T18:22:59.866Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3250,10 +3250,10 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-09T18:19:37.599Z</v>
+        <v>2026-08-09T18:22:59.881Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3270,10 +3270,10 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-09T18:19:37.614Z</v>
+        <v>2026-08-09T18:22:59.897Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3290,10 +3290,10 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-09T18:19:37.629Z</v>
+        <v>2026-08-09T18:22:59.913Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3313,7 +3313,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-09T18:19:37.644Z</v>
+        <v>2026-08-09T18:22:59.928Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3333,7 +3333,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-09T18:19:37.661Z</v>
+        <v>2026-08-09T18:22:59.945Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3350,10 +3350,10 @@
         <v>PASS</v>
       </c>
       <c r="D148" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-09T18:19:37.676Z</v>
+        <v>2026-08-09T18:22:59.961Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3373,7 +3373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-09T18:19:37.692Z</v>
+        <v>2026-08-09T18:22:59.977Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3393,7 +3393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-09T18:19:37.708Z</v>
+        <v>2026-08-09T18:22:59.993Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3410,10 +3410,10 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-09T18:19:37.723Z</v>
+        <v>2026-08-09T18:23:00.009Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3430,10 +3430,10 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-09T18:19:37.739Z</v>
+        <v>2026-08-09T18:23:00.025Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3450,10 +3450,10 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-09T18:19:37.754Z</v>
+        <v>2026-08-09T18:23:00.041Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3473,7 +3473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-09T18:19:37.769Z</v>
+        <v>2026-08-09T18:23:00.056Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3490,10 +3490,10 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-09T18:19:37.785Z</v>
+        <v>2026-08-09T18:23:00.071Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3513,7 +3513,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-09T18:19:37.801Z</v>
+        <v>2026-08-09T18:23:00.087Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3533,7 +3533,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-09T18:19:37.817Z</v>
+        <v>2026-08-09T18:23:00.103Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3550,10 +3550,10 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-09T18:19:37.832Z</v>
+        <v>2026-08-09T18:23:00.119Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3573,7 +3573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-09T18:19:37.848Z</v>
+        <v>2026-08-09T18:23:00.135Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3590,10 +3590,10 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-09T18:19:37.863Z</v>
+        <v>2026-08-09T18:23:00.151Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3610,10 +3610,10 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-09T18:19:37.879Z</v>
+        <v>2026-08-09T18:23:00.166Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3630,10 +3630,10 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-09T18:19:37.896Z</v>
+        <v>2026-08-09T18:23:00.180Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3650,10 +3650,10 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-09T18:19:37.911Z</v>
+        <v>2026-08-09T18:23:00.197Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3673,7 +3673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-09T18:19:37.927Z</v>
+        <v>2026-08-09T18:23:00.213Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3693,7 +3693,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-09T18:19:37.941Z</v>
+        <v>2026-08-09T18:23:00.228Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3710,10 +3710,10 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-09T18:19:37.957Z</v>
+        <v>2026-08-09T18:23:00.243Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3733,7 +3733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-09T18:19:37.972Z</v>
+        <v>2026-08-09T18:23:00.258Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3750,10 +3750,10 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-09T18:19:37.987Z</v>
+        <v>2026-08-09T18:23:00.274Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -3773,7 +3773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-09T18:19:38.002Z</v>
+        <v>2026-08-09T18:23:00.289Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -3790,10 +3790,10 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-09T18:19:38.018Z</v>
+        <v>2026-08-09T18:23:00.304Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -3813,7 +3813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-09T18:19:38.034Z</v>
+        <v>2026-08-09T18:23:00.320Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -3833,7 +3833,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-09T18:19:38.050Z</v>
+        <v>2026-08-09T18:23:00.336Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -3853,7 +3853,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-09T18:19:38.066Z</v>
+        <v>2026-08-09T18:23:00.352Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -3873,7 +3873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-09T18:19:38.081Z</v>
+        <v>2026-08-09T18:23:00.366Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -3893,7 +3893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-09T18:19:38.097Z</v>
+        <v>2026-08-09T18:23:00.383Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -3913,7 +3913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-09T18:19:38.112Z</v>
+        <v>2026-08-09T18:23:00.398Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -3930,10 +3930,10 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-09T18:19:38.128Z</v>
+        <v>2026-08-09T18:23:00.413Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -3953,7 +3953,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-09T18:19:38.143Z</v>
+        <v>2026-08-09T18:23:00.428Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -3970,10 +3970,10 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-09T18:19:38.159Z</v>
+        <v>2026-08-09T18:23:00.443Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -3993,7 +3993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-09T18:19:38.177Z</v>
+        <v>2026-08-09T18:23:00.459Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4010,10 +4010,10 @@
         <v>PASS</v>
       </c>
       <c r="D181" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-09T18:19:38.190Z</v>
+        <v>2026-08-09T18:23:00.475Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4033,7 +4033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-09T18:19:38.205Z</v>
+        <v>2026-08-09T18:23:00.491Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4053,7 +4053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-09T18:19:38.221Z</v>
+        <v>2026-08-09T18:23:00.507Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4070,10 +4070,10 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>0.02 sec</v>
+        <v>0.03 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-09T18:19:38.237Z</v>
+        <v>2026-08-09T18:23:00.537Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4090,10 +4090,10 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-09T18:19:38.252Z</v>
+        <v>2026-08-09T18:23:00.556Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4110,10 +4110,10 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-09T18:19:38.267Z</v>
+        <v>2026-08-09T18:23:00.572Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4133,7 +4133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-09T18:19:38.283Z</v>
+        <v>2026-08-09T18:23:00.588Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4150,10 +4150,10 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-09T18:19:38.299Z</v>
+        <v>2026-08-09T18:23:00.600Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4170,10 +4170,10 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-09T18:19:38.314Z</v>
+        <v>2026-08-09T18:23:00.616Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4193,7 +4193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-09T18:19:38.330Z</v>
+        <v>2026-08-09T18:23:00.632Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4213,7 +4213,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-09T18:19:38.346Z</v>
+        <v>2026-08-09T18:23:00.648Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4230,10 +4230,10 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-09T18:19:38.363Z</v>
+        <v>2026-08-09T18:23:00.664Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4250,10 +4250,10 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-09T18:19:38.377Z</v>
+        <v>2026-08-09T18:23:00.680Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4270,10 +4270,10 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-09T18:19:38.395Z</v>
+        <v>2026-08-09T18:23:00.696Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4293,7 +4293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-09T18:19:38.409Z</v>
+        <v>2026-08-09T18:23:00.711Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4313,7 +4313,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-09T18:19:38.423Z</v>
+        <v>2026-08-09T18:23:00.726Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4333,7 +4333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-09T18:19:38.438Z</v>
+        <v>2026-08-09T18:23:00.741Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4350,10 +4350,10 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-09T18:19:38.453Z</v>
+        <v>2026-08-09T18:23:00.757Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4370,10 +4370,10 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-09T18:19:38.469Z</v>
+        <v>2026-08-09T18:23:00.772Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4393,7 +4393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-09T18:19:38.485Z</v>
+        <v>2026-08-09T18:23:00.789Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4413,7 +4413,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-09T18:19:38.500Z</v>
+        <v>2026-08-09T18:23:00.804Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4433,7 +4433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-09T18:19:38.515Z</v>
+        <v>2026-08-09T18:23:00.820Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4453,7 +4453,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-09T18:19:38.531Z</v>
+        <v>2026-08-09T18:23:00.836Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4470,10 +4470,10 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-09T18:19:38.547Z</v>
+        <v>2026-08-09T18:23:00.851Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4490,10 +4490,10 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-09T18:19:38.562Z</v>
+        <v>2026-08-09T18:23:00.867Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4513,7 +4513,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-09T18:19:38.578Z</v>
+        <v>2026-08-09T18:23:00.883Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4530,10 +4530,10 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-09T18:19:38.595Z</v>
+        <v>2026-08-09T18:23:00.898Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4553,7 +4553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-09T18:19:38.609Z</v>
+        <v>2026-08-09T18:23:00.913Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4570,10 +4570,10 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-09T18:19:38.624Z</v>
+        <v>2026-08-09T18:23:00.929Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4590,10 +4590,10 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-09T18:19:38.639Z</v>
+        <v>2026-08-09T18:23:00.945Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4610,10 +4610,10 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-09T18:19:38.654Z</v>
+        <v>2026-08-09T18:23:00.961Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4630,10 +4630,10 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-09T18:19:38.669Z</v>
+        <v>2026-08-09T18:23:00.978Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4650,10 +4650,10 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-09T18:19:38.685Z</v>
+        <v>2026-08-09T18:23:00.993Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4673,7 +4673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-09T18:19:38.701Z</v>
+        <v>2026-08-09T18:23:01.009Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4690,10 +4690,10 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-09T18:19:38.715Z</v>
+        <v>2026-08-09T18:23:01.025Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4713,7 +4713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-09T18:19:38.731Z</v>
+        <v>2026-08-09T18:23:01.041Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4730,10 +4730,10 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-09T18:19:38.746Z</v>
+        <v>2026-08-09T18:23:01.057Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4753,7 +4753,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-09T18:19:38.762Z</v>
+        <v>2026-08-09T18:23:01.073Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -4770,10 +4770,10 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-09T18:19:38.777Z</v>
+        <v>2026-08-09T18:23:01.089Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -4790,10 +4790,10 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-09T18:19:38.794Z</v>
+        <v>2026-08-09T18:23:01.104Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -4810,10 +4810,10 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-09T18:19:38.810Z</v>
+        <v>2026-08-09T18:23:01.119Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -4830,10 +4830,10 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-09T18:19:38.826Z</v>
+        <v>2026-08-09T18:23:01.136Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -4853,7 +4853,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-09T18:19:38.841Z</v>
+        <v>2026-08-09T18:23:01.151Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -4873,7 +4873,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-09T18:19:38.856Z</v>
+        <v>2026-08-09T18:23:01.166Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -4893,7 +4893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-09T18:19:38.872Z</v>
+        <v>2026-08-09T18:23:01.182Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -4910,10 +4910,10 @@
         <v>PASS</v>
       </c>
       <c r="D226" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-09T18:19:38.888Z</v>
+        <v>2026-08-09T18:23:01.197Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -4933,7 +4933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-09T18:19:38.903Z</v>
+        <v>2026-08-09T18:23:01.212Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -4953,7 +4953,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-09T18:19:38.919Z</v>
+        <v>2026-08-09T18:23:01.228Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -4970,10 +4970,10 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-09T18:19:38.935Z</v>
+        <v>2026-08-09T18:23:01.242Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -4993,7 +4993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-09T18:19:38.951Z</v>
+        <v>2026-08-09T18:23:01.258Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5013,7 +5013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-09T18:19:38.965Z</v>
+        <v>2026-08-09T18:23:01.273Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5033,7 +5033,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-09T18:19:38.981Z</v>
+        <v>2026-08-09T18:23:01.290Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5050,10 +5050,10 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-09T18:19:38.997Z</v>
+        <v>2026-08-09T18:23:01.304Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5070,10 +5070,10 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-09T18:19:39.012Z</v>
+        <v>2026-08-09T18:23:01.320Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5093,7 +5093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-09T18:19:39.029Z</v>
+        <v>2026-08-09T18:23:01.336Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5113,7 +5113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-09T18:19:39.045Z</v>
+        <v>2026-08-09T18:23:01.352Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5133,7 +5133,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-09T18:19:39.059Z</v>
+        <v>2026-08-09T18:23:01.366Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5153,7 +5153,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-09T18:19:39.076Z</v>
+        <v>2026-08-09T18:23:01.382Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5173,7 +5173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-09T18:19:39.091Z</v>
+        <v>2026-08-09T18:23:01.397Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5193,7 +5193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-09T18:19:39.107Z</v>
+        <v>2026-08-09T18:23:01.413Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5213,7 +5213,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-09T18:19:39.122Z</v>
+        <v>2026-08-09T18:23:01.428Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5233,7 +5233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-09T18:19:39.137Z</v>
+        <v>2026-08-09T18:23:01.444Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5250,10 +5250,10 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-09T18:19:39.153Z</v>
+        <v>2026-08-09T18:23:01.459Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5273,7 +5273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-09T18:19:39.169Z</v>
+        <v>2026-08-09T18:23:01.476Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5293,7 +5293,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-09T18:19:39.184Z</v>
+        <v>2026-08-09T18:23:01.490Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5310,10 +5310,10 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-09T18:19:39.199Z</v>
+        <v>2026-08-09T18:23:01.507Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5330,10 +5330,10 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-09T18:19:39.215Z</v>
+        <v>2026-08-09T18:23:01.522Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5350,10 +5350,10 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-09T18:19:39.231Z</v>
+        <v>2026-08-09T18:23:01.537Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5370,10 +5370,10 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-09T18:19:39.247Z</v>
+        <v>2026-08-09T18:23:01.552Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5390,10 +5390,10 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-09T18:19:39.263Z</v>
+        <v>2026-08-09T18:23:01.567Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5410,10 +5410,10 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-09T18:19:39.279Z</v>
+        <v>2026-08-09T18:23:01.582Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5433,7 +5433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-09T18:19:39.294Z</v>
+        <v>2026-08-09T18:23:01.598Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5450,10 +5450,10 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-09T18:19:39.309Z</v>
+        <v>2026-08-09T18:23:01.614Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5473,7 +5473,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-09T18:19:39.324Z</v>
+        <v>2026-08-09T18:23:01.629Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5493,7 +5493,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-09T18:19:39.339Z</v>
+        <v>2026-08-09T18:23:01.644Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5513,7 +5513,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-09T18:19:39.355Z</v>
+        <v>2026-08-09T18:23:01.661Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5530,10 +5530,10 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-09T18:19:39.371Z</v>
+        <v>2026-08-09T18:23:01.677Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5553,7 +5553,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-09T18:19:39.385Z</v>
+        <v>2026-08-09T18:23:01.692Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5570,10 +5570,10 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-09T18:19:39.400Z</v>
+        <v>2026-08-09T18:23:01.709Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5590,10 +5590,10 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-09T18:19:39.416Z</v>
+        <v>2026-08-09T18:23:01.723Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5613,7 +5613,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-09T18:19:39.432Z</v>
+        <v>2026-08-09T18:23:01.740Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5630,10 +5630,10 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-09T18:19:39.448Z</v>
+        <v>2026-08-09T18:23:01.755Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5650,10 +5650,10 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-09T18:19:39.462Z</v>
+        <v>2026-08-09T18:23:01.771Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5670,10 +5670,10 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-09T18:19:39.478Z</v>
+        <v>2026-08-09T18:23:01.785Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5690,10 +5690,10 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-09T18:19:39.495Z</v>
+        <v>2026-08-09T18:23:01.801Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5713,7 +5713,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-09T18:19:39.510Z</v>
+        <v>2026-08-09T18:23:01.816Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5730,10 +5730,10 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-09T18:19:39.525Z</v>
+        <v>2026-08-09T18:23:01.832Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5750,10 +5750,10 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-09T18:19:39.541Z</v>
+        <v>2026-08-09T18:23:01.848Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -5773,7 +5773,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-09T18:19:39.555Z</v>
+        <v>2026-08-09T18:23:01.863Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -5793,7 +5793,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-09T18:19:39.570Z</v>
+        <v>2026-08-09T18:23:01.878Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -5813,7 +5813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-09T18:19:39.587Z</v>
+        <v>2026-08-09T18:23:01.894Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -5830,10 +5830,10 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-09T18:19:39.601Z</v>
+        <v>2026-08-09T18:23:01.911Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -5850,10 +5850,10 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-09T18:19:39.618Z</v>
+        <v>2026-08-09T18:23:01.926Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -5870,10 +5870,10 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-09T18:19:39.633Z</v>
+        <v>2026-08-09T18:23:01.942Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -5890,10 +5890,10 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-09T18:19:39.649Z</v>
+        <v>2026-08-09T18:23:01.957Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -5910,10 +5910,10 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-09T18:19:39.665Z</v>
+        <v>2026-08-09T18:23:01.972Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -5933,7 +5933,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-09T18:19:39.681Z</v>
+        <v>2026-08-09T18:23:01.988Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -5950,10 +5950,10 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-09T18:19:39.696Z</v>
+        <v>2026-08-09T18:23:02.004Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -5970,10 +5970,10 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-09T18:19:39.712Z</v>
+        <v>2026-08-09T18:23:02.018Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -5990,10 +5990,10 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-09T18:19:39.727Z</v>
+        <v>2026-08-09T18:23:02.034Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6010,10 +6010,10 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-09T18:19:39.742Z</v>
+        <v>2026-08-09T18:23:02.050Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6033,7 +6033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-09T18:19:39.757Z</v>
+        <v>2026-08-09T18:23:02.065Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6050,10 +6050,10 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-09T18:19:39.774Z</v>
+        <v>2026-08-09T18:23:02.080Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6070,10 +6070,10 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-09T18:19:39.788Z</v>
+        <v>2026-08-09T18:23:02.096Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6090,10 +6090,10 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-09T18:19:39.803Z</v>
+        <v>2026-08-09T18:23:02.112Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6113,7 +6113,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-09T18:19:39.819Z</v>
+        <v>2026-08-09T18:23:02.128Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6130,10 +6130,10 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-09T18:19:39.835Z</v>
+        <v>2026-08-09T18:23:02.143Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6153,7 +6153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-09T18:19:39.850Z</v>
+        <v>2026-08-09T18:23:02.158Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6173,7 +6173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-09T18:19:39.866Z</v>
+        <v>2026-08-09T18:23:02.174Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6190,10 +6190,10 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-09T18:19:39.882Z</v>
+        <v>2026-08-09T18:23:02.189Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6210,10 +6210,10 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-09T18:19:39.897Z</v>
+        <v>2026-08-09T18:23:02.205Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6230,10 +6230,10 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-09T18:19:39.914Z</v>
+        <v>2026-08-09T18:23:02.221Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6250,10 +6250,10 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-09T18:19:39.930Z</v>
+        <v>2026-08-09T18:23:02.237Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6270,10 +6270,10 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-09T18:19:39.944Z</v>
+        <v>2026-08-09T18:23:02.253Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6290,10 +6290,10 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-09T18:19:39.960Z</v>
+        <v>2026-08-09T18:23:02.268Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6310,10 +6310,10 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-09T18:19:39.976Z</v>
+        <v>2026-08-09T18:23:02.284Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6333,7 +6333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-09T18:19:39.991Z</v>
+        <v>2026-08-09T18:23:02.298Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6353,7 +6353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-09T18:19:40.007Z</v>
+        <v>2026-08-09T18:23:02.314Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6373,7 +6373,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-09T18:19:40.022Z</v>
+        <v>2026-08-09T18:23:02.329Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6390,10 +6390,10 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-09T18:19:40.037Z</v>
+        <v>2026-08-09T18:23:02.345Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6410,10 +6410,10 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-09T18:19:40.053Z</v>
+        <v>2026-08-09T18:23:02.360Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6433,7 +6433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-09T18:19:40.068Z</v>
+        <v>2026-08-09T18:23:02.376Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6450,10 +6450,10 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-09T18:19:40.084Z</v>
+        <v>2026-08-09T18:23:02.391Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6470,10 +6470,10 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-09T18:19:40.099Z</v>
+        <v>2026-08-09T18:23:02.407Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6493,7 +6493,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-09T18:19:40.115Z</v>
+        <v>2026-08-09T18:23:02.424Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6513,7 +6513,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-09T18:19:40.131Z</v>
+        <v>2026-08-09T18:23:02.439Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6530,10 +6530,10 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-09T18:19:40.147Z</v>
+        <v>2026-08-09T18:23:02.454Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6550,10 +6550,10 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-09T18:19:40.162Z</v>
+        <v>2026-08-09T18:23:02.470Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6570,10 +6570,10 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-09T18:19:40.178Z</v>
+        <v>2026-08-09T18:23:02.485Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6593,7 +6593,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-09T18:19:40.195Z</v>
+        <v>2026-08-09T18:23:02.501Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6610,10 +6610,10 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-09T18:19:40.211Z</v>
+        <v>2026-08-09T18:23:02.516Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6633,7 +6633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-09T18:19:40.226Z</v>
+        <v>2026-08-09T18:23:02.531Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6650,10 +6650,10 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-09T18:19:40.241Z</v>
+        <v>2026-08-09T18:23:02.547Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6670,10 +6670,10 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-09T18:19:40.256Z</v>
+        <v>2026-08-09T18:23:02.563Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6690,10 +6690,10 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-09T18:19:40.273Z</v>
+        <v>2026-08-09T18:23:02.578Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6710,10 +6710,10 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-09T18:19:40.288Z</v>
+        <v>2026-08-09T18:23:02.594Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6733,7 +6733,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-09T18:19:40.303Z</v>
+        <v>2026-08-09T18:23:02.609Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6750,10 +6750,10 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-09T18:19:40.319Z</v>
+        <v>2026-08-09T18:23:02.624Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -6770,10 +6770,10 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-09T18:19:40.334Z</v>
+        <v>2026-08-09T18:23:02.640Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -6793,7 +6793,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-09T18:19:40.349Z</v>
+        <v>2026-08-09T18:23:02.655Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -6813,7 +6813,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-09T18:19:40.365Z</v>
+        <v>2026-08-09T18:23:02.671Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -6833,7 +6833,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-09T18:19:40.382Z</v>
+        <v>2026-08-09T18:23:02.687Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -6853,7 +6853,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-09T18:19:40.396Z</v>
+        <v>2026-08-09T18:23:02.702Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -6873,7 +6873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-09T18:19:40.412Z</v>
+        <v>2026-08-09T18:23:02.718Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -6893,7 +6893,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-09T18:19:40.427Z</v>
+        <v>2026-08-09T18:23:02.733Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -6913,7 +6913,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-09T18:19:40.444Z</v>
+        <v>2026-08-09T18:23:02.749Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -6930,10 +6930,10 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-09T18:19:40.460Z</v>
+        <v>2026-08-09T18:23:02.764Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -6950,10 +6950,10 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-09T18:19:40.476Z</v>
+        <v>2026-08-09T18:23:02.779Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -6973,7 +6973,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-09T18:19:40.490Z</v>
+        <v>2026-08-09T18:23:02.794Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -6990,10 +6990,10 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-09T18:19:40.505Z</v>
+        <v>2026-08-09T18:23:02.810Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7013,7 +7013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-09T18:19:40.520Z</v>
+        <v>2026-08-09T18:23:02.825Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7033,7 +7033,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-09T18:19:40.535Z</v>
+        <v>2026-08-09T18:23:02.840Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7053,7 +7053,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-09T18:19:40.551Z</v>
+        <v>2026-08-09T18:23:02.856Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7070,10 +7070,10 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-09T18:19:40.567Z</v>
+        <v>2026-08-09T18:23:02.871Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7093,7 +7093,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-09T18:19:40.583Z</v>
+        <v>2026-08-09T18:23:02.887Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7113,7 +7113,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-09T18:19:40.598Z</v>
+        <v>2026-08-09T18:23:02.902Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7130,10 +7130,10 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-09T18:19:40.614Z</v>
+        <v>2026-08-09T18:23:02.917Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7153,7 +7153,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-09T18:19:40.629Z</v>
+        <v>2026-08-09T18:23:02.932Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7173,7 +7173,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-09T18:19:40.645Z</v>
+        <v>2026-08-09T18:23:02.948Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7190,10 +7190,10 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-09T18:19:40.660Z</v>
+        <v>2026-08-09T18:23:02.964Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7213,7 +7213,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-09T18:19:40.676Z</v>
+        <v>2026-08-09T18:23:02.980Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7233,7 +7233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-09T18:19:40.691Z</v>
+        <v>2026-08-09T18:23:02.995Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7250,10 +7250,10 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-09T18:19:40.707Z</v>
+        <v>2026-08-09T18:23:03.010Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7270,10 +7270,10 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-09T18:19:40.722Z</v>
+        <v>2026-08-09T18:23:03.026Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7290,10 +7290,10 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-09T18:19:40.737Z</v>
+        <v>2026-08-09T18:23:03.042Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7310,10 +7310,10 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-09T18:19:40.753Z</v>
+        <v>2026-08-09T18:23:03.057Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7333,7 +7333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-09T18:19:40.768Z</v>
+        <v>2026-08-09T18:23:03.073Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7353,7 +7353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-09T18:19:40.784Z</v>
+        <v>2026-08-09T18:23:03.088Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7370,10 +7370,10 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-09T18:19:40.799Z</v>
+        <v>2026-08-09T18:23:03.104Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7390,10 +7390,10 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-09T18:19:40.815Z</v>
+        <v>2026-08-09T18:23:03.119Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7410,10 +7410,10 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-09T18:19:40.830Z</v>
+        <v>2026-08-09T18:23:03.135Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7433,7 +7433,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-09T18:19:40.846Z</v>
+        <v>2026-08-09T18:23:03.151Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7450,10 +7450,10 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-09T18:19:40.862Z</v>
+        <v>2026-08-09T18:23:03.166Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7470,10 +7470,10 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-09T18:19:40.877Z</v>
+        <v>2026-08-09T18:23:03.184Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7490,10 +7490,10 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-09T18:19:40.893Z</v>
+        <v>2026-08-09T18:23:03.198Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7510,10 +7510,10 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-09T18:19:40.908Z</v>
+        <v>2026-08-09T18:23:03.214Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7533,7 +7533,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-09T18:19:40.923Z</v>
+        <v>2026-08-09T18:23:03.228Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7550,10 +7550,10 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-09T18:19:40.938Z</v>
+        <v>2026-08-09T18:23:03.244Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7573,7 +7573,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-09T18:19:40.954Z</v>
+        <v>2026-08-09T18:23:03.260Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7590,10 +7590,10 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-09T18:19:40.970Z</v>
+        <v>2026-08-09T18:23:03.275Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7610,10 +7610,10 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-09T18:19:40.984Z</v>
+        <v>2026-08-09T18:23:03.292Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7633,7 +7633,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-09T18:19:41.000Z</v>
+        <v>2026-08-09T18:23:03.306Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7650,10 +7650,10 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-09T18:19:41.015Z</v>
+        <v>2026-08-09T18:23:03.322Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7673,7 +7673,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-09T18:19:41.031Z</v>
+        <v>2026-08-09T18:23:03.338Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7690,10 +7690,10 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-09T18:19:41.047Z</v>
+        <v>2026-08-09T18:23:03.352Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7713,7 +7713,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-09T18:19:41.063Z</v>
+        <v>2026-08-09T18:23:03.368Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7733,7 +7733,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-09T18:19:41.079Z</v>
+        <v>2026-08-09T18:23:03.384Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7753,7 +7753,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-09T18:19:41.094Z</v>
+        <v>2026-08-09T18:23:03.399Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -7770,10 +7770,10 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-09T18:19:41.110Z</v>
+        <v>2026-08-09T18:23:03.413Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -7793,7 +7793,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-09T18:19:41.125Z</v>
+        <v>2026-08-09T18:23:03.429Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -7810,10 +7810,10 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-09T18:19:41.140Z</v>
+        <v>2026-08-09T18:23:03.445Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -7830,10 +7830,10 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-09T18:19:41.156Z</v>
+        <v>2026-08-09T18:23:03.461Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -7850,10 +7850,10 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-09T18:19:41.172Z</v>
+        <v>2026-08-09T18:23:03.476Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -7873,7 +7873,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-09T18:19:41.188Z</v>
+        <v>2026-08-09T18:23:03.492Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -7893,7 +7893,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-09T18:19:41.204Z</v>
+        <v>2026-08-09T18:23:03.508Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -7913,7 +7913,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-09T18:19:41.219Z</v>
+        <v>2026-08-09T18:23:03.524Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -7933,7 +7933,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-09T18:19:41.234Z</v>
+        <v>2026-08-09T18:23:03.539Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -7953,7 +7953,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-09T18:19:41.250Z</v>
+        <v>2026-08-09T18:23:03.555Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -7970,10 +7970,10 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-09T18:19:41.266Z</v>
+        <v>2026-08-09T18:23:03.570Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -7993,7 +7993,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-09T18:19:41.282Z</v>
+        <v>2026-08-09T18:23:03.586Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8013,7 +8013,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-09T18:19:41.298Z</v>
+        <v>2026-08-09T18:23:03.601Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8030,10 +8030,10 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-09T18:19:41.314Z</v>
+        <v>2026-08-09T18:23:03.617Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8053,7 +8053,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-09T18:19:41.329Z</v>
+        <v>2026-08-09T18:23:03.633Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8073,7 +8073,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-09T18:19:41.344Z</v>
+        <v>2026-08-09T18:23:03.648Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8090,10 +8090,10 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-09T18:19:41.359Z</v>
+        <v>2026-08-09T18:23:03.664Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8113,7 +8113,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-09T18:19:41.374Z</v>
+        <v>2026-08-09T18:23:03.678Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8133,7 +8133,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-09T18:19:41.390Z</v>
+        <v>2026-08-09T18:23:03.694Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8150,10 +8150,10 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.02 sec</v>
+        <v>0.01 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-09T18:19:41.406Z</v>
+        <v>2026-08-09T18:23:03.709Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8173,7 +8173,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-09T18:19:41.421Z</v>
+        <v>2026-08-09T18:23:03.724Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8193,7 +8193,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-09T18:19:41.437Z</v>
+        <v>2026-08-09T18:23:03.740Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8210,10 +8210,10 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-09T18:19:41.452Z</v>
+        <v>2026-08-09T18:23:03.756Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8233,7 +8233,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-09T18:19:41.467Z</v>
+        <v>2026-08-09T18:23:03.771Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8253,7 +8253,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-09T18:19:41.483Z</v>
+        <v>2026-08-09T18:23:03.787Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8273,7 +8273,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-09T18:19:41.500Z</v>
+        <v>2026-08-09T18:23:03.803Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8290,10 +8290,10 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-09T18:19:41.515Z</v>
+        <v>2026-08-09T18:23:03.819Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8313,7 +8313,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-09T18:19:41.531Z</v>
+        <v>2026-08-09T18:23:03.835Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8333,7 +8333,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-09T18:19:41.546Z</v>
+        <v>2026-08-09T18:23:03.850Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8353,7 +8353,7 @@
         <v>0.01 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-09T18:19:41.561Z</v>
+        <v>2026-08-09T18:23:03.864Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8373,7 +8373,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-09T18:19:41.577Z</v>
+        <v>2026-08-09T18:23:03.880Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8393,7 +8393,7 @@
         <v>0.02 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-09T18:19:41.593Z</v>
+        <v>2026-08-09T18:23:03.896Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8410,10 +8410,10 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.01 sec</v>
+        <v>0.02 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-09T18:19:41.608Z</v>
+        <v>2026-08-09T18:23:03.912Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>
